--- a/ready-for-annotation/de/dailymail.co.uk.170665.xlsx
+++ b/ready-for-annotation/de/dailymail.co.uk.170665.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="333">
   <si>
     <t>ID</t>
   </si>
@@ -50,22 +50,40 @@
     <t>1</t>
   </si>
   <si>
-    <t>23</t>
+    <t>10</t>
   </si>
   <si>
     <t>_</t>
   </si>
   <si>
+    <t>senken</t>
+  </si>
+  <si>
+    <t>Das £2- pro Tag Medikament , das Herzinfarktrisiko senken kann</t>
+  </si>
+  <si>
+    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s1_0</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Nachdem?</t>
+  </si>
+  <si>
     <t>profitieren</t>
   </si>
   <si>
-    <t>Das £2- pro Tag Medikament , das Herzinfarktrisiko senken kann Tausende von Herzinfarktpatienten werden von einem £2- pro Tag Medikament profitieren , nachdem von den Behörden empfohlen wurde , dieses mehr Leuten für einen längeren Zeitraum zu verabreichen .</t>
-  </si>
-  <si>
-    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s1_0</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>Tausende von Herzinfarktpatienten werden von einem £2- pro Tag Medikament profitieren , nachdem von den Behörden empfohlen wurde , dieses mehr Leuten für einen längeren Zeitraum zu verabreichen .</t>
+  </si>
+  <si>
+    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s2_0</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>5</t>
@@ -77,10 +95,10 @@
     <t>Das gerinnungshemmende Medikament Ticagrelor reduziert das Risiko wiederholter Herzinfarkte für Personen mit einer Herzerkrankung .</t>
   </si>
   <si>
-    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s2_0</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s3_0</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>11</t>
@@ -92,13 +110,7 @@
     <t>Das Medikament wird bereits 12 Monate lang nach einem Herzinfarkt verabreicht , wodurch das Risiko eines Schlaganfalls oder eines weiteren Herzinfarkts reduziert wird .</t>
   </si>
   <si>
-    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s3_0</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s4_0</t>
   </si>
   <si>
     <t>empfehlen</t>
@@ -107,25 +119,28 @@
     <t>Die Regulierungsbehörde NICE des NHS hat eine vier Jahre lange Einnahme empfohlen , um das Risiko kardiovaskulärer Probleme weiter zu reduzieren .</t>
   </si>
   <si>
-    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s4_0</t>
-  </si>
-  <si>
     <t>file://conllu/de/dailymail.co.uk.170665.conllu#s5_0</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
+    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s6_0</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>erleiden</t>
   </si>
   <si>
     <t>Rund 140.000 Leute erleiden jedes Jahr einen Herzinfarkt und ein Viertel davon erleiden einen weiteren Herzinfarkt oder einen Schlaganfall .</t>
   </si>
   <si>
-    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s6_0</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s7_0</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>Durch?</t>
@@ -137,22 +152,16 @@
     <t>Herzinfarkte und Schlaganfälle werden durch Ansammlungen fetthaltigen Materials in den Arterienwänden verursacht , die Beläge bilden .</t>
   </si>
   <si>
-    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s7_0</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s8_0</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>Wenn der Belag auseinanderbricht , kann es ein Blutgerinnsel verursachen , das den Blutfluss bis zum zu dem Herzen verstopft und dadurch einen Herzinfarkt verursacht .</t>
   </si>
   <si>
-    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s8_0</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s9_0</t>
   </si>
   <si>
     <t>fließen</t>
@@ -161,7 +170,7 @@
     <t>Wenn sich das Blutgerinnsel löst , kann es durch den Blutstrom fließen und den Blutfluss zum zu dem Gehirn verstopfen , was einen Schlaganfall verursacht .</t>
   </si>
   <si>
-    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s9_0</t>
+    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s10_0</t>
   </si>
   <si>
     <t>unterliegen</t>
@@ -170,7 +179,7 @@
     <t>Personen , die bereits einen Herzinfarkt hatten , unterliegen einem höheren Risiko einen weiteren zu haben .</t>
   </si>
   <si>
-    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s10_0</t>
+    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s11_0</t>
   </si>
   <si>
     <t>19</t>
@@ -182,16 +191,19 @@
     <t>Ticagrelor , das von dem britischen Unternehmen AstraZeneca hergestellt wird und unter dem Handelsnamen Brilique vertrieben wird , reduziert dieses Risiko , indem es die Bildung von Blutgerinnseln unwahrscheinlicher macht .</t>
   </si>
   <si>
-    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s11_0</t>
+    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s12_0</t>
+  </si>
+  <si>
+    <t>13</t>
   </si>
   <si>
     <t>Der Anleitungsentwurf von NICE , der heute veröffentlicht wurde , empfiehlt eine 12-monatige Einnahme von 90mg Ticagrelor , gefolgt von 60mg mit einer zweimal täglichen Einnahme von Aspirin für die nächsten drei Jahre .</t>
   </si>
   <si>
-    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s12_0</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s13_0</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
   <si>
     <t>sagen</t>
@@ -200,10 +212,10 @@
     <t>Professor Carole Longson , Direktorin des NICE Gesundheitstechnologieevaluierungszentrums sagte : &amp;quot; Trotz der Verfügbarkeit von Sekundärprävention haben ein Viertel aller Personen , die einen Herzinfarkt erlitten haben , einen weiteren Herzinfarkt oder einen Schlaganfall oft mit desaströsen Folgen . &amp;quot;</t>
   </si>
   <si>
-    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s13_0</t>
-  </si>
-  <si>
-    <t>14</t>
+    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s14_0</t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
   <si>
     <t>16</t>
@@ -215,10 +227,7 @@
     <t>Die Angst vor einem erneuten Herzinfarkt kann erhebliche negative Auswirkungen auf die Lebensqualität einer Person haben .</t>
   </si>
   <si>
-    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s14_0</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s15_0</t>
   </si>
   <si>
     <t>zeigen</t>
@@ -227,7 +236,10 @@
     <t>Die Erfahrung zeigt , dass Ticagrelor in Kombination mit Aspirin effektiv bei der Reduzierung weiterer Herzinfarkte und Schlaganfälle bei Leuten ist , die bereits einen Herzinfarkt hatten .</t>
   </si>
   <si>
-    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s15_0</t>
+    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s16_0</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
   <si>
     <t>freuen</t>
@@ -236,10 +248,10 @@
     <t>Durch eine vorläufige Empfehlung von Ticagrelor freuen wir uns , dass wir in der Lage sind , verfügbare Behandlungsoptionen an tausende von Menschen zu erweitern , die davon profitieren können .</t>
   </si>
   <si>
-    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s16_0</t>
-  </si>
-  <si>
-    <t>17</t>
+    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s17_0</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>sein (sein beschränken)</t>
@@ -248,10 +260,7 @@
     <t>Die Information über die Wirksamkeit und Sicherheit von Ticagrelor vor allem das Blutungsrisiko ist auf einen Zeitraum von bis zu drei Jahren beschränkt .</t>
   </si>
   <si>
-    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s17_0</t>
-  </si>
-  <si>
-    <t>18</t>
+    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s18_0</t>
   </si>
   <si>
     <t>empfiehlen</t>
@@ -260,7 +269,7 @@
     <t>Der Anleitungsentwurf empfiehlt keine Behandlung , die über diesen Zeitraum hinausgeht .</t>
   </si>
   <si>
-    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s18_0</t>
+    <t>file://conllu/de/dailymail.co.uk.170665.conllu#s19_0</t>
   </si>
   <si>
     <t>WORD</t>
@@ -296,7 +305,7 @@
     <t>REF_DIST_ANTE</t>
   </si>
   <si>
-    <t># text = Das £2-pro Tag- Medikament, das Herzinfarktrisiko senken kann Tausende von Herzinfarktpatienten werden von einem £2-pro Tag-Medikament profitieren, nachdem von den Behörden empfohlen wurde, dieses mehr Leuten für einen längeren Zeitraum zu verabreichen.</t>
+    <t># text = Das £2-pro Tag- Medikament, das Herzinfarktrisiko senken kann</t>
   </si>
   <si>
     <t>Das</t>
@@ -338,214 +347,214 @@
     <t>Herzinfarktrisiko</t>
   </si>
   <si>
+    <t>OBJ</t>
+  </si>
+  <si>
+    <t>kann</t>
+  </si>
+  <si>
+    <t># text = Tausende von Herzinfarktpatienten werden von einem £2-pro Tag-Medikament profitieren, nachdem von den Behörden empfohlen wurde, dieses mehr Leuten für einen längeren Zeitraum zu verabreichen.</t>
+  </si>
+  <si>
+    <t>Tausende</t>
+  </si>
+  <si>
+    <t>von</t>
+  </si>
+  <si>
+    <t>Herzinfarktpatienten</t>
+  </si>
+  <si>
+    <t>werden</t>
+  </si>
+  <si>
+    <t>einem</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>indef-np.a</t>
+  </si>
+  <si>
+    <t>nachdem</t>
+  </si>
+  <si>
+    <t>den</t>
+  </si>
+  <si>
+    <t>Behörden</t>
+  </si>
+  <si>
+    <t>empfohlen</t>
+  </si>
+  <si>
+    <t>wurde</t>
+  </si>
+  <si>
+    <t>dieses</t>
+  </si>
+  <si>
+    <t>other_4</t>
+  </si>
+  <si>
+    <t>pron.pds</t>
+  </si>
+  <si>
+    <t>mehr</t>
+  </si>
+  <si>
+    <t>Leuten</t>
+  </si>
+  <si>
     <t>OBJ_3</t>
   </si>
   <si>
-    <t>senken</t>
-  </si>
-  <si>
-    <t>kann</t>
-  </si>
-  <si>
-    <t>Tausende</t>
-  </si>
-  <si>
-    <t>von</t>
-  </si>
-  <si>
-    <t>Herzinfarktpatienten</t>
+    <t>def-np.dem</t>
+  </si>
+  <si>
+    <t>für</t>
+  </si>
+  <si>
+    <t>einen</t>
+  </si>
+  <si>
+    <t>längeren</t>
+  </si>
+  <si>
+    <t>Zeitraum</t>
   </si>
   <si>
     <t>other_3</t>
   </si>
   <si>
-    <t>werden</t>
-  </si>
-  <si>
-    <t>einem</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
-    <t>indef-np.a</t>
-  </si>
-  <si>
-    <t>nachdem</t>
-  </si>
-  <si>
-    <t>den</t>
-  </si>
-  <si>
-    <t>Behörden</t>
-  </si>
-  <si>
-    <t>empfohlen</t>
-  </si>
-  <si>
-    <t>wurde</t>
-  </si>
-  <si>
-    <t>dieses</t>
-  </si>
-  <si>
-    <t>pron.pds</t>
-  </si>
-  <si>
-    <t>mehr</t>
-  </si>
-  <si>
-    <t>Leuten</t>
+    <t>zu</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t># text = Das gerinnungshemmende Medikament Ticagrelor reduziert das Risiko wiederholter Herzinfarkte für Personen mit einer Herzerkrankung.</t>
+  </si>
+  <si>
+    <t>gerinnungshemmende</t>
+  </si>
+  <si>
+    <t>Ticagrelor</t>
+  </si>
+  <si>
+    <t>ne</t>
+  </si>
+  <si>
+    <t>Risiko</t>
+  </si>
+  <si>
+    <t>wiederholter</t>
+  </si>
+  <si>
+    <t>Herzinfarkte</t>
+  </si>
+  <si>
+    <t>Personen</t>
+  </si>
+  <si>
+    <t>mit</t>
+  </si>
+  <si>
+    <t>einer</t>
+  </si>
+  <si>
+    <t>Herzerkrankung</t>
+  </si>
+  <si>
+    <t># text = Das Medikament wird bereits 12 Monate lang nach einem Herzinfarkt verabreicht, wodurch das Risiko eines Schlaganfalls oder eines weiteren Herzinfarkts reduziert wird.</t>
+  </si>
+  <si>
+    <t>wird</t>
+  </si>
+  <si>
+    <t>bereits</t>
+  </si>
+  <si>
+    <t>Monate</t>
+  </si>
+  <si>
+    <t>indef-np.quant</t>
+  </si>
+  <si>
+    <t>lang</t>
+  </si>
+  <si>
+    <t>nach</t>
+  </si>
+  <si>
+    <t>Herzinfarkt</t>
+  </si>
+  <si>
+    <t>verabreicht</t>
+  </si>
+  <si>
+    <t>wodurch</t>
+  </si>
+  <si>
+    <t>SBJ_2</t>
+  </si>
+  <si>
+    <t>eines</t>
+  </si>
+  <si>
+    <t>Schlaganfalls</t>
+  </si>
+  <si>
+    <t>oder</t>
+  </si>
+  <si>
+    <t>weiteren</t>
+  </si>
+  <si>
+    <t>Herzinfarkts</t>
+  </si>
+  <si>
+    <t># text = Die Regulierungsbehörde NICE des NHS hat eine vier Jahre lange Einnahme empfohlen, um das Risiko kardiovaskulärer Probleme weiter zu reduzieren.</t>
+  </si>
+  <si>
+    <t>Die</t>
+  </si>
+  <si>
+    <t>Regulierungsbehörde</t>
+  </si>
+  <si>
+    <t>NICE</t>
+  </si>
+  <si>
+    <t>des</t>
+  </si>
+  <si>
+    <t>NHS</t>
+  </si>
+  <si>
+    <t>hat</t>
+  </si>
+  <si>
+    <t>eine</t>
+  </si>
+  <si>
+    <t>vier</t>
+  </si>
+  <si>
+    <t>Jahre</t>
+  </si>
+  <si>
+    <t>lange</t>
+  </si>
+  <si>
+    <t>Einnahme</t>
+  </si>
+  <si>
+    <t>um</t>
   </si>
   <si>
     <t>OBJ_2</t>
-  </si>
-  <si>
-    <t>def-np.dem</t>
-  </si>
-  <si>
-    <t>für</t>
-  </si>
-  <si>
-    <t>einen</t>
-  </si>
-  <si>
-    <t>längeren</t>
-  </si>
-  <si>
-    <t>Zeitraum</t>
-  </si>
-  <si>
-    <t>zu</t>
-  </si>
-  <si>
-    <t>.</t>
-  </si>
-  <si>
-    <t># text = Das gerinnungshemmende Medikament Ticagrelor reduziert das Risiko wiederholter Herzinfarkte für Personen mit einer Herzerkrankung.</t>
-  </si>
-  <si>
-    <t>gerinnungshemmende</t>
-  </si>
-  <si>
-    <t>Ticagrelor</t>
-  </si>
-  <si>
-    <t>ne</t>
-  </si>
-  <si>
-    <t>Risiko</t>
-  </si>
-  <si>
-    <t>OBJ</t>
-  </si>
-  <si>
-    <t>wiederholter</t>
-  </si>
-  <si>
-    <t>Herzinfarkte</t>
-  </si>
-  <si>
-    <t>Personen</t>
-  </si>
-  <si>
-    <t>mit</t>
-  </si>
-  <si>
-    <t>einer</t>
-  </si>
-  <si>
-    <t>Herzerkrankung</t>
-  </si>
-  <si>
-    <t># text = Das Medikament wird bereits 12 Monate lang nach einem Herzinfarkt verabreicht, wodurch das Risiko eines Schlaganfalls oder eines weiteren Herzinfarkts reduziert wird.</t>
-  </si>
-  <si>
-    <t>wird</t>
-  </si>
-  <si>
-    <t>bereits</t>
-  </si>
-  <si>
-    <t>Monate</t>
-  </si>
-  <si>
-    <t>indef-np.quant</t>
-  </si>
-  <si>
-    <t>lang</t>
-  </si>
-  <si>
-    <t>nach</t>
-  </si>
-  <si>
-    <t>Herzinfarkt</t>
-  </si>
-  <si>
-    <t>verabreicht</t>
-  </si>
-  <si>
-    <t>wodurch</t>
-  </si>
-  <si>
-    <t>SBJ_2</t>
-  </si>
-  <si>
-    <t>eines</t>
-  </si>
-  <si>
-    <t>Schlaganfalls</t>
-  </si>
-  <si>
-    <t>oder</t>
-  </si>
-  <si>
-    <t>weiteren</t>
-  </si>
-  <si>
-    <t>Herzinfarkts</t>
-  </si>
-  <si>
-    <t>other_4</t>
-  </si>
-  <si>
-    <t># text = Die Regulierungsbehörde NICE des NHS hat eine vier Jahre lange Einnahme empfohlen, um das Risiko kardiovaskulärer Probleme weiter zu reduzieren.</t>
-  </si>
-  <si>
-    <t>Die</t>
-  </si>
-  <si>
-    <t>Regulierungsbehörde</t>
-  </si>
-  <si>
-    <t>NICE</t>
-  </si>
-  <si>
-    <t>des</t>
-  </si>
-  <si>
-    <t>NHS</t>
-  </si>
-  <si>
-    <t>hat</t>
-  </si>
-  <si>
-    <t>eine</t>
-  </si>
-  <si>
-    <t>vier</t>
-  </si>
-  <si>
-    <t>Jahre</t>
-  </si>
-  <si>
-    <t>lange</t>
-  </si>
-  <si>
-    <t>Einnahme</t>
-  </si>
-  <si>
-    <t>um</t>
   </si>
   <si>
     <t>kardiovaskulärer</t>
@@ -1480,7 +1489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="60" customHeight="1"/>
   <cols>
     <col min="2" max="3" width="0" hidden="1" customWidth="1"/>
@@ -1563,16 +1572,16 @@
         <v>17</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="9">
         <f>IF(A3=1,"_",IF(C3="_","???",C3))</f>
@@ -1588,22 +1597,22 @@
     </row>
     <row r="4" spans="1:10" ht="60" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" s="9">
         <f>IF(A4=1,"_",IF(C4="_","???",C4))</f>
@@ -1619,22 +1628,22 @@
     </row>
     <row r="5" spans="1:10" ht="60" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" s="9">
         <f>IF(A5=1,"_",IF(C5="_","???",C5))</f>
@@ -1650,22 +1659,22 @@
     </row>
     <row r="6" spans="1:10" ht="60" customHeight="1">
       <c r="A6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G6" s="9">
         <f>IF(A6=1,"_",IF(C6="_","???",C6))</f>
@@ -1681,22 +1690,22 @@
     </row>
     <row r="7" spans="1:10" ht="60" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>34</v>
-      </c>
       <c r="F7" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" s="9">
         <f>IF(A7=1,"_",IF(C7="_","???",C7))</f>
@@ -1712,13 +1721,13 @@
     </row>
     <row r="8" spans="1:10" ht="60" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>38</v>
@@ -1746,19 +1755,19 @@
         <v>41</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D9" s="7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G9" s="9">
         <f>IF(A9=1,"_",IF(C9="_","???",C9))</f>
@@ -1774,16 +1783,16 @@
     </row>
     <row r="10" spans="1:10" ht="60" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>47</v>
@@ -1805,13 +1814,13 @@
     </row>
     <row r="11" spans="1:10" ht="60" customHeight="1">
       <c r="A11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>12</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>49</v>
@@ -1836,22 +1845,22 @@
     </row>
     <row r="12" spans="1:10" ht="60" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="F12" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="G12" s="9">
         <f>IF(A12=1,"_",IF(C12="_","???",C12))</f>
@@ -1867,22 +1876,22 @@
     </row>
     <row r="13" spans="1:10" ht="60" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G13" s="9">
         <f>IF(A13=1,"_",IF(C13="_","???",C13))</f>
@@ -1898,16 +1907,16 @@
     </row>
     <row r="14" spans="1:10" ht="60" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>60</v>
@@ -1932,19 +1941,19 @@
         <v>62</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="F15" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="G15" s="9">
         <f>IF(A15=1,"_",IF(C15="_","???",C15))</f>
@@ -1960,10 +1969,10 @@
     </row>
     <row r="16" spans="1:10" ht="60" customHeight="1">
       <c r="A16" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>12</v>
@@ -1991,13 +2000,13 @@
     </row>
     <row r="17" spans="1:10" ht="60" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>71</v>
@@ -2025,10 +2034,10 @@
         <v>74</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>75</v>
@@ -2056,7 +2065,7 @@
         <v>78</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>12</v>
@@ -2081,6 +2090,37 @@
         <v>12</v>
       </c>
       <c r="J19" s="12"/>
+    </row>
+    <row r="20" spans="1:10" ht="60" customHeight="1">
+      <c r="A20" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="9">
+        <f>IF(A20=1,"_",IF(C20="_","???",C20))</f>
+        <v/>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="12"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
@@ -2090,7 +2130,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L486"/>
+  <dimension ref="A1:L488"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2102,37 +2142,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L1" s="19" t="s">
         <v>9</v>
@@ -2140,12 +2180,12 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="20" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E3" s="21">
         <f>IF(D3="?OLD","!!!","")</f>
@@ -2179,16 +2219,16 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="20" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E4" s="21">
         <f>IF(D4="?OLD","!!!","")</f>
@@ -2222,7 +2262,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E5" s="21">
         <f>IF(D5="?OLD","!!!","")</f>
@@ -2256,7 +2296,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="20" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E6" s="21">
         <f>IF(D6="?OLD","!!!","")</f>
@@ -2324,13 +2364,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="20" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E8" s="21">
         <f>IF(D8="?OLD","!!!","")</f>
@@ -2364,7 +2404,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="20" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E9" s="21">
         <f>IF(D9="?OLD","!!!","")</f>
@@ -2398,7 +2438,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="20" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E10" s="21">
         <f>IF(D10="?OLD","!!!","")</f>
@@ -2432,16 +2472,16 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="20" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E11" s="21">
         <f>IF(D11="?OLD","!!!","")</f>
@@ -2475,7 +2515,7 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="20" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="E12" s="21">
         <f>IF(D12="?OLD","!!!","")</f>
@@ -2509,7 +2549,7 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E13" s="21">
         <f>IF(D13="?OLD","!!!","")</f>
@@ -2542,88 +2582,22 @@
       <c r="L13" s="26"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" s="21">
-        <f>IF(D14="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F14" s="22" t="str">
-        <f>IF(OR(E14="",E14="!!!"),"",IF(NOT(ISNA(VLOOKUP(E14,E$1:E13,1,FALSE()))),"OLD",IF(AND(E14&lt;&gt;"",E14&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G14" s="23" t="str">
-        <f>IF(OR(E14="",E14="!!!"),"",IF(OR(J14=0,AND(J14=1,K14=1),AND(J14=1,I14="SBJ"),AND(J14=1,I14=0)),"?IN_FOCUS",IF(J14&lt;=2,"?ACTIVATED",IF(J14&lt;&gt;"","?FAMILIAR",IF(F14="NEW",IF(ISNA(VLOOKUP(E14,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H14" s="24" t="str">
-        <f>IF(J14&lt;&gt;1,"",IF(I14="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I14" s="25" t="str">
-        <f>IF(OR(E14="",E14="!!!",F14="NEW"),"",INDEX(B13:B$2,-1+SUMPRODUCT(MAX(ROW(E13:E$2)*(E14=E13:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J14" s="25" t="str">
-        <f>IF(OR(E14="",E14="!!!",F14="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E14)*(E14=E$2:E14)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E13)*(E2=E$1:E13))))))</f>
-        <v> </v>
-      </c>
-      <c r="K14" s="25" t="str">
-        <f>IF(OR(E14="",E14="!!!",F14="NEW"),"",INDEX(J$1:J13,SUMPRODUCT(MAX(ROW(E$1:E13)*(E14=E$1:E13)))))</f>
-        <v> </v>
-      </c>
-      <c r="L14" s="26"/>
+      <c r="A14" s="20"/>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="E15" s="21">
-        <f>IF(D15="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F15" s="22" t="str">
-        <f>IF(OR(E15="",E15="!!!"),"",IF(NOT(ISNA(VLOOKUP(E15,E$1:E14,1,FALSE()))),"OLD",IF(AND(E15&lt;&gt;"",E15&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G15" s="23" t="str">
-        <f>IF(OR(E15="",E15="!!!"),"",IF(OR(J15=0,AND(J15=1,K15=1),AND(J15=1,I15="SBJ"),AND(J15=1,I15=0)),"?IN_FOCUS",IF(J15&lt;=2,"?ACTIVATED",IF(J15&lt;&gt;"","?FAMILIAR",IF(F15="NEW",IF(ISNA(VLOOKUP(E15,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H15" s="24" t="str">
-        <f>IF(J15&lt;&gt;1,"",IF(I15="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I15" s="25" t="str">
-        <f>IF(OR(E15="",E15="!!!",F15="NEW"),"",INDEX(B14:B$2,-1+SUMPRODUCT(MAX(ROW(E14:E$2)*(E15=E14:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J15" s="25" t="str">
-        <f>IF(OR(E15="",E15="!!!",F15="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E15)*(E15=E$2:E15)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E14)*(E2=E$1:E14))))))</f>
-        <v> </v>
-      </c>
-      <c r="K15" s="25" t="str">
-        <f>IF(OR(E15="",E15="!!!",F15="NEW"),"",INDEX(J$1:J14,SUMPRODUCT(MAX(ROW(E$1:E14)*(E15=E$1:E14)))))</f>
-        <v> </v>
-      </c>
-      <c r="L15" s="26"/>
+        <v>112</v>
+      </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E16" s="21">
         <f>IF(D16="?OLD","!!!","")</f>
@@ -2691,7 +2665,13 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="20" t="s">
-        <v>111</v>
+        <v>115</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>106</v>
       </c>
       <c r="E18" s="21">
         <f>IF(D18="?OLD","!!!","")</f>
@@ -2725,7 +2705,7 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E19" s="21">
         <f>IF(D19="?OLD","!!!","")</f>
@@ -2759,13 +2739,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E20" s="21">
         <f>IF(D20="?OLD","!!!","")</f>
@@ -2799,7 +2773,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="20" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="E21" s="21">
         <f>IF(D21="?OLD","!!!","")</f>
@@ -2833,7 +2807,13 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E22" s="21">
         <f>IF(D22="?OLD","!!!","")</f>
@@ -2867,7 +2847,7 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="20" t="s">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="E23" s="21">
         <f>IF(D23="?OLD","!!!","")</f>
@@ -2901,12 +2881,6 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C24" s="27" t="s">
         <v>103</v>
       </c>
       <c r="E24" s="21">
@@ -2941,7 +2915,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E25" s="21">
         <f>IF(D25="?OLD","!!!","")</f>
@@ -2977,6 +2951,12 @@
       <c r="A26" s="20" t="s">
         <v>104</v>
       </c>
+      <c r="B26" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>106</v>
+      </c>
       <c r="E26" s="21">
         <f>IF(D26="?OLD","!!!","")</f>
         <v/>
@@ -3009,7 +2989,7 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="20" t="s">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="E27" s="21">
         <f>IF(D27="?OLD","!!!","")</f>
@@ -3043,7 +3023,7 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="20" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E28" s="21">
         <f>IF(D28="?OLD","!!!","")</f>
@@ -3077,7 +3057,7 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E29" s="21">
         <f>IF(D29="?OLD","!!!","")</f>
@@ -3111,16 +3091,7 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="B30" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C30" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D30" s="27" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E30" s="21">
         <f>IF(D30="?OLD","!!!","")</f>
@@ -3190,6 +3161,15 @@
       <c r="A32" s="20" t="s">
         <v>122</v>
       </c>
+      <c r="B32" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>101</v>
+      </c>
       <c r="E32" s="21">
         <f>IF(D32="?OLD","!!!","")</f>
         <v/>
@@ -3222,7 +3202,7 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="20" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="E33" s="21">
         <f>IF(D33="?OLD","!!!","")</f>
@@ -3256,16 +3236,7 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="B34" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C34" s="27" t="s">
         <v>124</v>
-      </c>
-      <c r="D34" s="27" t="s">
-        <v>98</v>
       </c>
       <c r="E34" s="21">
         <f>IF(D34="?OLD","!!!","")</f>
@@ -3299,7 +3270,7 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="20" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="E35" s="21">
         <f>IF(D35="?OLD","!!!","")</f>
@@ -3333,16 +3304,16 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B36" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="B36" s="27" t="s">
+      <c r="C36" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="27" t="s">
-        <v>128</v>
-      </c>
       <c r="D36" s="27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E36" s="21">
         <f>IF(D36="?OLD","!!!","")</f>
@@ -3376,7 +3347,7 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E37" s="21">
         <f>IF(D37="?OLD","!!!","")</f>
@@ -3410,7 +3381,16 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B38" s="27" t="s">
         <v>130</v>
+      </c>
+      <c r="C38" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="D38" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E38" s="21">
         <f>IF(D38="?OLD","!!!","")</f>
@@ -3444,7 +3424,7 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E39" s="21">
         <f>IF(D39="?OLD","!!!","")</f>
@@ -3478,13 +3458,7 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="B40" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C40" s="27" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="E40" s="21">
         <f>IF(D40="?OLD","!!!","")</f>
@@ -3518,7 +3492,7 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E41" s="21">
         <f>IF(D41="?OLD","!!!","")</f>
@@ -3552,7 +3526,13 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="20" t="s">
-        <v>23</v>
+        <v>135</v>
+      </c>
+      <c r="B42" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E42" s="21">
         <f>IF(D42="?OLD","!!!","")</f>
@@ -3586,7 +3566,7 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="20" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E43" s="21">
         <f>IF(D43="?OLD","!!!","")</f>
@@ -3619,93 +3599,84 @@
       <c r="L43" s="26"/>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="20"/>
+      <c r="A44" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="21">
+        <f>IF(D44="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F44" s="22" t="str">
+        <f>IF(OR(E44="",E44="!!!"),"",IF(NOT(ISNA(VLOOKUP(E44,E$1:E43,1,FALSE()))),"OLD",IF(AND(E44&lt;&gt;"",E44&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G44" s="23" t="str">
+        <f>IF(OR(E44="",E44="!!!"),"",IF(OR(J44=0,AND(J44=1,K44=1),AND(J44=1,I44="SBJ"),AND(J44=1,I44=0)),"?IN_FOCUS",IF(J44&lt;=2,"?ACTIVATED",IF(J44&lt;&gt;"","?FAMILIAR",IF(F44="NEW",IF(ISNA(VLOOKUP(E44,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H44" s="24" t="str">
+        <f>IF(J44&lt;&gt;1,"",IF(I44="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I44" s="25" t="str">
+        <f>IF(OR(E44="",E44="!!!",F44="NEW"),"",INDEX(B43:B$2,-1+SUMPRODUCT(MAX(ROW(E43:E$2)*(E44=E43:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J44" s="25" t="str">
+        <f>IF(OR(E44="",E44="!!!",F44="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E44)*(E44=E$2:E44)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E43)*(E2=E$1:E43))))))</f>
+        <v> </v>
+      </c>
+      <c r="K44" s="25" t="str">
+        <f>IF(OR(E44="",E44="!!!",F44="NEW"),"",INDEX(J$1:J43,SUMPRODUCT(MAX(ROW(E$1:E43)*(E44=E$1:E43)))))</f>
+        <v> </v>
+      </c>
+      <c r="L44" s="26"/>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" s="20" t="s">
-        <v>135</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E45" s="21">
+        <f>IF(D45="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F45" s="22" t="str">
+        <f>IF(OR(E45="",E45="!!!"),"",IF(NOT(ISNA(VLOOKUP(E45,E$1:E44,1,FALSE()))),"OLD",IF(AND(E45&lt;&gt;"",E45&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G45" s="23" t="str">
+        <f>IF(OR(E45="",E45="!!!"),"",IF(OR(J45=0,AND(J45=1,K45=1),AND(J45=1,I45="SBJ"),AND(J45=1,I45=0)),"?IN_FOCUS",IF(J45&lt;=2,"?ACTIVATED",IF(J45&lt;&gt;"","?FAMILIAR",IF(F45="NEW",IF(ISNA(VLOOKUP(E45,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H45" s="24" t="str">
+        <f>IF(J45&lt;&gt;1,"",IF(I45="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I45" s="25" t="str">
+        <f>IF(OR(E45="",E45="!!!",F45="NEW"),"",INDEX(B44:B$2,-1+SUMPRODUCT(MAX(ROW(E44:E$2)*(E45=E44:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J45" s="25" t="str">
+        <f>IF(OR(E45="",E45="!!!",F45="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E45)*(E45=E$2:E45)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E44)*(E2=E$1:E44))))))</f>
+        <v> </v>
+      </c>
+      <c r="K45" s="25" t="str">
+        <f>IF(OR(E45="",E45="!!!",F45="NEW"),"",INDEX(J$1:J44,SUMPRODUCT(MAX(ROW(E$1:E44)*(E45=E$1:E44)))))</f>
+        <v> </v>
+      </c>
+      <c r="L45" s="26"/>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="E46" s="21">
-        <f>IF(D46="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F46" s="22" t="str">
-        <f>IF(OR(E46="",E46="!!!"),"",IF(NOT(ISNA(VLOOKUP(E46,E$1:E45,1,FALSE()))),"OLD",IF(AND(E46&lt;&gt;"",E46&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G46" s="23" t="str">
-        <f>IF(OR(E46="",E46="!!!"),"",IF(OR(J46=0,AND(J46=1,K46=1),AND(J46=1,I46="SBJ"),AND(J46=1,I46=0)),"?IN_FOCUS",IF(J46&lt;=2,"?ACTIVATED",IF(J46&lt;&gt;"","?FAMILIAR",IF(F46="NEW",IF(ISNA(VLOOKUP(E46,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H46" s="24" t="str">
-        <f>IF(J46&lt;&gt;1,"",IF(I46="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I46" s="25" t="str">
-        <f>IF(OR(E46="",E46="!!!",F46="NEW"),"",INDEX(B45:B$2,-1+SUMPRODUCT(MAX(ROW(E45:E$2)*(E46=E45:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J46" s="25" t="str">
-        <f>IF(OR(E46="",E46="!!!",F46="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E46)*(E46=E$2:E46)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E45)*(E2=E$1:E45))))))</f>
-        <v> </v>
-      </c>
-      <c r="K46" s="25" t="str">
-        <f>IF(OR(E46="",E46="!!!",F46="NEW"),"",INDEX(J$1:J45,SUMPRODUCT(MAX(ROW(E$1:E45)*(E46=E$1:E45)))))</f>
-        <v> </v>
-      </c>
-      <c r="L46" s="26"/>
+      <c r="A46" s="20"/>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="E47" s="21">
-        <f>IF(D47="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F47" s="22" t="str">
-        <f>IF(OR(E47="",E47="!!!"),"",IF(NOT(ISNA(VLOOKUP(E47,E$1:E46,1,FALSE()))),"OLD",IF(AND(E47&lt;&gt;"",E47&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G47" s="23" t="str">
-        <f>IF(OR(E47="",E47="!!!"),"",IF(OR(J47=0,AND(J47=1,K47=1),AND(J47=1,I47="SBJ"),AND(J47=1,I47=0)),"?IN_FOCUS",IF(J47&lt;=2,"?ACTIVATED",IF(J47&lt;&gt;"","?FAMILIAR",IF(F47="NEW",IF(ISNA(VLOOKUP(E47,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H47" s="24" t="str">
-        <f>IF(J47&lt;&gt;1,"",IF(I47="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I47" s="25" t="str">
-        <f>IF(OR(E47="",E47="!!!",F47="NEW"),"",INDEX(B46:B$2,-1+SUMPRODUCT(MAX(ROW(E46:E$2)*(E47=E46:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J47" s="25" t="str">
-        <f>IF(OR(E47="",E47="!!!",F47="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E47)*(E47=E$2:E47)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E46)*(E2=E$1:E46))))))</f>
-        <v> </v>
-      </c>
-      <c r="K47" s="25" t="str">
-        <f>IF(OR(E47="",E47="!!!",F47="NEW"),"",INDEX(J$1:J46,SUMPRODUCT(MAX(ROW(E$1:E46)*(E47=E$1:E46)))))</f>
-        <v> </v>
-      </c>
-      <c r="L47" s="26"/>
+        <v>139</v>
+      </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="B48" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C48" s="27" t="s">
         <v>97</v>
-      </c>
-      <c r="D48" s="27" t="s">
-        <v>98</v>
       </c>
       <c r="E48" s="21">
         <f>IF(D48="?OLD","!!!","")</f>
@@ -3739,16 +3710,7 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="B49" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C49" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="D49" s="27" t="s">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="E49" s="21">
         <f>IF(D49="?OLD","!!!","")</f>
@@ -3782,7 +3744,16 @@
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="20" t="s">
-        <v>53</v>
+        <v>104</v>
+      </c>
+      <c r="B50" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E50" s="21">
         <f>IF(D50="?OLD","!!!","")</f>
@@ -3816,7 +3787,16 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="B51" s="27" t="s">
         <v>105</v>
+      </c>
+      <c r="C51" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D51" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E51" s="21">
         <f>IF(D51="?OLD","!!!","")</f>
@@ -3850,16 +3830,7 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="B52" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="C52" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D52" s="27" t="s">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="E52" s="21">
         <f>IF(D52="?OLD","!!!","")</f>
@@ -3893,7 +3864,7 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" s="20" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="E53" s="21">
         <f>IF(D53="?OLD","!!!","")</f>
@@ -3927,13 +3898,16 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="20" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B54" s="27" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="C54" s="27" t="s">
-        <v>103</v>
+        <v>100</v>
+      </c>
+      <c r="D54" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E54" s="21">
         <f>IF(D54="?OLD","!!!","")</f>
@@ -3967,7 +3941,7 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="20" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="E55" s="21">
         <f>IF(D55="?OLD","!!!","")</f>
@@ -4001,13 +3975,13 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="20" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C56" s="27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E56" s="21">
         <f>IF(D56="?OLD","!!!","")</f>
@@ -4041,7 +4015,7 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="20" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="E57" s="21">
         <f>IF(D57="?OLD","!!!","")</f>
@@ -4075,7 +4049,13 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="20" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="B58" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C58" s="27" t="s">
+        <v>106</v>
       </c>
       <c r="E58" s="21">
         <f>IF(D58="?OLD","!!!","")</f>
@@ -4109,13 +4089,7 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="B59" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="C59" s="27" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="E59" s="21">
         <f>IF(D59="?OLD","!!!","")</f>
@@ -4149,7 +4123,7 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="20" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="E60" s="21">
         <f>IF(D60="?OLD","!!!","")</f>
@@ -4182,93 +4156,90 @@
       <c r="L60" s="26"/>
     </row>
     <row r="61" spans="1:12">
-      <c r="A61" s="20"/>
+      <c r="A61" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B61" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C61" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="E61" s="21">
+        <f>IF(D61="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F61" s="22" t="str">
+        <f>IF(OR(E61="",E61="!!!"),"",IF(NOT(ISNA(VLOOKUP(E61,E$1:E60,1,FALSE()))),"OLD",IF(AND(E61&lt;&gt;"",E61&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G61" s="23" t="str">
+        <f>IF(OR(E61="",E61="!!!"),"",IF(OR(J61=0,AND(J61=1,K61=1),AND(J61=1,I61="SBJ"),AND(J61=1,I61=0)),"?IN_FOCUS",IF(J61&lt;=2,"?ACTIVATED",IF(J61&lt;&gt;"","?FAMILIAR",IF(F61="NEW",IF(ISNA(VLOOKUP(E61,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H61" s="24" t="str">
+        <f>IF(J61&lt;&gt;1,"",IF(I61="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I61" s="25" t="str">
+        <f>IF(OR(E61="",E61="!!!",F61="NEW"),"",INDEX(B60:B$2,-1+SUMPRODUCT(MAX(ROW(E60:E$2)*(E61=E60:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J61" s="25" t="str">
+        <f>IF(OR(E61="",E61="!!!",F61="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E61)*(E61=E$2:E61)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E60)*(E2=E$1:E60))))))</f>
+        <v> </v>
+      </c>
+      <c r="K61" s="25" t="str">
+        <f>IF(OR(E61="",E61="!!!",F61="NEW"),"",INDEX(J$1:J60,SUMPRODUCT(MAX(ROW(E$1:E60)*(E61=E$1:E60)))))</f>
+        <v> </v>
+      </c>
+      <c r="L61" s="26"/>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="20" t="s">
-        <v>147</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E62" s="21">
+        <f>IF(D62="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F62" s="22" t="str">
+        <f>IF(OR(E62="",E62="!!!"),"",IF(NOT(ISNA(VLOOKUP(E62,E$1:E61,1,FALSE()))),"OLD",IF(AND(E62&lt;&gt;"",E62&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G62" s="23" t="str">
+        <f>IF(OR(E62="",E62="!!!"),"",IF(OR(J62=0,AND(J62=1,K62=1),AND(J62=1,I62="SBJ"),AND(J62=1,I62=0)),"?IN_FOCUS",IF(J62&lt;=2,"?ACTIVATED",IF(J62&lt;&gt;"","?FAMILIAR",IF(F62="NEW",IF(ISNA(VLOOKUP(E62,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H62" s="24" t="str">
+        <f>IF(J62&lt;&gt;1,"",IF(I62="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I62" s="25" t="str">
+        <f>IF(OR(E62="",E62="!!!",F62="NEW"),"",INDEX(B61:B$2,-1+SUMPRODUCT(MAX(ROW(E61:E$2)*(E62=E61:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J62" s="25" t="str">
+        <f>IF(OR(E62="",E62="!!!",F62="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E62)*(E62=E$2:E62)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E61)*(E2=E$1:E61))))))</f>
+        <v> </v>
+      </c>
+      <c r="K62" s="25" t="str">
+        <f>IF(OR(E62="",E62="!!!",F62="NEW"),"",INDEX(J$1:J61,SUMPRODUCT(MAX(ROW(E$1:E61)*(E62=E$1:E61)))))</f>
+        <v> </v>
+      </c>
+      <c r="L62" s="26"/>
     </row>
     <row r="63" spans="1:12">
-      <c r="A63" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="E63" s="21">
-        <f>IF(D63="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F63" s="22" t="str">
-        <f>IF(OR(E63="",E63="!!!"),"",IF(NOT(ISNA(VLOOKUP(E63,E$1:E62,1,FALSE()))),"OLD",IF(AND(E63&lt;&gt;"",E63&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G63" s="23" t="str">
-        <f>IF(OR(E63="",E63="!!!"),"",IF(OR(J63=0,AND(J63=1,K63=1),AND(J63=1,I63="SBJ"),AND(J63=1,I63=0)),"?IN_FOCUS",IF(J63&lt;=2,"?ACTIVATED",IF(J63&lt;&gt;"","?FAMILIAR",IF(F63="NEW",IF(ISNA(VLOOKUP(E63,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H63" s="24" t="str">
-        <f>IF(J63&lt;&gt;1,"",IF(I63="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I63" s="25" t="str">
-        <f>IF(OR(E63="",E63="!!!",F63="NEW"),"",INDEX(B62:B$2,-1+SUMPRODUCT(MAX(ROW(E62:E$2)*(E63=E62:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J63" s="25" t="str">
-        <f>IF(OR(E63="",E63="!!!",F63="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E63)*(E63=E$2:E63)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E62)*(E2=E$1:E62))))))</f>
-        <v> </v>
-      </c>
-      <c r="K63" s="25" t="str">
-        <f>IF(OR(E63="",E63="!!!",F63="NEW"),"",INDEX(J$1:J62,SUMPRODUCT(MAX(ROW(E$1:E62)*(E63=E$1:E62)))))</f>
-        <v> </v>
-      </c>
-      <c r="L63" s="26"/>
+      <c r="A63" s="20"/>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="B64" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C64" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D64" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="E64" s="21">
-        <f>IF(D64="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F64" s="22" t="str">
-        <f>IF(OR(E64="",E64="!!!"),"",IF(NOT(ISNA(VLOOKUP(E64,E$1:E63,1,FALSE()))),"OLD",IF(AND(E64&lt;&gt;"",E64&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G64" s="23" t="str">
-        <f>IF(OR(E64="",E64="!!!"),"",IF(OR(J64=0,AND(J64=1,K64=1),AND(J64=1,I64="SBJ"),AND(J64=1,I64=0)),"?IN_FOCUS",IF(J64&lt;=2,"?ACTIVATED",IF(J64&lt;&gt;"","?FAMILIAR",IF(F64="NEW",IF(ISNA(VLOOKUP(E64,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H64" s="24" t="str">
-        <f>IF(J64&lt;&gt;1,"",IF(I64="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I64" s="25" t="str">
-        <f>IF(OR(E64="",E64="!!!",F64="NEW"),"",INDEX(B63:B$2,-1+SUMPRODUCT(MAX(ROW(E63:E$2)*(E64=E63:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J64" s="25" t="str">
-        <f>IF(OR(E64="",E64="!!!",F64="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E64)*(E64=E$2:E64)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E63)*(E2=E$1:E63))))))</f>
-        <v> </v>
-      </c>
-      <c r="K64" s="25" t="str">
-        <f>IF(OR(E64="",E64="!!!",F64="NEW"),"",INDEX(J$1:J63,SUMPRODUCT(MAX(ROW(E$1:E63)*(E64=E$1:E63)))))</f>
-        <v> </v>
-      </c>
-      <c r="L64" s="26"/>
+        <v>150</v>
+      </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" s="20" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="E65" s="21">
         <f>IF(D65="?OLD","!!!","")</f>
@@ -4302,7 +4273,16 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" s="20" t="s">
-        <v>149</v>
+        <v>104</v>
+      </c>
+      <c r="B66" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C66" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D66" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E66" s="21">
         <f>IF(D66="?OLD","!!!","")</f>
@@ -4336,7 +4316,7 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" s="20" t="s">
-        <v>27</v>
+        <v>151</v>
       </c>
       <c r="E67" s="21">
         <f>IF(D67="?OLD","!!!","")</f>
@@ -4370,13 +4350,7 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="B68" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C68" s="27" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E68" s="21">
         <f>IF(D68="?OLD","!!!","")</f>
@@ -4410,7 +4384,7 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" s="20" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="E69" s="21">
         <f>IF(D69="?OLD","!!!","")</f>
@@ -4446,6 +4420,12 @@
       <c r="A70" s="20" t="s">
         <v>153</v>
       </c>
+      <c r="B70" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C70" s="27" t="s">
+        <v>154</v>
+      </c>
       <c r="E70" s="21">
         <f>IF(D70="?OLD","!!!","")</f>
         <v/>
@@ -4478,7 +4458,7 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71" s="20" t="s">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="E71" s="21">
         <f>IF(D71="?OLD","!!!","")</f>
@@ -4512,13 +4492,7 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="B72" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="C72" s="27" t="s">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="E72" s="21">
         <f>IF(D72="?OLD","!!!","")</f>
@@ -4552,7 +4526,7 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73" s="20" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="E73" s="21">
         <f>IF(D73="?OLD","!!!","")</f>
@@ -4586,7 +4560,13 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" s="20" t="s">
-        <v>104</v>
+        <v>157</v>
+      </c>
+      <c r="B74" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C74" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E74" s="21">
         <f>IF(D74="?OLD","!!!","")</f>
@@ -4620,7 +4600,7 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" s="20" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E75" s="21">
         <f>IF(D75="?OLD","!!!","")</f>
@@ -4654,7 +4634,7 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" s="20" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E76" s="21">
         <f>IF(D76="?OLD","!!!","")</f>
@@ -4688,16 +4668,7 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="B77" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="C77" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D77" s="27" t="s">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="E77" s="21">
         <f>IF(D77="?OLD","!!!","")</f>
@@ -4731,7 +4702,7 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" s="20" t="s">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="E78" s="21">
         <f>IF(D78="?OLD","!!!","")</f>
@@ -4765,13 +4736,16 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" s="20" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="B79" s="27" t="s">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="C79" s="27" t="s">
-        <v>117</v>
+        <v>100</v>
+      </c>
+      <c r="D79" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E79" s="21">
         <f>IF(D79="?OLD","!!!","")</f>
@@ -4805,7 +4779,7 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" s="20" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E80" s="21">
         <f>IF(D80="?OLD","!!!","")</f>
@@ -4839,7 +4813,13 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" s="20" t="s">
-        <v>158</v>
+        <v>162</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C81" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E81" s="21">
         <f>IF(D81="?OLD","!!!","")</f>
@@ -4873,7 +4853,7 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82" s="20" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E82" s="21">
         <f>IF(D82="?OLD","!!!","")</f>
@@ -4907,13 +4887,7 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="B83" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="C83" s="27" t="s">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="E83" s="21">
         <f>IF(D83="?OLD","!!!","")</f>
@@ -4947,7 +4921,7 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84" s="20" t="s">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="E84" s="21">
         <f>IF(D84="?OLD","!!!","")</f>
@@ -4981,7 +4955,13 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85" s="20" t="s">
-        <v>148</v>
+        <v>165</v>
+      </c>
+      <c r="B85" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C85" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E85" s="21">
         <f>IF(D85="?OLD","!!!","")</f>
@@ -5015,7 +4995,7 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86" s="20" t="s">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="E86" s="21">
         <f>IF(D86="?OLD","!!!","")</f>
@@ -5048,103 +5028,85 @@
       <c r="L86" s="26"/>
     </row>
     <row r="87" spans="1:12">
-      <c r="A87" s="20"/>
+      <c r="A87" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="E87" s="21">
+        <f>IF(D87="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F87" s="22" t="str">
+        <f>IF(OR(E87="",E87="!!!"),"",IF(NOT(ISNA(VLOOKUP(E87,E$1:E86,1,FALSE()))),"OLD",IF(AND(E87&lt;&gt;"",E87&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G87" s="23" t="str">
+        <f>IF(OR(E87="",E87="!!!"),"",IF(OR(J87=0,AND(J87=1,K87=1),AND(J87=1,I87="SBJ"),AND(J87=1,I87=0)),"?IN_FOCUS",IF(J87&lt;=2,"?ACTIVATED",IF(J87&lt;&gt;"","?FAMILIAR",IF(F87="NEW",IF(ISNA(VLOOKUP(E87,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H87" s="24" t="str">
+        <f>IF(J87&lt;&gt;1,"",IF(I87="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I87" s="25" t="str">
+        <f>IF(OR(E87="",E87="!!!",F87="NEW"),"",INDEX(B86:B$2,-1+SUMPRODUCT(MAX(ROW(E86:E$2)*(E87=E86:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J87" s="25" t="str">
+        <f>IF(OR(E87="",E87="!!!",F87="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E87)*(E87=E$2:E87)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E86)*(E2=E$1:E86))))))</f>
+        <v> </v>
+      </c>
+      <c r="K87" s="25" t="str">
+        <f>IF(OR(E87="",E87="!!!",F87="NEW"),"",INDEX(J$1:J86,SUMPRODUCT(MAX(ROW(E$1:E86)*(E87=E$1:E86)))))</f>
+        <v> </v>
+      </c>
+      <c r="L87" s="26"/>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" s="20" t="s">
-        <v>164</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E88" s="21">
+        <f>IF(D88="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F88" s="22" t="str">
+        <f>IF(OR(E88="",E88="!!!"),"",IF(NOT(ISNA(VLOOKUP(E88,E$1:E87,1,FALSE()))),"OLD",IF(AND(E88&lt;&gt;"",E88&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G88" s="23" t="str">
+        <f>IF(OR(E88="",E88="!!!"),"",IF(OR(J88=0,AND(J88=1,K88=1),AND(J88=1,I88="SBJ"),AND(J88=1,I88=0)),"?IN_FOCUS",IF(J88&lt;=2,"?ACTIVATED",IF(J88&lt;&gt;"","?FAMILIAR",IF(F88="NEW",IF(ISNA(VLOOKUP(E88,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H88" s="24" t="str">
+        <f>IF(J88&lt;&gt;1,"",IF(I88="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I88" s="25" t="str">
+        <f>IF(OR(E88="",E88="!!!",F88="NEW"),"",INDEX(B87:B$2,-1+SUMPRODUCT(MAX(ROW(E87:E$2)*(E88=E87:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J88" s="25" t="str">
+        <f>IF(OR(E88="",E88="!!!",F88="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E88)*(E88=E$2:E88)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E87)*(E2=E$1:E87))))))</f>
+        <v> </v>
+      </c>
+      <c r="K88" s="25" t="str">
+        <f>IF(OR(E88="",E88="!!!",F88="NEW"),"",INDEX(J$1:J87,SUMPRODUCT(MAX(ROW(E$1:E87)*(E88=E$1:E87)))))</f>
+        <v> </v>
+      </c>
+      <c r="L88" s="26"/>
     </row>
     <row r="89" spans="1:12">
-      <c r="A89" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="E89" s="21">
-        <f>IF(D89="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F89" s="22" t="str">
-        <f>IF(OR(E89="",E89="!!!"),"",IF(NOT(ISNA(VLOOKUP(E89,E$1:E88,1,FALSE()))),"OLD",IF(AND(E89&lt;&gt;"",E89&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G89" s="23" t="str">
-        <f>IF(OR(E89="",E89="!!!"),"",IF(OR(J89=0,AND(J89=1,K89=1),AND(J89=1,I89="SBJ"),AND(J89=1,I89=0)),"?IN_FOCUS",IF(J89&lt;=2,"?ACTIVATED",IF(J89&lt;&gt;"","?FAMILIAR",IF(F89="NEW",IF(ISNA(VLOOKUP(E89,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H89" s="24" t="str">
-        <f>IF(J89&lt;&gt;1,"",IF(I89="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I89" s="25" t="str">
-        <f>IF(OR(E89="",E89="!!!",F89="NEW"),"",INDEX(B88:B$2,-1+SUMPRODUCT(MAX(ROW(E88:E$2)*(E89=E88:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J89" s="25" t="str">
-        <f>IF(OR(E89="",E89="!!!",F89="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E89)*(E89=E$2:E89)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E88)*(E2=E$1:E88))))))</f>
-        <v> </v>
-      </c>
-      <c r="K89" s="25" t="str">
-        <f>IF(OR(E89="",E89="!!!",F89="NEW"),"",INDEX(J$1:J88,SUMPRODUCT(MAX(ROW(E$1:E88)*(E89=E$1:E88)))))</f>
-        <v> </v>
-      </c>
-      <c r="L89" s="26"/>
+      <c r="A89" s="20"/>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="B90" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="C90" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D90" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="E90" s="21">
-        <f>IF(D90="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F90" s="22" t="str">
-        <f>IF(OR(E90="",E90="!!!"),"",IF(NOT(ISNA(VLOOKUP(E90,E$1:E89,1,FALSE()))),"OLD",IF(AND(E90&lt;&gt;"",E90&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G90" s="23" t="str">
-        <f>IF(OR(E90="",E90="!!!"),"",IF(OR(J90=0,AND(J90=1,K90=1),AND(J90=1,I90="SBJ"),AND(J90=1,I90=0)),"?IN_FOCUS",IF(J90&lt;=2,"?ACTIVATED",IF(J90&lt;&gt;"","?FAMILIAR",IF(F90="NEW",IF(ISNA(VLOOKUP(E90,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H90" s="24" t="str">
-        <f>IF(J90&lt;&gt;1,"",IF(I90="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I90" s="25" t="str">
-        <f>IF(OR(E90="",E90="!!!",F90="NEW"),"",INDEX(B89:B$2,-1+SUMPRODUCT(MAX(ROW(E89:E$2)*(E90=E89:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J90" s="25" t="str">
-        <f>IF(OR(E90="",E90="!!!",F90="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E90)*(E90=E$2:E90)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E89)*(E2=E$1:E89))))))</f>
-        <v> </v>
-      </c>
-      <c r="K90" s="25" t="str">
-        <f>IF(OR(E90="",E90="!!!",F90="NEW"),"",INDEX(J$1:J89,SUMPRODUCT(MAX(ROW(E$1:E89)*(E90=E$1:E89)))))</f>
-        <v> </v>
-      </c>
-      <c r="L90" s="26"/>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="B91" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C91" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="D91" s="27" t="s">
-        <v>98</v>
-      </c>
       <c r="E91" s="21">
         <f>IF(D91="?OLD","!!!","")</f>
         <v/>
@@ -5179,6 +5141,15 @@
       <c r="A92" s="20" t="s">
         <v>168</v>
       </c>
+      <c r="B92" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="C92" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D92" s="27" t="s">
+        <v>101</v>
+      </c>
       <c r="E92" s="21">
         <f>IF(D92="?OLD","!!!","")</f>
         <v/>
@@ -5214,13 +5185,13 @@
         <v>169</v>
       </c>
       <c r="B93" s="27" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="C93" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E93" s="21">
         <f>IF(D93="?OLD","!!!","")</f>
@@ -5290,6 +5261,15 @@
       <c r="A95" s="20" t="s">
         <v>171</v>
       </c>
+      <c r="B95" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C95" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D95" s="27" t="s">
+        <v>101</v>
+      </c>
       <c r="E95" s="21">
         <f>IF(D95="?OLD","!!!","")</f>
         <v/>
@@ -5358,12 +5338,6 @@
       <c r="A97" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="B97" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C97" s="27" t="s">
-        <v>151</v>
-      </c>
       <c r="E97" s="21">
         <f>IF(D97="?OLD","!!!","")</f>
         <v/>
@@ -5433,10 +5407,10 @@
         <v>175</v>
       </c>
       <c r="B99" s="27" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C99" s="27" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="E99" s="21">
         <f>IF(D99="?OLD","!!!","")</f>
@@ -5470,7 +5444,7 @@
     </row>
     <row r="100" spans="1:12">
       <c r="A100" s="20" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="E100" s="21">
         <f>IF(D100="?OLD","!!!","")</f>
@@ -5504,7 +5478,13 @@
     </row>
     <row r="101" spans="1:12">
       <c r="A101" s="20" t="s">
-        <v>104</v>
+        <v>177</v>
+      </c>
+      <c r="B101" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C101" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E101" s="21">
         <f>IF(D101="?OLD","!!!","")</f>
@@ -5538,7 +5518,7 @@
     </row>
     <row r="102" spans="1:12">
       <c r="A102" s="20" t="s">
-        <v>176</v>
+        <v>123</v>
       </c>
       <c r="E102" s="21">
         <f>IF(D102="?OLD","!!!","")</f>
@@ -5572,7 +5552,7 @@
     </row>
     <row r="103" spans="1:12">
       <c r="A103" s="20" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E103" s="21">
         <f>IF(D103="?OLD","!!!","")</f>
@@ -5606,16 +5586,7 @@
     </row>
     <row r="104" spans="1:12">
       <c r="A104" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="B104" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="C104" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D104" s="27" t="s">
-        <v>98</v>
+        <v>178</v>
       </c>
       <c r="E104" s="21">
         <f>IF(D104="?OLD","!!!","")</f>
@@ -5649,7 +5620,7 @@
     </row>
     <row r="105" spans="1:12">
       <c r="A105" s="20" t="s">
-        <v>177</v>
+        <v>108</v>
       </c>
       <c r="E105" s="21">
         <f>IF(D105="?OLD","!!!","")</f>
@@ -5683,13 +5654,16 @@
     </row>
     <row r="106" spans="1:12">
       <c r="A106" s="20" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="B106" s="27" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="C106" s="27" t="s">
-        <v>103</v>
+        <v>100</v>
+      </c>
+      <c r="D106" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E106" s="21">
         <f>IF(D106="?OLD","!!!","")</f>
@@ -5723,7 +5697,7 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" s="20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E107" s="21">
         <f>IF(D107="?OLD","!!!","")</f>
@@ -5757,7 +5731,13 @@
     </row>
     <row r="108" spans="1:12">
       <c r="A108" s="20" t="s">
-        <v>133</v>
+        <v>181</v>
+      </c>
+      <c r="B108" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="C108" s="27" t="s">
+        <v>106</v>
       </c>
       <c r="E108" s="21">
         <f>IF(D108="?OLD","!!!","")</f>
@@ -5791,7 +5771,7 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109" s="20" t="s">
-        <v>18</v>
+        <v>182</v>
       </c>
       <c r="E109" s="21">
         <f>IF(D109="?OLD","!!!","")</f>
@@ -5825,7 +5805,7 @@
     </row>
     <row r="110" spans="1:12">
       <c r="A110" s="20" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E110" s="21">
         <f>IF(D110="?OLD","!!!","")</f>
@@ -5858,103 +5838,85 @@
       <c r="L110" s="26"/>
     </row>
     <row r="111" spans="1:12">
-      <c r="A111" s="20"/>
+      <c r="A111" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E111" s="21">
+        <f>IF(D111="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F111" s="22" t="str">
+        <f>IF(OR(E111="",E111="!!!"),"",IF(NOT(ISNA(VLOOKUP(E111,E$1:E110,1,FALSE()))),"OLD",IF(AND(E111&lt;&gt;"",E111&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G111" s="23" t="str">
+        <f>IF(OR(E111="",E111="!!!"),"",IF(OR(J111=0,AND(J111=1,K111=1),AND(J111=1,I111="SBJ"),AND(J111=1,I111=0)),"?IN_FOCUS",IF(J111&lt;=2,"?ACTIVATED",IF(J111&lt;&gt;"","?FAMILIAR",IF(F111="NEW",IF(ISNA(VLOOKUP(E111,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H111" s="24" t="str">
+        <f>IF(J111&lt;&gt;1,"",IF(I111="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I111" s="25" t="str">
+        <f>IF(OR(E111="",E111="!!!",F111="NEW"),"",INDEX(B110:B$2,-1+SUMPRODUCT(MAX(ROW(E110:E$2)*(E111=E110:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J111" s="25" t="str">
+        <f>IF(OR(E111="",E111="!!!",F111="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E111)*(E111=E$2:E111)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E110)*(E2=E$1:E110))))))</f>
+        <v> </v>
+      </c>
+      <c r="K111" s="25" t="str">
+        <f>IF(OR(E111="",E111="!!!",F111="NEW"),"",INDEX(J$1:J110,SUMPRODUCT(MAX(ROW(E$1:E110)*(E111=E$1:E110)))))</f>
+        <v> </v>
+      </c>
+      <c r="L111" s="26"/>
     </row>
     <row r="112" spans="1:12">
       <c r="A112" s="20" t="s">
-        <v>164</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E112" s="21">
+        <f>IF(D112="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F112" s="22" t="str">
+        <f>IF(OR(E112="",E112="!!!"),"",IF(NOT(ISNA(VLOOKUP(E112,E$1:E111,1,FALSE()))),"OLD",IF(AND(E112&lt;&gt;"",E112&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G112" s="23" t="str">
+        <f>IF(OR(E112="",E112="!!!"),"",IF(OR(J112=0,AND(J112=1,K112=1),AND(J112=1,I112="SBJ"),AND(J112=1,I112=0)),"?IN_FOCUS",IF(J112&lt;=2,"?ACTIVATED",IF(J112&lt;&gt;"","?FAMILIAR",IF(F112="NEW",IF(ISNA(VLOOKUP(E112,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H112" s="24" t="str">
+        <f>IF(J112&lt;&gt;1,"",IF(I112="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I112" s="25" t="str">
+        <f>IF(OR(E112="",E112="!!!",F112="NEW"),"",INDEX(B111:B$2,-1+SUMPRODUCT(MAX(ROW(E111:E$2)*(E112=E111:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J112" s="25" t="str">
+        <f>IF(OR(E112="",E112="!!!",F112="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E112)*(E112=E$2:E112)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E111)*(E2=E$1:E111))))))</f>
+        <v> </v>
+      </c>
+      <c r="K112" s="25" t="str">
+        <f>IF(OR(E112="",E112="!!!",F112="NEW"),"",INDEX(J$1:J111,SUMPRODUCT(MAX(ROW(E$1:E111)*(E112=E$1:E111)))))</f>
+        <v> </v>
+      </c>
+      <c r="L112" s="26"/>
     </row>
     <row r="113" spans="1:12">
-      <c r="A113" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="E113" s="21">
-        <f>IF(D113="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F113" s="22" t="str">
-        <f>IF(OR(E113="",E113="!!!"),"",IF(NOT(ISNA(VLOOKUP(E113,E$1:E112,1,FALSE()))),"OLD",IF(AND(E113&lt;&gt;"",E113&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G113" s="23" t="str">
-        <f>IF(OR(E113="",E113="!!!"),"",IF(OR(J113=0,AND(J113=1,K113=1),AND(J113=1,I113="SBJ"),AND(J113=1,I113=0)),"?IN_FOCUS",IF(J113&lt;=2,"?ACTIVATED",IF(J113&lt;&gt;"","?FAMILIAR",IF(F113="NEW",IF(ISNA(VLOOKUP(E113,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H113" s="24" t="str">
-        <f>IF(J113&lt;&gt;1,"",IF(I113="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I113" s="25" t="str">
-        <f>IF(OR(E113="",E113="!!!",F113="NEW"),"",INDEX(B112:B$2,-1+SUMPRODUCT(MAX(ROW(E112:E$2)*(E113=E112:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J113" s="25" t="str">
-        <f>IF(OR(E113="",E113="!!!",F113="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E113)*(E113=E$2:E113)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E112)*(E2=E$1:E112))))))</f>
-        <v> </v>
-      </c>
-      <c r="K113" s="25" t="str">
-        <f>IF(OR(E113="",E113="!!!",F113="NEW"),"",INDEX(J$1:J112,SUMPRODUCT(MAX(ROW(E$1:E112)*(E113=E$1:E112)))))</f>
-        <v> </v>
-      </c>
-      <c r="L113" s="26"/>
+      <c r="A113" s="20"/>
     </row>
     <row r="114" spans="1:12">
       <c r="A114" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="B114" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="C114" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D114" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="E114" s="21">
-        <f>IF(D114="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F114" s="22" t="str">
-        <f>IF(OR(E114="",E114="!!!"),"",IF(NOT(ISNA(VLOOKUP(E114,E$1:E113,1,FALSE()))),"OLD",IF(AND(E114&lt;&gt;"",E114&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G114" s="23" t="str">
-        <f>IF(OR(E114="",E114="!!!"),"",IF(OR(J114=0,AND(J114=1,K114=1),AND(J114=1,I114="SBJ"),AND(J114=1,I114=0)),"?IN_FOCUS",IF(J114&lt;=2,"?ACTIVATED",IF(J114&lt;&gt;"","?FAMILIAR",IF(F114="NEW",IF(ISNA(VLOOKUP(E114,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H114" s="24" t="str">
-        <f>IF(J114&lt;&gt;1,"",IF(I114="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I114" s="25" t="str">
-        <f>IF(OR(E114="",E114="!!!",F114="NEW"),"",INDEX(B113:B$2,-1+SUMPRODUCT(MAX(ROW(E113:E$2)*(E114=E113:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J114" s="25" t="str">
-        <f>IF(OR(E114="",E114="!!!",F114="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E114)*(E114=E$2:E114)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E113)*(E2=E$1:E113))))))</f>
-        <v> </v>
-      </c>
-      <c r="K114" s="25" t="str">
-        <f>IF(OR(E114="",E114="!!!",F114="NEW"),"",INDEX(J$1:J113,SUMPRODUCT(MAX(ROW(E$1:E113)*(E114=E$1:E113)))))</f>
-        <v> </v>
-      </c>
-      <c r="L114" s="26"/>
     </row>
     <row r="115" spans="1:12">
       <c r="A115" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="B115" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C115" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="D115" s="27" t="s">
-        <v>98</v>
-      </c>
       <c r="E115" s="21">
         <f>IF(D115="?OLD","!!!","")</f>
         <v/>
@@ -5989,6 +5951,15 @@
       <c r="A116" s="20" t="s">
         <v>168</v>
       </c>
+      <c r="B116" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="C116" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D116" s="27" t="s">
+        <v>101</v>
+      </c>
       <c r="E116" s="21">
         <f>IF(D116="?OLD","!!!","")</f>
         <v/>
@@ -6024,13 +5995,13 @@
         <v>169</v>
       </c>
       <c r="B117" s="27" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="C117" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D117" s="27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E117" s="21">
         <f>IF(D117="?OLD","!!!","")</f>
@@ -6100,6 +6071,15 @@
       <c r="A119" s="20" t="s">
         <v>171</v>
       </c>
+      <c r="B119" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C119" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D119" s="27" t="s">
+        <v>101</v>
+      </c>
       <c r="E119" s="21">
         <f>IF(D119="?OLD","!!!","")</f>
         <v/>
@@ -6168,12 +6148,6 @@
       <c r="A121" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="B121" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C121" s="27" t="s">
-        <v>151</v>
-      </c>
       <c r="E121" s="21">
         <f>IF(D121="?OLD","!!!","")</f>
         <v/>
@@ -6243,10 +6217,10 @@
         <v>175</v>
       </c>
       <c r="B123" s="27" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C123" s="27" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="E123" s="21">
         <f>IF(D123="?OLD","!!!","")</f>
@@ -6280,7 +6254,7 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124" s="20" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="E124" s="21">
         <f>IF(D124="?OLD","!!!","")</f>
@@ -6314,7 +6288,13 @@
     </row>
     <row r="125" spans="1:12">
       <c r="A125" s="20" t="s">
-        <v>104</v>
+        <v>177</v>
+      </c>
+      <c r="B125" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C125" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E125" s="21">
         <f>IF(D125="?OLD","!!!","")</f>
@@ -6348,7 +6328,7 @@
     </row>
     <row r="126" spans="1:12">
       <c r="A126" s="20" t="s">
-        <v>176</v>
+        <v>123</v>
       </c>
       <c r="E126" s="21">
         <f>IF(D126="?OLD","!!!","")</f>
@@ -6382,7 +6362,7 @@
     </row>
     <row r="127" spans="1:12">
       <c r="A127" s="20" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E127" s="21">
         <f>IF(D127="?OLD","!!!","")</f>
@@ -6416,16 +6396,7 @@
     </row>
     <row r="128" spans="1:12">
       <c r="A128" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="B128" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="C128" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D128" s="27" t="s">
-        <v>98</v>
+        <v>178</v>
       </c>
       <c r="E128" s="21">
         <f>IF(D128="?OLD","!!!","")</f>
@@ -6459,7 +6430,7 @@
     </row>
     <row r="129" spans="1:12">
       <c r="A129" s="20" t="s">
-        <v>177</v>
+        <v>108</v>
       </c>
       <c r="E129" s="21">
         <f>IF(D129="?OLD","!!!","")</f>
@@ -6493,13 +6464,16 @@
     </row>
     <row r="130" spans="1:12">
       <c r="A130" s="20" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="B130" s="27" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="C130" s="27" t="s">
-        <v>103</v>
+        <v>100</v>
+      </c>
+      <c r="D130" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E130" s="21">
         <f>IF(D130="?OLD","!!!","")</f>
@@ -6533,7 +6507,7 @@
     </row>
     <row r="131" spans="1:12">
       <c r="A131" s="20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E131" s="21">
         <f>IF(D131="?OLD","!!!","")</f>
@@ -6567,7 +6541,13 @@
     </row>
     <row r="132" spans="1:12">
       <c r="A132" s="20" t="s">
-        <v>133</v>
+        <v>181</v>
+      </c>
+      <c r="B132" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="C132" s="27" t="s">
+        <v>106</v>
       </c>
       <c r="E132" s="21">
         <f>IF(D132="?OLD","!!!","")</f>
@@ -6601,7 +6581,7 @@
     </row>
     <row r="133" spans="1:12">
       <c r="A133" s="20" t="s">
-        <v>18</v>
+        <v>182</v>
       </c>
       <c r="E133" s="21">
         <f>IF(D133="?OLD","!!!","")</f>
@@ -6635,7 +6615,7 @@
     </row>
     <row r="134" spans="1:12">
       <c r="A134" s="20" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E134" s="21">
         <f>IF(D134="?OLD","!!!","")</f>
@@ -6668,90 +6648,84 @@
       <c r="L134" s="26"/>
     </row>
     <row r="135" spans="1:12">
-      <c r="A135" s="20"/>
+      <c r="A135" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E135" s="21">
+        <f>IF(D135="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F135" s="22" t="str">
+        <f>IF(OR(E135="",E135="!!!"),"",IF(NOT(ISNA(VLOOKUP(E135,E$1:E134,1,FALSE()))),"OLD",IF(AND(E135&lt;&gt;"",E135&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G135" s="23" t="str">
+        <f>IF(OR(E135="",E135="!!!"),"",IF(OR(J135=0,AND(J135=1,K135=1),AND(J135=1,I135="SBJ"),AND(J135=1,I135=0)),"?IN_FOCUS",IF(J135&lt;=2,"?ACTIVATED",IF(J135&lt;&gt;"","?FAMILIAR",IF(F135="NEW",IF(ISNA(VLOOKUP(E135,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H135" s="24" t="str">
+        <f>IF(J135&lt;&gt;1,"",IF(I135="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I135" s="25" t="str">
+        <f>IF(OR(E135="",E135="!!!",F135="NEW"),"",INDEX(B134:B$2,-1+SUMPRODUCT(MAX(ROW(E134:E$2)*(E135=E134:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J135" s="25" t="str">
+        <f>IF(OR(E135="",E135="!!!",F135="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E135)*(E135=E$2:E135)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E134)*(E2=E$1:E134))))))</f>
+        <v> </v>
+      </c>
+      <c r="K135" s="25" t="str">
+        <f>IF(OR(E135="",E135="!!!",F135="NEW"),"",INDEX(J$1:J134,SUMPRODUCT(MAX(ROW(E$1:E134)*(E135=E$1:E134)))))</f>
+        <v> </v>
+      </c>
+      <c r="L135" s="26"/>
     </row>
     <row r="136" spans="1:12">
       <c r="A136" s="20" t="s">
-        <v>180</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E136" s="21">
+        <f>IF(D136="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F136" s="22" t="str">
+        <f>IF(OR(E136="",E136="!!!"),"",IF(NOT(ISNA(VLOOKUP(E136,E$1:E135,1,FALSE()))),"OLD",IF(AND(E136&lt;&gt;"",E136&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G136" s="23" t="str">
+        <f>IF(OR(E136="",E136="!!!"),"",IF(OR(J136=0,AND(J136=1,K136=1),AND(J136=1,I136="SBJ"),AND(J136=1,I136=0)),"?IN_FOCUS",IF(J136&lt;=2,"?ACTIVATED",IF(J136&lt;&gt;"","?FAMILIAR",IF(F136="NEW",IF(ISNA(VLOOKUP(E136,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H136" s="24" t="str">
+        <f>IF(J136&lt;&gt;1,"",IF(I136="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I136" s="25" t="str">
+        <f>IF(OR(E136="",E136="!!!",F136="NEW"),"",INDEX(B135:B$2,-1+SUMPRODUCT(MAX(ROW(E135:E$2)*(E136=E135:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J136" s="25" t="str">
+        <f>IF(OR(E136="",E136="!!!",F136="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E136)*(E136=E$2:E136)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E135)*(E2=E$1:E135))))))</f>
+        <v> </v>
+      </c>
+      <c r="K136" s="25" t="str">
+        <f>IF(OR(E136="",E136="!!!",F136="NEW"),"",INDEX(J$1:J135,SUMPRODUCT(MAX(ROW(E$1:E135)*(E136=E$1:E135)))))</f>
+        <v> </v>
+      </c>
+      <c r="L136" s="26"/>
     </row>
     <row r="137" spans="1:12">
-      <c r="A137" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="E137" s="21">
-        <f>IF(D137="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F137" s="22" t="str">
-        <f>IF(OR(E137="",E137="!!!"),"",IF(NOT(ISNA(VLOOKUP(E137,E$1:E136,1,FALSE()))),"OLD",IF(AND(E137&lt;&gt;"",E137&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G137" s="23" t="str">
-        <f>IF(OR(E137="",E137="!!!"),"",IF(OR(J137=0,AND(J137=1,K137=1),AND(J137=1,I137="SBJ"),AND(J137=1,I137=0)),"?IN_FOCUS",IF(J137&lt;=2,"?ACTIVATED",IF(J137&lt;&gt;"","?FAMILIAR",IF(F137="NEW",IF(ISNA(VLOOKUP(E137,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H137" s="24" t="str">
-        <f>IF(J137&lt;&gt;1,"",IF(I137="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I137" s="25" t="str">
-        <f>IF(OR(E137="",E137="!!!",F137="NEW"),"",INDEX(B136:B$2,-1+SUMPRODUCT(MAX(ROW(E136:E$2)*(E137=E136:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J137" s="25" t="str">
-        <f>IF(OR(E137="",E137="!!!",F137="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E137)*(E137=E$2:E137)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E136)*(E2=E$1:E136))))))</f>
-        <v> </v>
-      </c>
-      <c r="K137" s="25" t="str">
-        <f>IF(OR(E137="",E137="!!!",F137="NEW"),"",INDEX(J$1:J136,SUMPRODUCT(MAX(ROW(E$1:E136)*(E137=E$1:E136)))))</f>
-        <v> </v>
-      </c>
-      <c r="L137" s="26"/>
+      <c r="A137" s="20"/>
     </row>
     <row r="138" spans="1:12">
       <c r="A138" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="E138" s="21">
-        <f>IF(D138="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F138" s="22" t="str">
-        <f>IF(OR(E138="",E138="!!!"),"",IF(NOT(ISNA(VLOOKUP(E138,E$1:E137,1,FALSE()))),"OLD",IF(AND(E138&lt;&gt;"",E138&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G138" s="23" t="str">
-        <f>IF(OR(E138="",E138="!!!"),"",IF(OR(J138=0,AND(J138=1,K138=1),AND(J138=1,I138="SBJ"),AND(J138=1,I138=0)),"?IN_FOCUS",IF(J138&lt;=2,"?ACTIVATED",IF(J138&lt;&gt;"","?FAMILIAR",IF(F138="NEW",IF(ISNA(VLOOKUP(E138,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H138" s="24" t="str">
-        <f>IF(J138&lt;&gt;1,"",IF(I138="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I138" s="25" t="str">
-        <f>IF(OR(E138="",E138="!!!",F138="NEW"),"",INDEX(B137:B$2,-1+SUMPRODUCT(MAX(ROW(E137:E$2)*(E138=E137:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J138" s="25" t="str">
-        <f>IF(OR(E138="",E138="!!!",F138="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E138)*(E138=E$2:E138)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E137)*(E2=E$1:E137))))))</f>
-        <v> </v>
-      </c>
-      <c r="K138" s="25" t="str">
-        <f>IF(OR(E138="",E138="!!!",F138="NEW"),"",INDEX(J$1:J137,SUMPRODUCT(MAX(ROW(E$1:E137)*(E138=E$1:E137)))))</f>
-        <v> </v>
-      </c>
-      <c r="L138" s="26"/>
+        <v>183</v>
+      </c>
     </row>
     <row r="139" spans="1:12">
       <c r="A139" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="B139" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C139" s="27" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="E139" s="21">
         <f>IF(D139="?OLD","!!!","")</f>
@@ -6785,7 +6759,7 @@
     </row>
     <row r="140" spans="1:12">
       <c r="A140" s="20" t="s">
-        <v>33</v>
+        <v>185</v>
       </c>
       <c r="E140" s="21">
         <f>IF(D140="?OLD","!!!","")</f>
@@ -6819,13 +6793,13 @@
     </row>
     <row r="141" spans="1:12">
       <c r="A141" s="20" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B141" s="27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C141" s="27" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="E141" s="21">
         <f>IF(D141="?OLD","!!!","")</f>
@@ -6859,13 +6833,7 @@
     </row>
     <row r="142" spans="1:12">
       <c r="A142" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="B142" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="C142" s="27" t="s">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="E142" s="21">
         <f>IF(D142="?OLD","!!!","")</f>
@@ -6899,7 +6867,13 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143" s="20" t="s">
-        <v>130</v>
+        <v>187</v>
+      </c>
+      <c r="B143" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C143" s="27" t="s">
+        <v>188</v>
       </c>
       <c r="E143" s="21">
         <f>IF(D143="?OLD","!!!","")</f>
@@ -6933,13 +6907,13 @@
     </row>
     <row r="144" spans="1:12">
       <c r="A144" s="20" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="B144" s="27" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="C144" s="27" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="E144" s="21">
         <f>IF(D144="?OLD","!!!","")</f>
@@ -6973,7 +6947,7 @@
     </row>
     <row r="145" spans="1:12">
       <c r="A145" s="20" t="s">
-        <v>187</v>
+        <v>133</v>
       </c>
       <c r="E145" s="21">
         <f>IF(D145="?OLD","!!!","")</f>
@@ -7007,7 +6981,13 @@
     </row>
     <row r="146" spans="1:12">
       <c r="A146" s="20" t="s">
-        <v>188</v>
+        <v>157</v>
+      </c>
+      <c r="B146" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C146" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E146" s="21">
         <f>IF(D146="?OLD","!!!","")</f>
@@ -7041,13 +7021,7 @@
     </row>
     <row r="147" spans="1:12">
       <c r="A147" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="B147" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C147" s="27" t="s">
-        <v>117</v>
+        <v>190</v>
       </c>
       <c r="E147" s="21">
         <f>IF(D147="?OLD","!!!","")</f>
@@ -7081,7 +7055,7 @@
     </row>
     <row r="148" spans="1:12">
       <c r="A148" s="20" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E148" s="21">
         <f>IF(D148="?OLD","!!!","")</f>
@@ -7115,7 +7089,13 @@
     </row>
     <row r="149" spans="1:12">
       <c r="A149" s="20" t="s">
-        <v>33</v>
+        <v>192</v>
+      </c>
+      <c r="B149" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C149" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E149" s="21">
         <f>IF(D149="?OLD","!!!","")</f>
@@ -7149,7 +7129,7 @@
     </row>
     <row r="150" spans="1:12">
       <c r="A150" s="20" t="s">
-        <v>130</v>
+        <v>193</v>
       </c>
       <c r="E150" s="21">
         <f>IF(D150="?OLD","!!!","")</f>
@@ -7183,7 +7163,7 @@
     </row>
     <row r="151" spans="1:12">
       <c r="A151" s="20" t="s">
-        <v>161</v>
+        <v>38</v>
       </c>
       <c r="E151" s="21">
         <f>IF(D151="?OLD","!!!","")</f>
@@ -7217,13 +7197,7 @@
     </row>
     <row r="152" spans="1:12">
       <c r="A152" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="B152" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="C152" s="27" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="E152" s="21">
         <f>IF(D152="?OLD","!!!","")</f>
@@ -7257,7 +7231,7 @@
     </row>
     <row r="153" spans="1:12">
       <c r="A153" s="20" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E153" s="21">
         <f>IF(D153="?OLD","!!!","")</f>
@@ -7291,7 +7265,13 @@
     </row>
     <row r="154" spans="1:12">
       <c r="A154" s="20" t="s">
-        <v>130</v>
+        <v>157</v>
+      </c>
+      <c r="B154" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="C154" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E154" s="21">
         <f>IF(D154="?OLD","!!!","")</f>
@@ -7325,13 +7305,7 @@
     </row>
     <row r="155" spans="1:12">
       <c r="A155" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="B155" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C155" s="27" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="E155" s="21">
         <f>IF(D155="?OLD","!!!","")</f>
@@ -7365,7 +7339,7 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E156" s="21">
         <f>IF(D156="?OLD","!!!","")</f>
@@ -7398,96 +7372,96 @@
       <c r="L156" s="26"/>
     </row>
     <row r="157" spans="1:12">
-      <c r="A157" s="20"/>
+      <c r="A157" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="B157" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C157" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="E157" s="21">
+        <f>IF(D157="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F157" s="22" t="str">
+        <f>IF(OR(E157="",E157="!!!"),"",IF(NOT(ISNA(VLOOKUP(E157,E$1:E156,1,FALSE()))),"OLD",IF(AND(E157&lt;&gt;"",E157&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G157" s="23" t="str">
+        <f>IF(OR(E157="",E157="!!!"),"",IF(OR(J157=0,AND(J157=1,K157=1),AND(J157=1,I157="SBJ"),AND(J157=1,I157=0)),"?IN_FOCUS",IF(J157&lt;=2,"?ACTIVATED",IF(J157&lt;&gt;"","?FAMILIAR",IF(F157="NEW",IF(ISNA(VLOOKUP(E157,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H157" s="24" t="str">
+        <f>IF(J157&lt;&gt;1,"",IF(I157="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I157" s="25" t="str">
+        <f>IF(OR(E157="",E157="!!!",F157="NEW"),"",INDEX(B156:B$2,-1+SUMPRODUCT(MAX(ROW(E156:E$2)*(E157=E156:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J157" s="25" t="str">
+        <f>IF(OR(E157="",E157="!!!",F157="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E157)*(E157=E$2:E157)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E156)*(E2=E$1:E156))))))</f>
+        <v> </v>
+      </c>
+      <c r="K157" s="25" t="str">
+        <f>IF(OR(E157="",E157="!!!",F157="NEW"),"",INDEX(J$1:J156,SUMPRODUCT(MAX(ROW(E$1:E156)*(E157=E$1:E156)))))</f>
+        <v> </v>
+      </c>
+      <c r="L157" s="26"/>
     </row>
     <row r="158" spans="1:12">
       <c r="A158" s="20" t="s">
-        <v>192</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E158" s="21">
+        <f>IF(D158="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F158" s="22" t="str">
+        <f>IF(OR(E158="",E158="!!!"),"",IF(NOT(ISNA(VLOOKUP(E158,E$1:E157,1,FALSE()))),"OLD",IF(AND(E158&lt;&gt;"",E158&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G158" s="23" t="str">
+        <f>IF(OR(E158="",E158="!!!"),"",IF(OR(J158=0,AND(J158=1,K158=1),AND(J158=1,I158="SBJ"),AND(J158=1,I158=0)),"?IN_FOCUS",IF(J158&lt;=2,"?ACTIVATED",IF(J158&lt;&gt;"","?FAMILIAR",IF(F158="NEW",IF(ISNA(VLOOKUP(E158,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H158" s="24" t="str">
+        <f>IF(J158&lt;&gt;1,"",IF(I158="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I158" s="25" t="str">
+        <f>IF(OR(E158="",E158="!!!",F158="NEW"),"",INDEX(B157:B$2,-1+SUMPRODUCT(MAX(ROW(E157:E$2)*(E158=E157:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J158" s="25" t="str">
+        <f>IF(OR(E158="",E158="!!!",F158="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E158)*(E158=E$2:E158)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E157)*(E2=E$1:E157))))))</f>
+        <v> </v>
+      </c>
+      <c r="K158" s="25" t="str">
+        <f>IF(OR(E158="",E158="!!!",F158="NEW"),"",INDEX(J$1:J157,SUMPRODUCT(MAX(ROW(E$1:E157)*(E158=E$1:E157)))))</f>
+        <v> </v>
+      </c>
+      <c r="L158" s="26"/>
     </row>
     <row r="159" spans="1:12">
-      <c r="A159" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="B159" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C159" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="E159" s="21">
-        <f>IF(D159="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F159" s="22" t="str">
-        <f>IF(OR(E159="",E159="!!!"),"",IF(NOT(ISNA(VLOOKUP(E159,E$1:E158,1,FALSE()))),"OLD",IF(AND(E159&lt;&gt;"",E159&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G159" s="23" t="str">
-        <f>IF(OR(E159="",E159="!!!"),"",IF(OR(J159=0,AND(J159=1,K159=1),AND(J159=1,I159="SBJ"),AND(J159=1,I159=0)),"?IN_FOCUS",IF(J159&lt;=2,"?ACTIVATED",IF(J159&lt;&gt;"","?FAMILIAR",IF(F159="NEW",IF(ISNA(VLOOKUP(E159,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H159" s="24" t="str">
-        <f>IF(J159&lt;&gt;1,"",IF(I159="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I159" s="25" t="str">
-        <f>IF(OR(E159="",E159="!!!",F159="NEW"),"",INDEX(B158:B$2,-1+SUMPRODUCT(MAX(ROW(E158:E$2)*(E159=E158:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J159" s="25" t="str">
-        <f>IF(OR(E159="",E159="!!!",F159="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E159)*(E159=E$2:E159)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E158)*(E2=E$1:E158))))))</f>
-        <v> </v>
-      </c>
-      <c r="K159" s="25" t="str">
-        <f>IF(OR(E159="",E159="!!!",F159="NEW"),"",INDEX(J$1:J158,SUMPRODUCT(MAX(ROW(E$1:E158)*(E159=E$1:E158)))))</f>
-        <v> </v>
-      </c>
-      <c r="L159" s="26"/>
+      <c r="A159" s="20"/>
     </row>
     <row r="160" spans="1:12">
       <c r="A160" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="E160" s="21">
-        <f>IF(D160="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F160" s="22" t="str">
-        <f>IF(OR(E160="",E160="!!!"),"",IF(NOT(ISNA(VLOOKUP(E160,E$1:E159,1,FALSE()))),"OLD",IF(AND(E160&lt;&gt;"",E160&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G160" s="23" t="str">
-        <f>IF(OR(E160="",E160="!!!"),"",IF(OR(J160=0,AND(J160=1,K160=1),AND(J160=1,I160="SBJ"),AND(J160=1,I160=0)),"?IN_FOCUS",IF(J160&lt;=2,"?ACTIVATED",IF(J160&lt;&gt;"","?FAMILIAR",IF(F160="NEW",IF(ISNA(VLOOKUP(E160,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H160" s="24" t="str">
-        <f>IF(J160&lt;&gt;1,"",IF(I160="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I160" s="25" t="str">
-        <f>IF(OR(E160="",E160="!!!",F160="NEW"),"",INDEX(B159:B$2,-1+SUMPRODUCT(MAX(ROW(E159:E$2)*(E160=E159:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J160" s="25" t="str">
-        <f>IF(OR(E160="",E160="!!!",F160="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E160)*(E160=E$2:E160)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E159)*(E2=E$1:E159))))))</f>
-        <v> </v>
-      </c>
-      <c r="K160" s="25" t="str">
-        <f>IF(OR(E160="",E160="!!!",F160="NEW"),"",INDEX(J$1:J159,SUMPRODUCT(MAX(ROW(E$1:E159)*(E160=E$1:E159)))))</f>
-        <v> </v>
-      </c>
-      <c r="L160" s="26"/>
+        <v>195</v>
+      </c>
     </row>
     <row r="161" spans="1:12">
       <c r="A161" s="20" t="s">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="B161" s="27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C161" s="27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E161" s="21">
         <f>IF(D161="?OLD","!!!","")</f>
@@ -7521,7 +7495,7 @@
     </row>
     <row r="162" spans="1:12">
       <c r="A162" s="20" t="s">
-        <v>114</v>
+        <v>190</v>
       </c>
       <c r="E162" s="21">
         <f>IF(D162="?OLD","!!!","")</f>
@@ -7555,7 +7529,13 @@
     </row>
     <row r="163" spans="1:12">
       <c r="A163" s="20" t="s">
-        <v>194</v>
+        <v>196</v>
+      </c>
+      <c r="B163" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C163" s="27" t="s">
+        <v>106</v>
       </c>
       <c r="E163" s="21">
         <f>IF(D163="?OLD","!!!","")</f>
@@ -7589,13 +7569,7 @@
     </row>
     <row r="164" spans="1:12">
       <c r="A164" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="B164" s="27" t="s">
         <v>116</v>
-      </c>
-      <c r="C164" s="27" t="s">
-        <v>103</v>
       </c>
       <c r="E164" s="21">
         <f>IF(D164="?OLD","!!!","")</f>
@@ -7629,7 +7603,7 @@
     </row>
     <row r="165" spans="1:12">
       <c r="A165" s="20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E165" s="21">
         <f>IF(D165="?OLD","!!!","")</f>
@@ -7663,13 +7637,13 @@
     </row>
     <row r="166" spans="1:12">
       <c r="A166" s="20" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B166" s="27" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="C166" s="27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E166" s="21">
         <f>IF(D166="?OLD","!!!","")</f>
@@ -7703,7 +7677,7 @@
     </row>
     <row r="167" spans="1:12">
       <c r="A167" s="20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E167" s="21">
         <f>IF(D167="?OLD","!!!","")</f>
@@ -7737,7 +7711,13 @@
     </row>
     <row r="168" spans="1:12">
       <c r="A168" s="20" t="s">
-        <v>119</v>
+        <v>200</v>
+      </c>
+      <c r="B168" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C168" s="27" t="s">
+        <v>106</v>
       </c>
       <c r="E168" s="21">
         <f>IF(D168="?OLD","!!!","")</f>
@@ -7771,16 +7751,7 @@
     </row>
     <row r="169" spans="1:12">
       <c r="A169" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="B169" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="C169" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D169" s="27" t="s">
-        <v>98</v>
+        <v>201</v>
       </c>
       <c r="E169" s="21">
         <f>IF(D169="?OLD","!!!","")</f>
@@ -7814,7 +7785,7 @@
     </row>
     <row r="170" spans="1:12">
       <c r="A170" s="20" t="s">
-        <v>200</v>
+        <v>121</v>
       </c>
       <c r="E170" s="21">
         <f>IF(D170="?OLD","!!!","")</f>
@@ -7848,7 +7819,16 @@
     </row>
     <row r="171" spans="1:12">
       <c r="A171" s="20" t="s">
-        <v>104</v>
+        <v>202</v>
+      </c>
+      <c r="B171" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C171" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D171" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E171" s="21">
         <f>IF(D171="?OLD","!!!","")</f>
@@ -7882,7 +7862,7 @@
     </row>
     <row r="172" spans="1:12">
       <c r="A172" s="20" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E172" s="21">
         <f>IF(D172="?OLD","!!!","")</f>
@@ -7916,16 +7896,7 @@
     </row>
     <row r="173" spans="1:12">
       <c r="A173" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="B173" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="C173" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D173" s="27" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E173" s="21">
         <f>IF(D173="?OLD","!!!","")</f>
@@ -7959,7 +7930,7 @@
     </row>
     <row r="174" spans="1:12">
       <c r="A174" s="20" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E174" s="21">
         <f>IF(D174="?OLD","!!!","")</f>
@@ -7993,7 +7964,16 @@
     </row>
     <row r="175" spans="1:12">
       <c r="A175" s="20" t="s">
-        <v>134</v>
+        <v>205</v>
+      </c>
+      <c r="B175" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="C175" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D175" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E175" s="21">
         <f>IF(D175="?OLD","!!!","")</f>
@@ -8026,93 +8006,84 @@
       <c r="L175" s="26"/>
     </row>
     <row r="176" spans="1:12">
-      <c r="A176" s="20"/>
+      <c r="A176" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="E176" s="21">
+        <f>IF(D176="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F176" s="22" t="str">
+        <f>IF(OR(E176="",E176="!!!"),"",IF(NOT(ISNA(VLOOKUP(E176,E$1:E175,1,FALSE()))),"OLD",IF(AND(E176&lt;&gt;"",E176&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G176" s="23" t="str">
+        <f>IF(OR(E176="",E176="!!!"),"",IF(OR(J176=0,AND(J176=1,K176=1),AND(J176=1,I176="SBJ"),AND(J176=1,I176=0)),"?IN_FOCUS",IF(J176&lt;=2,"?ACTIVATED",IF(J176&lt;&gt;"","?FAMILIAR",IF(F176="NEW",IF(ISNA(VLOOKUP(E176,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H176" s="24" t="str">
+        <f>IF(J176&lt;&gt;1,"",IF(I176="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I176" s="25" t="str">
+        <f>IF(OR(E176="",E176="!!!",F176="NEW"),"",INDEX(B175:B$2,-1+SUMPRODUCT(MAX(ROW(E175:E$2)*(E176=E175:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J176" s="25" t="str">
+        <f>IF(OR(E176="",E176="!!!",F176="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E176)*(E176=E$2:E176)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E175)*(E2=E$1:E175))))))</f>
+        <v> </v>
+      </c>
+      <c r="K176" s="25" t="str">
+        <f>IF(OR(E176="",E176="!!!",F176="NEW"),"",INDEX(J$1:J175,SUMPRODUCT(MAX(ROW(E$1:E175)*(E176=E$1:E175)))))</f>
+        <v> </v>
+      </c>
+      <c r="L176" s="26"/>
     </row>
     <row r="177" spans="1:12">
       <c r="A177" s="20" t="s">
-        <v>204</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E177" s="21">
+        <f>IF(D177="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F177" s="22" t="str">
+        <f>IF(OR(E177="",E177="!!!"),"",IF(NOT(ISNA(VLOOKUP(E177,E$1:E176,1,FALSE()))),"OLD",IF(AND(E177&lt;&gt;"",E177&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G177" s="23" t="str">
+        <f>IF(OR(E177="",E177="!!!"),"",IF(OR(J177=0,AND(J177=1,K177=1),AND(J177=1,I177="SBJ"),AND(J177=1,I177=0)),"?IN_FOCUS",IF(J177&lt;=2,"?ACTIVATED",IF(J177&lt;&gt;"","?FAMILIAR",IF(F177="NEW",IF(ISNA(VLOOKUP(E177,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H177" s="24" t="str">
+        <f>IF(J177&lt;&gt;1,"",IF(I177="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I177" s="25" t="str">
+        <f>IF(OR(E177="",E177="!!!",F177="NEW"),"",INDEX(B176:B$2,-1+SUMPRODUCT(MAX(ROW(E176:E$2)*(E177=E176:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J177" s="25" t="str">
+        <f>IF(OR(E177="",E177="!!!",F177="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E177)*(E177=E$2:E177)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E176)*(E2=E$1:E176))))))</f>
+        <v> </v>
+      </c>
+      <c r="K177" s="25" t="str">
+        <f>IF(OR(E177="",E177="!!!",F177="NEW"),"",INDEX(J$1:J176,SUMPRODUCT(MAX(ROW(E$1:E176)*(E177=E$1:E176)))))</f>
+        <v> </v>
+      </c>
+      <c r="L177" s="26"/>
     </row>
     <row r="178" spans="1:12">
-      <c r="A178" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="E178" s="21">
-        <f>IF(D178="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F178" s="22" t="str">
-        <f>IF(OR(E178="",E178="!!!"),"",IF(NOT(ISNA(VLOOKUP(E178,E$1:E177,1,FALSE()))),"OLD",IF(AND(E178&lt;&gt;"",E178&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G178" s="23" t="str">
-        <f>IF(OR(E178="",E178="!!!"),"",IF(OR(J178=0,AND(J178=1,K178=1),AND(J178=1,I178="SBJ"),AND(J178=1,I178=0)),"?IN_FOCUS",IF(J178&lt;=2,"?ACTIVATED",IF(J178&lt;&gt;"","?FAMILIAR",IF(F178="NEW",IF(ISNA(VLOOKUP(E178,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H178" s="24" t="str">
-        <f>IF(J178&lt;&gt;1,"",IF(I178="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I178" s="25" t="str">
-        <f>IF(OR(E178="",E178="!!!",F178="NEW"),"",INDEX(B177:B$2,-1+SUMPRODUCT(MAX(ROW(E177:E$2)*(E178=E177:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J178" s="25" t="str">
-        <f>IF(OR(E178="",E178="!!!",F178="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E178)*(E178=E$2:E178)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E177)*(E2=E$1:E177))))))</f>
-        <v> </v>
-      </c>
-      <c r="K178" s="25" t="str">
-        <f>IF(OR(E178="",E178="!!!",F178="NEW"),"",INDEX(J$1:J177,SUMPRODUCT(MAX(ROW(E$1:E177)*(E178=E$1:E177)))))</f>
-        <v> </v>
-      </c>
-      <c r="L178" s="26"/>
+      <c r="A178" s="20"/>
     </row>
     <row r="179" spans="1:12">
       <c r="A179" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="E179" s="21">
-        <f>IF(D179="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F179" s="22" t="str">
-        <f>IF(OR(E179="",E179="!!!"),"",IF(NOT(ISNA(VLOOKUP(E179,E$1:E178,1,FALSE()))),"OLD",IF(AND(E179&lt;&gt;"",E179&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G179" s="23" t="str">
-        <f>IF(OR(E179="",E179="!!!"),"",IF(OR(J179=0,AND(J179=1,K179=1),AND(J179=1,I179="SBJ"),AND(J179=1,I179=0)),"?IN_FOCUS",IF(J179&lt;=2,"?ACTIVATED",IF(J179&lt;&gt;"","?FAMILIAR",IF(F179="NEW",IF(ISNA(VLOOKUP(E179,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H179" s="24" t="str">
-        <f>IF(J179&lt;&gt;1,"",IF(I179="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I179" s="25" t="str">
-        <f>IF(OR(E179="",E179="!!!",F179="NEW"),"",INDEX(B178:B$2,-1+SUMPRODUCT(MAX(ROW(E178:E$2)*(E179=E178:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J179" s="25" t="str">
-        <f>IF(OR(E179="",E179="!!!",F179="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E179)*(E179=E$2:E179)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E178)*(E2=E$1:E178))))))</f>
-        <v> </v>
-      </c>
-      <c r="K179" s="25" t="str">
-        <f>IF(OR(E179="",E179="!!!",F179="NEW"),"",INDEX(J$1:J178,SUMPRODUCT(MAX(ROW(E$1:E178)*(E179=E$1:E178)))))</f>
-        <v> </v>
-      </c>
-      <c r="L179" s="26"/>
+        <v>207</v>
+      </c>
     </row>
     <row r="180" spans="1:12">
       <c r="A180" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="B180" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="C180" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D180" s="27" t="s">
-        <v>98</v>
+        <v>208</v>
       </c>
       <c r="E180" s="21">
         <f>IF(D180="?OLD","!!!","")</f>
@@ -8146,7 +8117,7 @@
     </row>
     <row r="181" spans="1:12">
       <c r="A181" s="20" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E181" s="21">
         <f>IF(D181="?OLD","!!!","")</f>
@@ -8180,7 +8151,16 @@
     </row>
     <row r="182" spans="1:12">
       <c r="A182" s="20" t="s">
-        <v>104</v>
+        <v>210</v>
+      </c>
+      <c r="B182" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="C182" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D182" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E182" s="21">
         <f>IF(D182="?OLD","!!!","")</f>
@@ -8214,7 +8194,7 @@
     </row>
     <row r="183" spans="1:12">
       <c r="A183" s="20" t="s">
-        <v>109</v>
+        <v>211</v>
       </c>
       <c r="E183" s="21">
         <f>IF(D183="?OLD","!!!","")</f>
@@ -8248,16 +8228,7 @@
     </row>
     <row r="184" spans="1:12">
       <c r="A184" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="B184" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="C184" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="D184" s="27" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E184" s="21">
         <f>IF(D184="?OLD","!!!","")</f>
@@ -8291,7 +8262,7 @@
     </row>
     <row r="185" spans="1:12">
       <c r="A185" s="20" t="s">
-        <v>188</v>
+        <v>111</v>
       </c>
       <c r="E185" s="21">
         <f>IF(D185="?OLD","!!!","")</f>
@@ -8325,13 +8296,16 @@
     </row>
     <row r="186" spans="1:12">
       <c r="A186" s="20" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B186" s="27" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="C186" s="27" t="s">
-        <v>117</v>
+        <v>213</v>
+      </c>
+      <c r="D186" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E186" s="21">
         <f>IF(D186="?OLD","!!!","")</f>
@@ -8365,7 +8339,7 @@
     </row>
     <row r="187" spans="1:12">
       <c r="A187" s="20" t="s">
-        <v>38</v>
+        <v>191</v>
       </c>
       <c r="E187" s="21">
         <f>IF(D187="?OLD","!!!","")</f>
@@ -8399,7 +8373,13 @@
     </row>
     <row r="188" spans="1:12">
       <c r="A188" s="20" t="s">
-        <v>104</v>
+        <v>214</v>
+      </c>
+      <c r="B188" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C188" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E188" s="21">
         <f>IF(D188="?OLD","!!!","")</f>
@@ -8433,10 +8413,7 @@
     </row>
     <row r="189" spans="1:12">
       <c r="A189" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="B189" s="27" t="s">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="E189" s="21">
         <f>IF(D189="?OLD","!!!","")</f>
@@ -8470,7 +8447,7 @@
     </row>
     <row r="190" spans="1:12">
       <c r="A190" s="20" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E190" s="21">
         <f>IF(D190="?OLD","!!!","")</f>
@@ -8504,16 +8481,10 @@
     </row>
     <row r="191" spans="1:12">
       <c r="A191" s="20" t="s">
-        <v>212</v>
+        <v>108</v>
       </c>
       <c r="B191" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="C191" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D191" s="27" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="E191" s="21">
         <f>IF(D191="?OLD","!!!","")</f>
@@ -8547,7 +8518,7 @@
     </row>
     <row r="192" spans="1:12">
       <c r="A192" s="20" t="s">
-        <v>213</v>
+        <v>121</v>
       </c>
       <c r="E192" s="21">
         <f>IF(D192="?OLD","!!!","")</f>
@@ -8581,13 +8552,16 @@
     </row>
     <row r="193" spans="1:12">
       <c r="A193" s="20" t="s">
-        <v>133</v>
+        <v>215</v>
       </c>
       <c r="B193" s="27" t="s">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="C193" s="27" t="s">
-        <v>185</v>
+        <v>100</v>
+      </c>
+      <c r="D193" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E193" s="21">
         <f>IF(D193="?OLD","!!!","")</f>
@@ -8621,7 +8595,7 @@
     </row>
     <row r="194" spans="1:12">
       <c r="A194" s="20" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E194" s="21">
         <f>IF(D194="?OLD","!!!","")</f>
@@ -8655,16 +8629,13 @@
     </row>
     <row r="195" spans="1:12">
       <c r="A195" s="20" t="s">
-        <v>215</v>
+        <v>137</v>
       </c>
       <c r="B195" s="27" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="C195" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D195" s="27" t="s">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="E195" s="21">
         <f>IF(D195="?OLD","!!!","")</f>
@@ -8698,7 +8669,7 @@
     </row>
     <row r="196" spans="1:12">
       <c r="A196" s="20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E196" s="21">
         <f>IF(D196="?OLD","!!!","")</f>
@@ -8732,7 +8703,16 @@
     </row>
     <row r="197" spans="1:12">
       <c r="A197" s="20" t="s">
-        <v>187</v>
+        <v>218</v>
+      </c>
+      <c r="B197" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C197" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D197" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E197" s="21">
         <f>IF(D197="?OLD","!!!","")</f>
@@ -8766,7 +8746,7 @@
     </row>
     <row r="198" spans="1:12">
       <c r="A198" s="20" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E198" s="21">
         <f>IF(D198="?OLD","!!!","")</f>
@@ -8800,7 +8780,7 @@
     </row>
     <row r="199" spans="1:12">
       <c r="A199" s="20" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="E199" s="21">
         <f>IF(D199="?OLD","!!!","")</f>
@@ -8834,13 +8814,7 @@
     </row>
     <row r="200" spans="1:12">
       <c r="A200" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="B200" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="C200" s="27" t="s">
-        <v>117</v>
+        <v>220</v>
       </c>
       <c r="E200" s="21">
         <f>IF(D200="?OLD","!!!","")</f>
@@ -8874,7 +8848,7 @@
     </row>
     <row r="201" spans="1:12">
       <c r="A201" s="20" t="s">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="E201" s="21">
         <f>IF(D201="?OLD","!!!","")</f>
@@ -8908,7 +8882,13 @@
     </row>
     <row r="202" spans="1:12">
       <c r="A202" s="20" t="s">
-        <v>134</v>
+        <v>157</v>
+      </c>
+      <c r="B202" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="C202" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E202" s="21">
         <f>IF(D202="?OLD","!!!","")</f>
@@ -8941,87 +8921,84 @@
       <c r="L202" s="26"/>
     </row>
     <row r="203" spans="1:12">
-      <c r="A203" s="20"/>
+      <c r="A203" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="E203" s="21">
+        <f>IF(D203="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F203" s="22" t="str">
+        <f>IF(OR(E203="",E203="!!!"),"",IF(NOT(ISNA(VLOOKUP(E203,E$1:E202,1,FALSE()))),"OLD",IF(AND(E203&lt;&gt;"",E203&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G203" s="23" t="str">
+        <f>IF(OR(E203="",E203="!!!"),"",IF(OR(J203=0,AND(J203=1,K203=1),AND(J203=1,I203="SBJ"),AND(J203=1,I203=0)),"?IN_FOCUS",IF(J203&lt;=2,"?ACTIVATED",IF(J203&lt;&gt;"","?FAMILIAR",IF(F203="NEW",IF(ISNA(VLOOKUP(E203,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H203" s="24" t="str">
+        <f>IF(J203&lt;&gt;1,"",IF(I203="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I203" s="25" t="str">
+        <f>IF(OR(E203="",E203="!!!",F203="NEW"),"",INDEX(B202:B$2,-1+SUMPRODUCT(MAX(ROW(E202:E$2)*(E203=E202:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J203" s="25" t="str">
+        <f>IF(OR(E203="",E203="!!!",F203="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E203)*(E203=E$2:E203)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E202)*(E2=E$1:E202))))))</f>
+        <v> </v>
+      </c>
+      <c r="K203" s="25" t="str">
+        <f>IF(OR(E203="",E203="!!!",F203="NEW"),"",INDEX(J$1:J202,SUMPRODUCT(MAX(ROW(E$1:E202)*(E203=E$1:E202)))))</f>
+        <v> </v>
+      </c>
+      <c r="L203" s="26"/>
     </row>
     <row r="204" spans="1:12">
       <c r="A204" s="20" t="s">
-        <v>218</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E204" s="21">
+        <f>IF(D204="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F204" s="22" t="str">
+        <f>IF(OR(E204="",E204="!!!"),"",IF(NOT(ISNA(VLOOKUP(E204,E$1:E203,1,FALSE()))),"OLD",IF(AND(E204&lt;&gt;"",E204&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G204" s="23" t="str">
+        <f>IF(OR(E204="",E204="!!!"),"",IF(OR(J204=0,AND(J204=1,K204=1),AND(J204=1,I204="SBJ"),AND(J204=1,I204=0)),"?IN_FOCUS",IF(J204&lt;=2,"?ACTIVATED",IF(J204&lt;&gt;"","?FAMILIAR",IF(F204="NEW",IF(ISNA(VLOOKUP(E204,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H204" s="24" t="str">
+        <f>IF(J204&lt;&gt;1,"",IF(I204="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I204" s="25" t="str">
+        <f>IF(OR(E204="",E204="!!!",F204="NEW"),"",INDEX(B203:B$2,-1+SUMPRODUCT(MAX(ROW(E203:E$2)*(E204=E203:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J204" s="25" t="str">
+        <f>IF(OR(E204="",E204="!!!",F204="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E204)*(E204=E$2:E204)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E203)*(E2=E$1:E203))))))</f>
+        <v> </v>
+      </c>
+      <c r="K204" s="25" t="str">
+        <f>IF(OR(E204="",E204="!!!",F204="NEW"),"",INDEX(J$1:J203,SUMPRODUCT(MAX(ROW(E$1:E203)*(E204=E$1:E203)))))</f>
+        <v> </v>
+      </c>
+      <c r="L204" s="26"/>
     </row>
     <row r="205" spans="1:12">
-      <c r="A205" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="E205" s="21">
-        <f>IF(D205="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F205" s="22" t="str">
-        <f>IF(OR(E205="",E205="!!!"),"",IF(NOT(ISNA(VLOOKUP(E205,E$1:E204,1,FALSE()))),"OLD",IF(AND(E205&lt;&gt;"",E205&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G205" s="23" t="str">
-        <f>IF(OR(E205="",E205="!!!"),"",IF(OR(J205=0,AND(J205=1,K205=1),AND(J205=1,I205="SBJ"),AND(J205=1,I205=0)),"?IN_FOCUS",IF(J205&lt;=2,"?ACTIVATED",IF(J205&lt;&gt;"","?FAMILIAR",IF(F205="NEW",IF(ISNA(VLOOKUP(E205,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H205" s="24" t="str">
-        <f>IF(J205&lt;&gt;1,"",IF(I205="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I205" s="25" t="str">
-        <f>IF(OR(E205="",E205="!!!",F205="NEW"),"",INDEX(B204:B$2,-1+SUMPRODUCT(MAX(ROW(E204:E$2)*(E205=E204:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J205" s="25" t="str">
-        <f>IF(OR(E205="",E205="!!!",F205="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E205)*(E205=E$2:E205)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E204)*(E2=E$1:E204))))))</f>
-        <v> </v>
-      </c>
-      <c r="K205" s="25" t="str">
-        <f>IF(OR(E205="",E205="!!!",F205="NEW"),"",INDEX(J$1:J204,SUMPRODUCT(MAX(ROW(E$1:E204)*(E205=E$1:E204)))))</f>
-        <v> </v>
-      </c>
-      <c r="L205" s="26"/>
+      <c r="A205" s="20"/>
     </row>
     <row r="206" spans="1:12">
       <c r="A206" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="B206" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="E206" s="21">
-        <f>IF(D206="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F206" s="22" t="str">
-        <f>IF(OR(E206="",E206="!!!"),"",IF(NOT(ISNA(VLOOKUP(E206,E$1:E205,1,FALSE()))),"OLD",IF(AND(E206&lt;&gt;"",E206&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G206" s="23" t="str">
-        <f>IF(OR(E206="",E206="!!!"),"",IF(OR(J206=0,AND(J206=1,K206=1),AND(J206=1,I206="SBJ"),AND(J206=1,I206=0)),"?IN_FOCUS",IF(J206&lt;=2,"?ACTIVATED",IF(J206&lt;&gt;"","?FAMILIAR",IF(F206="NEW",IF(ISNA(VLOOKUP(E206,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H206" s="24" t="str">
-        <f>IF(J206&lt;&gt;1,"",IF(I206="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I206" s="25" t="str">
-        <f>IF(OR(E206="",E206="!!!",F206="NEW"),"",INDEX(B205:B$2,-1+SUMPRODUCT(MAX(ROW(E205:E$2)*(E206=E205:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J206" s="25" t="str">
-        <f>IF(OR(E206="",E206="!!!",F206="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E206)*(E206=E$2:E206)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E205)*(E2=E$1:E205))))))</f>
-        <v> </v>
-      </c>
-      <c r="K206" s="25" t="str">
-        <f>IF(OR(E206="",E206="!!!",F206="NEW"),"",INDEX(J$1:J205,SUMPRODUCT(MAX(ROW(E$1:E205)*(E206=E$1:E205)))))</f>
-        <v> </v>
-      </c>
-      <c r="L206" s="26"/>
+        <v>221</v>
+      </c>
     </row>
     <row r="207" spans="1:12">
       <c r="A207" s="20" t="s">
-        <v>105</v>
+        <v>208</v>
       </c>
       <c r="E207" s="21">
         <f>IF(D207="?OLD","!!!","")</f>
@@ -9055,16 +9032,10 @@
     </row>
     <row r="208" spans="1:12">
       <c r="A208" s="20" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="B208" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="C208" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D208" s="27" t="s">
-        <v>98</v>
+        <v>179</v>
       </c>
       <c r="E208" s="21">
         <f>IF(D208="?OLD","!!!","")</f>
@@ -9098,7 +9069,7 @@
     </row>
     <row r="209" spans="1:12">
       <c r="A209" s="20" t="s">
-        <v>220</v>
+        <v>108</v>
       </c>
       <c r="E209" s="21">
         <f>IF(D209="?OLD","!!!","")</f>
@@ -9132,7 +9103,16 @@
     </row>
     <row r="210" spans="1:12">
       <c r="A210" s="20" t="s">
-        <v>104</v>
+        <v>214</v>
+      </c>
+      <c r="B210" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="C210" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D210" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E210" s="21">
         <f>IF(D210="?OLD","!!!","")</f>
@@ -9166,7 +9146,7 @@
     </row>
     <row r="211" spans="1:12">
       <c r="A211" s="20" t="s">
-        <v>109</v>
+        <v>223</v>
       </c>
       <c r="E211" s="21">
         <f>IF(D211="?OLD","!!!","")</f>
@@ -9200,16 +9180,7 @@
     </row>
     <row r="212" spans="1:12">
       <c r="A212" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="B212" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C212" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="D212" s="27" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E212" s="21">
         <f>IF(D212="?OLD","!!!","")</f>
@@ -9243,7 +9214,7 @@
     </row>
     <row r="213" spans="1:12">
       <c r="A213" s="20" t="s">
-        <v>194</v>
+        <v>111</v>
       </c>
       <c r="E213" s="21">
         <f>IF(D213="?OLD","!!!","")</f>
@@ -9277,7 +9248,16 @@
     </row>
     <row r="214" spans="1:12">
       <c r="A214" s="20" t="s">
-        <v>119</v>
+        <v>212</v>
+      </c>
+      <c r="B214" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C214" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="D214" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E214" s="21">
         <f>IF(D214="?OLD","!!!","")</f>
@@ -9311,16 +9291,7 @@
     </row>
     <row r="215" spans="1:12">
       <c r="A215" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="B215" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="C215" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D215" s="27" t="s">
-        <v>98</v>
+        <v>197</v>
       </c>
       <c r="E215" s="21">
         <f>IF(D215="?OLD","!!!","")</f>
@@ -9354,7 +9325,7 @@
     </row>
     <row r="216" spans="1:12">
       <c r="A216" s="20" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="E216" s="21">
         <f>IF(D216="?OLD","!!!","")</f>
@@ -9388,7 +9359,16 @@
     </row>
     <row r="217" spans="1:12">
       <c r="A217" s="20" t="s">
-        <v>187</v>
+        <v>224</v>
+      </c>
+      <c r="B217" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C217" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D217" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E217" s="21">
         <f>IF(D217="?OLD","!!!","")</f>
@@ -9422,7 +9402,7 @@
     </row>
     <row r="218" spans="1:12">
       <c r="A218" s="20" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="E218" s="21">
         <f>IF(D218="?OLD","!!!","")</f>
@@ -9456,16 +9436,7 @@
     </row>
     <row r="219" spans="1:12">
       <c r="A219" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="B219" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="C219" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D219" s="27" t="s">
-        <v>98</v>
+        <v>190</v>
       </c>
       <c r="E219" s="21">
         <f>IF(D219="?OLD","!!!","")</f>
@@ -9499,13 +9470,7 @@
     </row>
     <row r="220" spans="1:12">
       <c r="A220" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="B220" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C220" s="27" t="s">
-        <v>185</v>
+        <v>121</v>
       </c>
       <c r="E220" s="21">
         <f>IF(D220="?OLD","!!!","")</f>
@@ -9539,7 +9504,16 @@
     </row>
     <row r="221" spans="1:12">
       <c r="A221" s="20" t="s">
-        <v>214</v>
+        <v>215</v>
+      </c>
+      <c r="B221" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="C221" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D221" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E221" s="21">
         <f>IF(D221="?OLD","!!!","")</f>
@@ -9573,16 +9547,13 @@
     </row>
     <row r="222" spans="1:12">
       <c r="A222" s="20" t="s">
-        <v>222</v>
+        <v>137</v>
       </c>
       <c r="B222" s="27" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="C222" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D222" s="27" t="s">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="E222" s="21">
         <f>IF(D222="?OLD","!!!","")</f>
@@ -9616,7 +9587,7 @@
     </row>
     <row r="223" spans="1:12">
       <c r="A223" s="20" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E223" s="21">
         <f>IF(D223="?OLD","!!!","")</f>
@@ -9650,7 +9621,16 @@
     </row>
     <row r="224" spans="1:12">
       <c r="A224" s="20" t="s">
-        <v>104</v>
+        <v>225</v>
+      </c>
+      <c r="B224" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C224" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D224" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E224" s="21">
         <f>IF(D224="?OLD","!!!","")</f>
@@ -9684,16 +9664,7 @@
     </row>
     <row r="225" spans="1:12">
       <c r="A225" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="B225" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="C225" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="D225" s="27" t="s">
-        <v>98</v>
+        <v>226</v>
       </c>
       <c r="E225" s="21">
         <f>IF(D225="?OLD","!!!","")</f>
@@ -9727,7 +9698,7 @@
     </row>
     <row r="226" spans="1:12">
       <c r="A226" s="20" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="E226" s="21">
         <f>IF(D226="?OLD","!!!","")</f>
@@ -9761,13 +9732,16 @@
     </row>
     <row r="227" spans="1:12">
       <c r="A227" s="20" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="B227" s="27" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="C227" s="27" t="s">
-        <v>117</v>
+        <v>228</v>
+      </c>
+      <c r="D227" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E227" s="21">
         <f>IF(D227="?OLD","!!!","")</f>
@@ -9801,7 +9775,7 @@
     </row>
     <row r="228" spans="1:12">
       <c r="A228" s="20" t="s">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="E228" s="21">
         <f>IF(D228="?OLD","!!!","")</f>
@@ -9835,7 +9809,13 @@
     </row>
     <row r="229" spans="1:12">
       <c r="A229" s="20" t="s">
-        <v>134</v>
+        <v>194</v>
+      </c>
+      <c r="B229" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="C229" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E229" s="21">
         <f>IF(D229="?OLD","!!!","")</f>
@@ -9868,93 +9848,90 @@
       <c r="L229" s="26"/>
     </row>
     <row r="230" spans="1:12">
-      <c r="A230" s="20"/>
+      <c r="A230" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="E230" s="21">
+        <f>IF(D230="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F230" s="22" t="str">
+        <f>IF(OR(E230="",E230="!!!"),"",IF(NOT(ISNA(VLOOKUP(E230,E$1:E229,1,FALSE()))),"OLD",IF(AND(E230&lt;&gt;"",E230&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G230" s="23" t="str">
+        <f>IF(OR(E230="",E230="!!!"),"",IF(OR(J230=0,AND(J230=1,K230=1),AND(J230=1,I230="SBJ"),AND(J230=1,I230=0)),"?IN_FOCUS",IF(J230&lt;=2,"?ACTIVATED",IF(J230&lt;&gt;"","?FAMILIAR",IF(F230="NEW",IF(ISNA(VLOOKUP(E230,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H230" s="24" t="str">
+        <f>IF(J230&lt;&gt;1,"",IF(I230="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I230" s="25" t="str">
+        <f>IF(OR(E230="",E230="!!!",F230="NEW"),"",INDEX(B229:B$2,-1+SUMPRODUCT(MAX(ROW(E229:E$2)*(E230=E229:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J230" s="25" t="str">
+        <f>IF(OR(E230="",E230="!!!",F230="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E230)*(E230=E$2:E230)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E229)*(E2=E$1:E229))))))</f>
+        <v> </v>
+      </c>
+      <c r="K230" s="25" t="str">
+        <f>IF(OR(E230="",E230="!!!",F230="NEW"),"",INDEX(J$1:J229,SUMPRODUCT(MAX(ROW(E$1:E229)*(E230=E$1:E229)))))</f>
+        <v> </v>
+      </c>
+      <c r="L230" s="26"/>
     </row>
     <row r="231" spans="1:12">
       <c r="A231" s="20" t="s">
-        <v>226</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E231" s="21">
+        <f>IF(D231="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F231" s="22" t="str">
+        <f>IF(OR(E231="",E231="!!!"),"",IF(NOT(ISNA(VLOOKUP(E231,E$1:E230,1,FALSE()))),"OLD",IF(AND(E231&lt;&gt;"",E231&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G231" s="23" t="str">
+        <f>IF(OR(E231="",E231="!!!"),"",IF(OR(J231=0,AND(J231=1,K231=1),AND(J231=1,I231="SBJ"),AND(J231=1,I231=0)),"?IN_FOCUS",IF(J231&lt;=2,"?ACTIVATED",IF(J231&lt;&gt;"","?FAMILIAR",IF(F231="NEW",IF(ISNA(VLOOKUP(E231,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H231" s="24" t="str">
+        <f>IF(J231&lt;&gt;1,"",IF(I231="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I231" s="25" t="str">
+        <f>IF(OR(E231="",E231="!!!",F231="NEW"),"",INDEX(B230:B$2,-1+SUMPRODUCT(MAX(ROW(E230:E$2)*(E231=E230:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J231" s="25" t="str">
+        <f>IF(OR(E231="",E231="!!!",F231="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E231)*(E231=E$2:E231)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E230)*(E2=E$1:E230))))))</f>
+        <v> </v>
+      </c>
+      <c r="K231" s="25" t="str">
+        <f>IF(OR(E231="",E231="!!!",F231="NEW"),"",INDEX(J$1:J230,SUMPRODUCT(MAX(ROW(E$1:E230)*(E231=E$1:E230)))))</f>
+        <v> </v>
+      </c>
+      <c r="L231" s="26"/>
     </row>
     <row r="232" spans="1:12">
-      <c r="A232" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="B232" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C232" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="E232" s="21">
-        <f>IF(D232="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F232" s="22" t="str">
-        <f>IF(OR(E232="",E232="!!!"),"",IF(NOT(ISNA(VLOOKUP(E232,E$1:E231,1,FALSE()))),"OLD",IF(AND(E232&lt;&gt;"",E232&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G232" s="23" t="str">
-        <f>IF(OR(E232="",E232="!!!"),"",IF(OR(J232=0,AND(J232=1,K232=1),AND(J232=1,I232="SBJ"),AND(J232=1,I232=0)),"?IN_FOCUS",IF(J232&lt;=2,"?ACTIVATED",IF(J232&lt;&gt;"","?FAMILIAR",IF(F232="NEW",IF(ISNA(VLOOKUP(E232,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H232" s="24" t="str">
-        <f>IF(J232&lt;&gt;1,"",IF(I232="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I232" s="25" t="str">
-        <f>IF(OR(E232="",E232="!!!",F232="NEW"),"",INDEX(B231:B$2,-1+SUMPRODUCT(MAX(ROW(E231:E$2)*(E232=E231:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J232" s="25" t="str">
-        <f>IF(OR(E232="",E232="!!!",F232="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E232)*(E232=E$2:E232)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E231)*(E2=E$1:E231))))))</f>
-        <v> </v>
-      </c>
-      <c r="K232" s="25" t="str">
-        <f>IF(OR(E232="",E232="!!!",F232="NEW"),"",INDEX(J$1:J231,SUMPRODUCT(MAX(ROW(E$1:E231)*(E232=E$1:E231)))))</f>
-        <v> </v>
-      </c>
-      <c r="L232" s="26"/>
+      <c r="A232" s="20"/>
     </row>
     <row r="233" spans="1:12">
       <c r="A233" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E233" s="21">
-        <f>IF(D233="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F233" s="22" t="str">
-        <f>IF(OR(E233="",E233="!!!"),"",IF(NOT(ISNA(VLOOKUP(E233,E$1:E232,1,FALSE()))),"OLD",IF(AND(E233&lt;&gt;"",E233&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G233" s="23" t="str">
-        <f>IF(OR(E233="",E233="!!!"),"",IF(OR(J233=0,AND(J233=1,K233=1),AND(J233=1,I233="SBJ"),AND(J233=1,I233=0)),"?IN_FOCUS",IF(J233&lt;=2,"?ACTIVATED",IF(J233&lt;&gt;"","?FAMILIAR",IF(F233="NEW",IF(ISNA(VLOOKUP(E233,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H233" s="24" t="str">
-        <f>IF(J233&lt;&gt;1,"",IF(I233="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I233" s="25" t="str">
-        <f>IF(OR(E233="",E233="!!!",F233="NEW"),"",INDEX(B232:B$2,-1+SUMPRODUCT(MAX(ROW(E232:E$2)*(E233=E232:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J233" s="25" t="str">
-        <f>IF(OR(E233="",E233="!!!",F233="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E233)*(E233=E$2:E233)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E232)*(E2=E$1:E232))))))</f>
-        <v> </v>
-      </c>
-      <c r="K233" s="25" t="str">
-        <f>IF(OR(E233="",E233="!!!",F233="NEW"),"",INDEX(J$1:J232,SUMPRODUCT(MAX(ROW(E$1:E232)*(E233=E$1:E232)))))</f>
-        <v> </v>
-      </c>
-      <c r="L233" s="26"/>
+        <v>229</v>
+      </c>
     </row>
     <row r="234" spans="1:12">
       <c r="A234" s="20" t="s">
-        <v>201</v>
+        <v>146</v>
       </c>
       <c r="B234" s="27" t="s">
-        <v>227</v>
+        <v>99</v>
+      </c>
+      <c r="C234" s="27" t="s">
+        <v>106</v>
       </c>
       <c r="E234" s="21">
         <f>IF(D234="?OLD","!!!","")</f>
@@ -9988,7 +9965,7 @@
     </row>
     <row r="235" spans="1:12">
       <c r="A235" s="20" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="E235" s="21">
         <f>IF(D235="?OLD","!!!","")</f>
@@ -10022,7 +9999,10 @@
     </row>
     <row r="236" spans="1:12">
       <c r="A236" s="20" t="s">
-        <v>130</v>
+        <v>204</v>
+      </c>
+      <c r="B236" s="27" t="s">
+        <v>230</v>
       </c>
       <c r="E236" s="21">
         <f>IF(D236="?OLD","!!!","")</f>
@@ -10056,13 +10036,7 @@
     </row>
     <row r="237" spans="1:12">
       <c r="A237" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="B237" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="C237" s="27" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="E237" s="21">
         <f>IF(D237="?OLD","!!!","")</f>
@@ -10096,7 +10070,7 @@
     </row>
     <row r="238" spans="1:12">
       <c r="A238" s="20" t="s">
-        <v>228</v>
+        <v>133</v>
       </c>
       <c r="E238" s="21">
         <f>IF(D238="?OLD","!!!","")</f>
@@ -10130,7 +10104,13 @@
     </row>
     <row r="239" spans="1:12">
       <c r="A239" s="20" t="s">
-        <v>104</v>
+        <v>157</v>
+      </c>
+      <c r="B239" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="C239" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E239" s="21">
         <f>IF(D239="?OLD","!!!","")</f>
@@ -10164,7 +10144,7 @@
     </row>
     <row r="240" spans="1:12">
       <c r="A240" s="20" t="s">
-        <v>49</v>
+        <v>231</v>
       </c>
       <c r="E240" s="21">
         <f>IF(D240="?OLD","!!!","")</f>
@@ -10198,7 +10178,7 @@
     </row>
     <row r="241" spans="1:12">
       <c r="A241" s="20" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E241" s="21">
         <f>IF(D241="?OLD","!!!","")</f>
@@ -10232,7 +10212,7 @@
     </row>
     <row r="242" spans="1:12">
       <c r="A242" s="20" t="s">
-        <v>229</v>
+        <v>52</v>
       </c>
       <c r="E242" s="21">
         <f>IF(D242="?OLD","!!!","")</f>
@@ -10266,12 +10246,6 @@
     </row>
     <row r="243" spans="1:12">
       <c r="A243" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="B243" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="C243" s="27" t="s">
         <v>117</v>
       </c>
       <c r="E243" s="21">
@@ -10306,10 +10280,7 @@
     </row>
     <row r="244" spans="1:12">
       <c r="A244" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="B244" s="27" t="s">
-        <v>127</v>
+        <v>232</v>
       </c>
       <c r="E244" s="21">
         <f>IF(D244="?OLD","!!!","")</f>
@@ -10343,10 +10314,13 @@
     </row>
     <row r="245" spans="1:12">
       <c r="A245" s="20" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="B245" s="27" t="s">
-        <v>127</v>
+        <v>110</v>
+      </c>
+      <c r="C245" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E245" s="21">
         <f>IF(D245="?OLD","!!!","")</f>
@@ -10382,6 +10356,9 @@
       <c r="A246" s="20" t="s">
         <v>133</v>
       </c>
+      <c r="B246" s="27" t="s">
+        <v>179</v>
+      </c>
       <c r="E246" s="21">
         <f>IF(D246="?OLD","!!!","")</f>
         <v/>
@@ -10414,7 +10391,10 @@
     </row>
     <row r="247" spans="1:12">
       <c r="A247" s="20" t="s">
-        <v>64</v>
+        <v>164</v>
+      </c>
+      <c r="B247" s="27" t="s">
+        <v>179</v>
       </c>
       <c r="E247" s="21">
         <f>IF(D247="?OLD","!!!","")</f>
@@ -10448,7 +10428,7 @@
     </row>
     <row r="248" spans="1:12">
       <c r="A248" s="20" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E248" s="21">
         <f>IF(D248="?OLD","!!!","")</f>
@@ -10481,99 +10461,90 @@
       <c r="L248" s="26"/>
     </row>
     <row r="249" spans="1:12">
-      <c r="A249" s="20"/>
+      <c r="A249" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E249" s="21">
+        <f>IF(D249="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F249" s="22" t="str">
+        <f>IF(OR(E249="",E249="!!!"),"",IF(NOT(ISNA(VLOOKUP(E249,E$1:E248,1,FALSE()))),"OLD",IF(AND(E249&lt;&gt;"",E249&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G249" s="23" t="str">
+        <f>IF(OR(E249="",E249="!!!"),"",IF(OR(J249=0,AND(J249=1,K249=1),AND(J249=1,I249="SBJ"),AND(J249=1,I249=0)),"?IN_FOCUS",IF(J249&lt;=2,"?ACTIVATED",IF(J249&lt;&gt;"","?FAMILIAR",IF(F249="NEW",IF(ISNA(VLOOKUP(E249,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H249" s="24" t="str">
+        <f>IF(J249&lt;&gt;1,"",IF(I249="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I249" s="25" t="str">
+        <f>IF(OR(E249="",E249="!!!",F249="NEW"),"",INDEX(B248:B$2,-1+SUMPRODUCT(MAX(ROW(E248:E$2)*(E249=E248:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J249" s="25" t="str">
+        <f>IF(OR(E249="",E249="!!!",F249="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E249)*(E249=E$2:E249)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E248)*(E2=E$1:E248))))))</f>
+        <v> </v>
+      </c>
+      <c r="K249" s="25" t="str">
+        <f>IF(OR(E249="",E249="!!!",F249="NEW"),"",INDEX(J$1:J248,SUMPRODUCT(MAX(ROW(E$1:E248)*(E249=E$1:E248)))))</f>
+        <v> </v>
+      </c>
+      <c r="L249" s="26"/>
     </row>
     <row r="250" spans="1:12">
       <c r="A250" s="20" t="s">
-        <v>230</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E250" s="21">
+        <f>IF(D250="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F250" s="22" t="str">
+        <f>IF(OR(E250="",E250="!!!"),"",IF(NOT(ISNA(VLOOKUP(E250,E$1:E249,1,FALSE()))),"OLD",IF(AND(E250&lt;&gt;"",E250&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G250" s="23" t="str">
+        <f>IF(OR(E250="",E250="!!!"),"",IF(OR(J250=0,AND(J250=1,K250=1),AND(J250=1,I250="SBJ"),AND(J250=1,I250=0)),"?IN_FOCUS",IF(J250&lt;=2,"?ACTIVATED",IF(J250&lt;&gt;"","?FAMILIAR",IF(F250="NEW",IF(ISNA(VLOOKUP(E250,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H250" s="24" t="str">
+        <f>IF(J250&lt;&gt;1,"",IF(I250="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I250" s="25" t="str">
+        <f>IF(OR(E250="",E250="!!!",F250="NEW"),"",INDEX(B249:B$2,-1+SUMPRODUCT(MAX(ROW(E249:E$2)*(E250=E249:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J250" s="25" t="str">
+        <f>IF(OR(E250="",E250="!!!",F250="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E250)*(E250=E$2:E250)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E249)*(E2=E$1:E249))))))</f>
+        <v> </v>
+      </c>
+      <c r="K250" s="25" t="str">
+        <f>IF(OR(E250="",E250="!!!",F250="NEW"),"",INDEX(J$1:J249,SUMPRODUCT(MAX(ROW(E$1:E249)*(E250=E$1:E249)))))</f>
+        <v> </v>
+      </c>
+      <c r="L250" s="26"/>
     </row>
     <row r="251" spans="1:12">
-      <c r="A251" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="B251" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C251" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="E251" s="21">
-        <f>IF(D251="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F251" s="22" t="str">
-        <f>IF(OR(E251="",E251="!!!"),"",IF(NOT(ISNA(VLOOKUP(E251,E$1:E250,1,FALSE()))),"OLD",IF(AND(E251&lt;&gt;"",E251&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G251" s="23" t="str">
-        <f>IF(OR(E251="",E251="!!!"),"",IF(OR(J251=0,AND(J251=1,K251=1),AND(J251=1,I251="SBJ"),AND(J251=1,I251=0)),"?IN_FOCUS",IF(J251&lt;=2,"?ACTIVATED",IF(J251&lt;&gt;"","?FAMILIAR",IF(F251="NEW",IF(ISNA(VLOOKUP(E251,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H251" s="24" t="str">
-        <f>IF(J251&lt;&gt;1,"",IF(I251="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I251" s="25" t="str">
-        <f>IF(OR(E251="",E251="!!!",F251="NEW"),"",INDEX(B250:B$2,-1+SUMPRODUCT(MAX(ROW(E250:E$2)*(E251=E250:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J251" s="25" t="str">
-        <f>IF(OR(E251="",E251="!!!",F251="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E251)*(E251=E$2:E251)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E250)*(E2=E$1:E250))))))</f>
-        <v> </v>
-      </c>
-      <c r="K251" s="25" t="str">
-        <f>IF(OR(E251="",E251="!!!",F251="NEW"),"",INDEX(J$1:J250,SUMPRODUCT(MAX(ROW(E$1:E250)*(E251=E$1:E250)))))</f>
-        <v> </v>
-      </c>
-      <c r="L251" s="26"/>
+      <c r="A251" s="20"/>
     </row>
     <row r="252" spans="1:12">
       <c r="A252" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E252" s="21">
-        <f>IF(D252="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F252" s="22" t="str">
-        <f>IF(OR(E252="",E252="!!!"),"",IF(NOT(ISNA(VLOOKUP(E252,E$1:E251,1,FALSE()))),"OLD",IF(AND(E252&lt;&gt;"",E252&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G252" s="23" t="str">
-        <f>IF(OR(E252="",E252="!!!"),"",IF(OR(J252=0,AND(J252=1,K252=1),AND(J252=1,I252="SBJ"),AND(J252=1,I252=0)),"?IN_FOCUS",IF(J252&lt;=2,"?ACTIVATED",IF(J252&lt;&gt;"","?FAMILIAR",IF(F252="NEW",IF(ISNA(VLOOKUP(E252,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H252" s="24" t="str">
-        <f>IF(J252&lt;&gt;1,"",IF(I252="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I252" s="25" t="str">
-        <f>IF(OR(E252="",E252="!!!",F252="NEW"),"",INDEX(B251:B$2,-1+SUMPRODUCT(MAX(ROW(E251:E$2)*(E252=E251:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J252" s="25" t="str">
-        <f>IF(OR(E252="",E252="!!!",F252="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E252)*(E252=E$2:E252)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E251)*(E2=E$1:E251))))))</f>
-        <v> </v>
-      </c>
-      <c r="K252" s="25" t="str">
-        <f>IF(OR(E252="",E252="!!!",F252="NEW"),"",INDEX(J$1:J251,SUMPRODUCT(MAX(ROW(E$1:E251)*(E252=E$1:E251)))))</f>
-        <v> </v>
-      </c>
-      <c r="L252" s="26"/>
+        <v>233</v>
+      </c>
     </row>
     <row r="253" spans="1:12">
       <c r="A253" s="20" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="B253" s="27" t="s">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="C253" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="D253" s="27" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E253" s="21">
         <f>IF(D253="?OLD","!!!","")</f>
@@ -10607,7 +10578,7 @@
     </row>
     <row r="254" spans="1:12">
       <c r="A254" s="20" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E254" s="21">
         <f>IF(D254="?OLD","!!!","")</f>
@@ -10641,7 +10612,16 @@
     </row>
     <row r="255" spans="1:12">
       <c r="A255" s="20" t="s">
-        <v>214</v>
+        <v>108</v>
+      </c>
+      <c r="B255" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="C255" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="D255" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E255" s="21">
         <f>IF(D255="?OLD","!!!","")</f>
@@ -10675,7 +10655,7 @@
     </row>
     <row r="256" spans="1:12">
       <c r="A256" s="20" t="s">
-        <v>231</v>
+        <v>114</v>
       </c>
       <c r="E256" s="21">
         <f>IF(D256="?OLD","!!!","")</f>
@@ -10709,16 +10689,7 @@
     </row>
     <row r="257" spans="1:12">
       <c r="A257" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="B257" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C257" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D257" s="27" t="s">
-        <v>98</v>
+        <v>217</v>
       </c>
       <c r="E257" s="21">
         <f>IF(D257="?OLD","!!!","")</f>
@@ -10752,16 +10723,7 @@
     </row>
     <row r="258" spans="1:12">
       <c r="A258" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="B258" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="C258" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="D258" s="27" t="s">
-        <v>98</v>
+        <v>234</v>
       </c>
       <c r="E258" s="21">
         <f>IF(D258="?OLD","!!!","")</f>
@@ -10795,7 +10757,16 @@
     </row>
     <row r="259" spans="1:12">
       <c r="A259" s="20" t="s">
-        <v>234</v>
+        <v>235</v>
+      </c>
+      <c r="B259" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C259" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D259" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E259" s="21">
         <f>IF(D259="?OLD","!!!","")</f>
@@ -10829,7 +10800,16 @@
     </row>
     <row r="260" spans="1:12">
       <c r="A260" s="20" t="s">
-        <v>148</v>
+        <v>236</v>
+      </c>
+      <c r="B260" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C260" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D260" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E260" s="21">
         <f>IF(D260="?OLD","!!!","")</f>
@@ -10863,7 +10843,7 @@
     </row>
     <row r="261" spans="1:12">
       <c r="A261" s="20" t="s">
-        <v>187</v>
+        <v>237</v>
       </c>
       <c r="E261" s="21">
         <f>IF(D261="?OLD","!!!","")</f>
@@ -10897,7 +10877,7 @@
     </row>
     <row r="262" spans="1:12">
       <c r="A262" s="20" t="s">
-        <v>235</v>
+        <v>151</v>
       </c>
       <c r="E262" s="21">
         <f>IF(D262="?OLD","!!!","")</f>
@@ -10931,7 +10911,7 @@
     </row>
     <row r="263" spans="1:12">
       <c r="A263" s="20" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="E263" s="21">
         <f>IF(D263="?OLD","!!!","")</f>
@@ -10965,16 +10945,7 @@
     </row>
     <row r="264" spans="1:12">
       <c r="A264" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="B264" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="C264" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D264" s="27" t="s">
-        <v>98</v>
+        <v>238</v>
       </c>
       <c r="E264" s="21">
         <f>IF(D264="?OLD","!!!","")</f>
@@ -11008,7 +10979,7 @@
     </row>
     <row r="265" spans="1:12">
       <c r="A265" s="20" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="E265" s="21">
         <f>IF(D265="?OLD","!!!","")</f>
@@ -11042,7 +11013,16 @@
     </row>
     <row r="266" spans="1:12">
       <c r="A266" s="20" t="s">
-        <v>238</v>
+        <v>239</v>
+      </c>
+      <c r="B266" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C266" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D266" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E266" s="21">
         <f>IF(D266="?OLD","!!!","")</f>
@@ -11076,7 +11056,7 @@
     </row>
     <row r="267" spans="1:12">
       <c r="A267" s="20" t="s">
-        <v>148</v>
+        <v>240</v>
       </c>
       <c r="E267" s="21">
         <f>IF(D267="?OLD","!!!","")</f>
@@ -11110,7 +11090,7 @@
     </row>
     <row r="268" spans="1:12">
       <c r="A268" s="20" t="s">
-        <v>104</v>
+        <v>241</v>
       </c>
       <c r="E268" s="21">
         <f>IF(D268="?OLD","!!!","")</f>
@@ -11144,7 +11124,7 @@
     </row>
     <row r="269" spans="1:12">
       <c r="A269" s="20" t="s">
-        <v>53</v>
+        <v>151</v>
       </c>
       <c r="E269" s="21">
         <f>IF(D269="?OLD","!!!","")</f>
@@ -11178,16 +11158,7 @@
     </row>
     <row r="270" spans="1:12">
       <c r="A270" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="B270" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C270" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="D270" s="27" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E270" s="21">
         <f>IF(D270="?OLD","!!!","")</f>
@@ -11221,16 +11192,7 @@
     </row>
     <row r="271" spans="1:12">
       <c r="A271" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="B271" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="C271" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="D271" s="27" t="s">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="E271" s="21">
         <f>IF(D271="?OLD","!!!","")</f>
@@ -11264,7 +11226,16 @@
     </row>
     <row r="272" spans="1:12">
       <c r="A272" s="20" t="s">
-        <v>104</v>
+        <v>125</v>
+      </c>
+      <c r="B272" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C272" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="D272" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E272" s="21">
         <f>IF(D272="?OLD","!!!","")</f>
@@ -11298,7 +11269,16 @@
     </row>
     <row r="273" spans="1:12">
       <c r="A273" s="20" t="s">
-        <v>239</v>
+        <v>143</v>
+      </c>
+      <c r="B273" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C273" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="D273" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E273" s="21">
         <f>IF(D273="?OLD","!!!","")</f>
@@ -11332,16 +11312,7 @@
     </row>
     <row r="274" spans="1:12">
       <c r="A274" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="B274" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="C274" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="D274" s="27" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E274" s="21">
         <f>IF(D274="?OLD","!!!","")</f>
@@ -11375,7 +11346,7 @@
     </row>
     <row r="275" spans="1:12">
       <c r="A275" s="20" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="E275" s="21">
         <f>IF(D275="?OLD","!!!","")</f>
@@ -11409,16 +11380,16 @@
     </row>
     <row r="276" spans="1:12">
       <c r="A276" s="20" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="B276" s="27" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="C276" s="27" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="D276" s="27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E276" s="21">
         <f>IF(D276="?OLD","!!!","")</f>
@@ -11452,7 +11423,7 @@
     </row>
     <row r="277" spans="1:12">
       <c r="A277" s="20" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="E277" s="21">
         <f>IF(D277="?OLD","!!!","")</f>
@@ -11486,16 +11457,16 @@
     </row>
     <row r="278" spans="1:12">
       <c r="A278" s="20" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B278" s="27" t="s">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="C278" s="27" t="s">
-        <v>138</v>
+        <v>244</v>
       </c>
       <c r="D278" s="27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E278" s="21">
         <f>IF(D278="?OLD","!!!","")</f>
@@ -11529,7 +11500,7 @@
     </row>
     <row r="279" spans="1:12">
       <c r="A279" s="20" t="s">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="E279" s="21">
         <f>IF(D279="?OLD","!!!","")</f>
@@ -11563,7 +11534,16 @@
     </row>
     <row r="280" spans="1:12">
       <c r="A280" s="20" t="s">
-        <v>244</v>
+        <v>245</v>
+      </c>
+      <c r="B280" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C280" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D280" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E280" s="21">
         <f>IF(D280="?OLD","!!!","")</f>
@@ -11597,7 +11577,7 @@
     </row>
     <row r="281" spans="1:12">
       <c r="A281" s="20" t="s">
-        <v>134</v>
+        <v>246</v>
       </c>
       <c r="E281" s="21">
         <f>IF(D281="?OLD","!!!","")</f>
@@ -11630,93 +11610,84 @@
       <c r="L281" s="26"/>
     </row>
     <row r="282" spans="1:12">
-      <c r="A282" s="20"/>
+      <c r="A282" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="E282" s="21">
+        <f>IF(D282="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F282" s="22" t="str">
+        <f>IF(OR(E282="",E282="!!!"),"",IF(NOT(ISNA(VLOOKUP(E282,E$1:E281,1,FALSE()))),"OLD",IF(AND(E282&lt;&gt;"",E282&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G282" s="23" t="str">
+        <f>IF(OR(E282="",E282="!!!"),"",IF(OR(J282=0,AND(J282=1,K282=1),AND(J282=1,I282="SBJ"),AND(J282=1,I282=0)),"?IN_FOCUS",IF(J282&lt;=2,"?ACTIVATED",IF(J282&lt;&gt;"","?FAMILIAR",IF(F282="NEW",IF(ISNA(VLOOKUP(E282,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H282" s="24" t="str">
+        <f>IF(J282&lt;&gt;1,"",IF(I282="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I282" s="25" t="str">
+        <f>IF(OR(E282="",E282="!!!",F282="NEW"),"",INDEX(B281:B$2,-1+SUMPRODUCT(MAX(ROW(E281:E$2)*(E282=E281:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J282" s="25" t="str">
+        <f>IF(OR(E282="",E282="!!!",F282="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E282)*(E282=E$2:E282)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E281)*(E2=E$1:E281))))))</f>
+        <v> </v>
+      </c>
+      <c r="K282" s="25" t="str">
+        <f>IF(OR(E282="",E282="!!!",F282="NEW"),"",INDEX(J$1:J281,SUMPRODUCT(MAX(ROW(E$1:E281)*(E282=E$1:E281)))))</f>
+        <v> </v>
+      </c>
+      <c r="L282" s="26"/>
     </row>
     <row r="283" spans="1:12">
       <c r="A283" s="20" t="s">
-        <v>245</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E283" s="21">
+        <f>IF(D283="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F283" s="22" t="str">
+        <f>IF(OR(E283="",E283="!!!"),"",IF(NOT(ISNA(VLOOKUP(E283,E$1:E282,1,FALSE()))),"OLD",IF(AND(E283&lt;&gt;"",E283&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G283" s="23" t="str">
+        <f>IF(OR(E283="",E283="!!!"),"",IF(OR(J283=0,AND(J283=1,K283=1),AND(J283=1,I283="SBJ"),AND(J283=1,I283=0)),"?IN_FOCUS",IF(J283&lt;=2,"?ACTIVATED",IF(J283&lt;&gt;"","?FAMILIAR",IF(F283="NEW",IF(ISNA(VLOOKUP(E283,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H283" s="24" t="str">
+        <f>IF(J283&lt;&gt;1,"",IF(I283="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I283" s="25" t="str">
+        <f>IF(OR(E283="",E283="!!!",F283="NEW"),"",INDEX(B282:B$2,-1+SUMPRODUCT(MAX(ROW(E282:E$2)*(E283=E282:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J283" s="25" t="str">
+        <f>IF(OR(E283="",E283="!!!",F283="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E283)*(E283=E$2:E283)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E282)*(E2=E$1:E282))))))</f>
+        <v> </v>
+      </c>
+      <c r="K283" s="25" t="str">
+        <f>IF(OR(E283="",E283="!!!",F283="NEW"),"",INDEX(J$1:J282,SUMPRODUCT(MAX(ROW(E$1:E282)*(E283=E$1:E282)))))</f>
+        <v> </v>
+      </c>
+      <c r="L283" s="26"/>
     </row>
     <row r="284" spans="1:12">
-      <c r="A284" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="E284" s="21">
-        <f>IF(D284="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F284" s="22" t="str">
-        <f>IF(OR(E284="",E284="!!!"),"",IF(NOT(ISNA(VLOOKUP(E284,E$1:E283,1,FALSE()))),"OLD",IF(AND(E284&lt;&gt;"",E284&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G284" s="23" t="str">
-        <f>IF(OR(E284="",E284="!!!"),"",IF(OR(J284=0,AND(J284=1,K284=1),AND(J284=1,I284="SBJ"),AND(J284=1,I284=0)),"?IN_FOCUS",IF(J284&lt;=2,"?ACTIVATED",IF(J284&lt;&gt;"","?FAMILIAR",IF(F284="NEW",IF(ISNA(VLOOKUP(E284,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H284" s="24" t="str">
-        <f>IF(J284&lt;&gt;1,"",IF(I284="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I284" s="25" t="str">
-        <f>IF(OR(E284="",E284="!!!",F284="NEW"),"",INDEX(B283:B$2,-1+SUMPRODUCT(MAX(ROW(E283:E$2)*(E284=E283:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J284" s="25" t="str">
-        <f>IF(OR(E284="",E284="!!!",F284="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E284)*(E284=E$2:E284)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E283)*(E2=E$1:E283))))))</f>
-        <v> </v>
-      </c>
-      <c r="K284" s="25" t="str">
-        <f>IF(OR(E284="",E284="!!!",F284="NEW"),"",INDEX(J$1:J283,SUMPRODUCT(MAX(ROW(E$1:E283)*(E284=E$1:E283)))))</f>
-        <v> </v>
-      </c>
-      <c r="L284" s="26"/>
+      <c r="A284" s="20"/>
     </row>
     <row r="285" spans="1:12">
       <c r="A285" s="20" t="s">
-        <v>247</v>
-      </c>
-      <c r="B285" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C285" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D285" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="E285" s="21">
-        <f>IF(D285="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F285" s="22" t="str">
-        <f>IF(OR(E285="",E285="!!!"),"",IF(NOT(ISNA(VLOOKUP(E285,E$1:E284,1,FALSE()))),"OLD",IF(AND(E285&lt;&gt;"",E285&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G285" s="23" t="str">
-        <f>IF(OR(E285="",E285="!!!"),"",IF(OR(J285=0,AND(J285=1,K285=1),AND(J285=1,I285="SBJ"),AND(J285=1,I285=0)),"?IN_FOCUS",IF(J285&lt;=2,"?ACTIVATED",IF(J285&lt;&gt;"","?FAMILIAR",IF(F285="NEW",IF(ISNA(VLOOKUP(E285,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H285" s="24" t="str">
-        <f>IF(J285&lt;&gt;1,"",IF(I285="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I285" s="25" t="str">
-        <f>IF(OR(E285="",E285="!!!",F285="NEW"),"",INDEX(B284:B$2,-1+SUMPRODUCT(MAX(ROW(E284:E$2)*(E285=E284:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J285" s="25" t="str">
-        <f>IF(OR(E285="",E285="!!!",F285="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E285)*(E285=E$2:E285)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E284)*(E2=E$1:E284))))))</f>
-        <v> </v>
-      </c>
-      <c r="K285" s="25" t="str">
-        <f>IF(OR(E285="",E285="!!!",F285="NEW"),"",INDEX(J$1:J284,SUMPRODUCT(MAX(ROW(E$1:E284)*(E285=E$1:E284)))))</f>
-        <v> </v>
-      </c>
-      <c r="L285" s="26"/>
+        <v>248</v>
+      </c>
     </row>
     <row r="286" spans="1:12">
       <c r="A286" s="20" t="s">
-        <v>111</v>
+        <v>249</v>
       </c>
       <c r="E286" s="21">
         <f>IF(D286="?OLD","!!!","")</f>
@@ -11750,16 +11721,16 @@
     </row>
     <row r="287" spans="1:12">
       <c r="A287" s="20" t="s">
-        <v>167</v>
+        <v>250</v>
       </c>
       <c r="B287" s="27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C287" s="27" t="s">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="D287" s="27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E287" s="21">
         <f>IF(D287="?OLD","!!!","")</f>
@@ -11793,7 +11764,7 @@
     </row>
     <row r="288" spans="1:12">
       <c r="A288" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E288" s="21">
         <f>IF(D288="?OLD","!!!","")</f>
@@ -11827,10 +11798,16 @@
     </row>
     <row r="289" spans="1:12">
       <c r="A289" s="20" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="B289" s="27" t="s">
-        <v>227</v>
+        <v>105</v>
+      </c>
+      <c r="C289" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D289" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E289" s="21">
         <f>IF(D289="?OLD","!!!","")</f>
@@ -11864,7 +11841,7 @@
     </row>
     <row r="290" spans="1:12">
       <c r="A290" s="20" t="s">
-        <v>248</v>
+        <v>107</v>
       </c>
       <c r="E290" s="21">
         <f>IF(D290="?OLD","!!!","")</f>
@@ -11898,7 +11875,10 @@
     </row>
     <row r="291" spans="1:12">
       <c r="A291" s="20" t="s">
-        <v>249</v>
+        <v>209</v>
+      </c>
+      <c r="B291" s="27" t="s">
+        <v>230</v>
       </c>
       <c r="E291" s="21">
         <f>IF(D291="?OLD","!!!","")</f>
@@ -11932,7 +11912,7 @@
     </row>
     <row r="292" spans="1:12">
       <c r="A292" s="20" t="s">
-        <v>122</v>
+        <v>251</v>
       </c>
       <c r="E292" s="21">
         <f>IF(D292="?OLD","!!!","")</f>
@@ -11966,7 +11946,7 @@
     </row>
     <row r="293" spans="1:12">
       <c r="A293" s="20" t="s">
-        <v>104</v>
+        <v>252</v>
       </c>
       <c r="E293" s="21">
         <f>IF(D293="?OLD","!!!","")</f>
@@ -12000,7 +11980,7 @@
     </row>
     <row r="294" spans="1:12">
       <c r="A294" s="20" t="s">
-        <v>250</v>
+        <v>124</v>
       </c>
       <c r="E294" s="21">
         <f>IF(D294="?OLD","!!!","")</f>
@@ -12034,7 +12014,7 @@
     </row>
     <row r="295" spans="1:12">
       <c r="A295" s="20" t="s">
-        <v>171</v>
+        <v>107</v>
       </c>
       <c r="E295" s="21">
         <f>IF(D295="?OLD","!!!","")</f>
@@ -12068,7 +12048,7 @@
     </row>
     <row r="296" spans="1:12">
       <c r="A296" s="20" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E296" s="21">
         <f>IF(D296="?OLD","!!!","")</f>
@@ -12102,13 +12082,7 @@
     </row>
     <row r="297" spans="1:12">
       <c r="A297" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="B297" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="C297" s="27" t="s">
-        <v>117</v>
+        <v>173</v>
       </c>
       <c r="E297" s="21">
         <f>IF(D297="?OLD","!!!","")</f>
@@ -12142,7 +12116,7 @@
     </row>
     <row r="298" spans="1:12">
       <c r="A298" s="20" t="s">
-        <v>111</v>
+        <v>254</v>
       </c>
       <c r="E298" s="21">
         <f>IF(D298="?OLD","!!!","")</f>
@@ -12176,7 +12150,13 @@
     </row>
     <row r="299" spans="1:12">
       <c r="A299" s="20" t="s">
-        <v>252</v>
+        <v>177</v>
+      </c>
+      <c r="B299" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C299" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E299" s="21">
         <f>IF(D299="?OLD","!!!","")</f>
@@ -12210,13 +12190,7 @@
     </row>
     <row r="300" spans="1:12">
       <c r="A300" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="B300" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C300" s="27" t="s">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="E300" s="21">
         <f>IF(D300="?OLD","!!!","")</f>
@@ -12250,7 +12224,7 @@
     </row>
     <row r="301" spans="1:12">
       <c r="A301" s="20" t="s">
-        <v>104</v>
+        <v>255</v>
       </c>
       <c r="E301" s="21">
         <f>IF(D301="?OLD","!!!","")</f>
@@ -12284,7 +12258,13 @@
     </row>
     <row r="302" spans="1:12">
       <c r="A302" s="20" t="s">
-        <v>253</v>
+        <v>141</v>
+      </c>
+      <c r="B302" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C302" s="27" t="s">
+        <v>154</v>
       </c>
       <c r="E302" s="21">
         <f>IF(D302="?OLD","!!!","")</f>
@@ -12318,7 +12298,7 @@
     </row>
     <row r="303" spans="1:12">
       <c r="A303" s="20" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E303" s="21">
         <f>IF(D303="?OLD","!!!","")</f>
@@ -12352,7 +12332,7 @@
     </row>
     <row r="304" spans="1:12">
       <c r="A304" s="20" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E304" s="21">
         <f>IF(D304="?OLD","!!!","")</f>
@@ -12386,7 +12366,7 @@
     </row>
     <row r="305" spans="1:12">
       <c r="A305" s="20" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="E305" s="21">
         <f>IF(D305="?OLD","!!!","")</f>
@@ -12420,7 +12400,7 @@
     </row>
     <row r="306" spans="1:12">
       <c r="A306" s="20" t="s">
-        <v>145</v>
+        <v>257</v>
       </c>
       <c r="E306" s="21">
         <f>IF(D306="?OLD","!!!","")</f>
@@ -12454,7 +12434,7 @@
     </row>
     <row r="307" spans="1:12">
       <c r="A307" s="20" t="s">
-        <v>255</v>
+        <v>147</v>
       </c>
       <c r="E307" s="21">
         <f>IF(D307="?OLD","!!!","")</f>
@@ -12488,7 +12468,7 @@
     </row>
     <row r="308" spans="1:12">
       <c r="A308" s="20" t="s">
-        <v>256</v>
+        <v>148</v>
       </c>
       <c r="E308" s="21">
         <f>IF(D308="?OLD","!!!","")</f>
@@ -12522,13 +12502,7 @@
     </row>
     <row r="309" spans="1:12">
       <c r="A309" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="B309" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C309" s="27" t="s">
-        <v>117</v>
+        <v>258</v>
       </c>
       <c r="E309" s="21">
         <f>IF(D309="?OLD","!!!","")</f>
@@ -12562,7 +12536,7 @@
     </row>
     <row r="310" spans="1:12">
       <c r="A310" s="20" t="s">
-        <v>111</v>
+        <v>259</v>
       </c>
       <c r="E310" s="21">
         <f>IF(D310="?OLD","!!!","")</f>
@@ -12596,13 +12570,13 @@
     </row>
     <row r="311" spans="1:12">
       <c r="A311" s="20" t="s">
-        <v>257</v>
+        <v>177</v>
       </c>
       <c r="B311" s="27" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="C311" s="27" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="E311" s="21">
         <f>IF(D311="?OLD","!!!","")</f>
@@ -12636,7 +12610,7 @@
     </row>
     <row r="312" spans="1:12">
       <c r="A312" s="20" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="E312" s="21">
         <f>IF(D312="?OLD","!!!","")</f>
@@ -12670,7 +12644,13 @@
     </row>
     <row r="313" spans="1:12">
       <c r="A313" s="20" t="s">
-        <v>201</v>
+        <v>260</v>
+      </c>
+      <c r="B313" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C313" s="27" t="s">
+        <v>106</v>
       </c>
       <c r="E313" s="21">
         <f>IF(D313="?OLD","!!!","")</f>
@@ -12704,7 +12684,7 @@
     </row>
     <row r="314" spans="1:12">
       <c r="A314" s="20" t="s">
-        <v>258</v>
+        <v>132</v>
       </c>
       <c r="E314" s="21">
         <f>IF(D314="?OLD","!!!","")</f>
@@ -12738,7 +12718,7 @@
     </row>
     <row r="315" spans="1:12">
       <c r="A315" s="20" t="s">
-        <v>259</v>
+        <v>204</v>
       </c>
       <c r="E315" s="21">
         <f>IF(D315="?OLD","!!!","")</f>
@@ -12772,16 +12752,7 @@
     </row>
     <row r="316" spans="1:12">
       <c r="A316" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="B316" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="C316" s="27" t="s">
-        <v>260</v>
-      </c>
-      <c r="D316" s="27" t="s">
-        <v>98</v>
+        <v>261</v>
       </c>
       <c r="E316" s="21">
         <f>IF(D316="?OLD","!!!","")</f>
@@ -12815,7 +12786,7 @@
     </row>
     <row r="317" spans="1:12">
       <c r="A317" s="20" t="s">
-        <v>134</v>
+        <v>262</v>
       </c>
       <c r="E317" s="21">
         <f>IF(D317="?OLD","!!!","")</f>
@@ -12848,11 +12819,51 @@
       <c r="L317" s="26"/>
     </row>
     <row r="318" spans="1:12">
-      <c r="A318" s="20"/>
+      <c r="A318" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="B318" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C318" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="D318" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="E318" s="21">
+        <f>IF(D318="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F318" s="22" t="str">
+        <f>IF(OR(E318="",E318="!!!"),"",IF(NOT(ISNA(VLOOKUP(E318,E$1:E317,1,FALSE()))),"OLD",IF(AND(E318&lt;&gt;"",E318&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G318" s="23" t="str">
+        <f>IF(OR(E318="",E318="!!!"),"",IF(OR(J318=0,AND(J318=1,K318=1),AND(J318=1,I318="SBJ"),AND(J318=1,I318=0)),"?IN_FOCUS",IF(J318&lt;=2,"?ACTIVATED",IF(J318&lt;&gt;"","?FAMILIAR",IF(F318="NEW",IF(ISNA(VLOOKUP(E318,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H318" s="24" t="str">
+        <f>IF(J318&lt;&gt;1,"",IF(I318="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I318" s="25" t="str">
+        <f>IF(OR(E318="",E318="!!!",F318="NEW"),"",INDEX(B317:B$2,-1+SUMPRODUCT(MAX(ROW(E317:E$2)*(E318=E317:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J318" s="25" t="str">
+        <f>IF(OR(E318="",E318="!!!",F318="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E318)*(E318=E$2:E318)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E317)*(E2=E$1:E317))))))</f>
+        <v> </v>
+      </c>
+      <c r="K318" s="25" t="str">
+        <f>IF(OR(E318="",E318="!!!",F318="NEW"),"",INDEX(J$1:J317,SUMPRODUCT(MAX(ROW(E$1:E317)*(E318=E$1:E317)))))</f>
+        <v> </v>
+      </c>
+      <c r="L318" s="26"/>
     </row>
     <row r="319" spans="1:12">
       <c r="A319" s="20" t="s">
-        <v>261</v>
+        <v>138</v>
       </c>
       <c r="E319" s="21">
         <f>IF(D319="?OLD","!!!","")</f>
@@ -12885,19 +12896,11 @@
       <c r="L319" s="26"/>
     </row>
     <row r="320" spans="1:12">
-      <c r="A320" s="20" t="s">
-        <v>262</v>
-      </c>
+      <c r="A320" s="20"/>
     </row>
     <row r="321" spans="1:12">
       <c r="A321" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="B321" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C321" s="27" t="s">
-        <v>103</v>
+        <v>264</v>
       </c>
       <c r="E321" s="21">
         <f>IF(D321="?OLD","!!!","")</f>
@@ -12931,50 +12934,18 @@
     </row>
     <row r="322" spans="1:12">
       <c r="A322" s="20" t="s">
-        <v>264</v>
-      </c>
-      <c r="B322" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C322" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="D322" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="E322" s="21">
-        <f>IF(D322="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F322" s="22" t="str">
-        <f>IF(OR(E322="",E322="!!!"),"",IF(NOT(ISNA(VLOOKUP(E322,E$1:E321,1,FALSE()))),"OLD",IF(AND(E322&lt;&gt;"",E322&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G322" s="23" t="str">
-        <f>IF(OR(E322="",E322="!!!"),"",IF(OR(J322=0,AND(J322=1,K322=1),AND(J322=1,I322="SBJ"),AND(J322=1,I322=0)),"?IN_FOCUS",IF(J322&lt;=2,"?ACTIVATED",IF(J322&lt;&gt;"","?FAMILIAR",IF(F322="NEW",IF(ISNA(VLOOKUP(E322,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H322" s="24" t="str">
-        <f>IF(J322&lt;&gt;1,"",IF(I322="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I322" s="25" t="str">
-        <f>IF(OR(E322="",E322="!!!",F322="NEW"),"",INDEX(B321:B$2,-1+SUMPRODUCT(MAX(ROW(E321:E$2)*(E322=E321:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J322" s="25" t="str">
-        <f>IF(OR(E322="",E322="!!!",F322="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E322)*(E322=E$2:E322)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E321)*(E2=E$1:E321))))))</f>
-        <v> </v>
-      </c>
-      <c r="K322" s="25" t="str">
-        <f>IF(OR(E322="",E322="!!!",F322="NEW"),"",INDEX(J$1:J321,SUMPRODUCT(MAX(ROW(E$1:E321)*(E322=E$1:E321)))))</f>
-        <v> </v>
-      </c>
-      <c r="L322" s="26"/>
+        <v>265</v>
+      </c>
     </row>
     <row r="323" spans="1:12">
       <c r="A323" s="20" t="s">
-        <v>265</v>
+        <v>266</v>
+      </c>
+      <c r="B323" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C323" s="27" t="s">
+        <v>106</v>
       </c>
       <c r="E323" s="21">
         <f>IF(D323="?OLD","!!!","")</f>
@@ -13008,7 +12979,16 @@
     </row>
     <row r="324" spans="1:12">
       <c r="A324" s="20" t="s">
-        <v>104</v>
+        <v>267</v>
+      </c>
+      <c r="B324" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C324" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D324" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E324" s="21">
         <f>IF(D324="?OLD","!!!","")</f>
@@ -13042,16 +13022,7 @@
     </row>
     <row r="325" spans="1:12">
       <c r="A325" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="B325" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C325" s="27" t="s">
-        <v>241</v>
-      </c>
-      <c r="D325" s="27" t="s">
-        <v>98</v>
+        <v>268</v>
       </c>
       <c r="E325" s="21">
         <f>IF(D325="?OLD","!!!","")</f>
@@ -13085,7 +13056,7 @@
     </row>
     <row r="326" spans="1:12">
       <c r="A326" s="20" t="s">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="E326" s="21">
         <f>IF(D326="?OLD","!!!","")</f>
@@ -13119,16 +13090,16 @@
     </row>
     <row r="327" spans="1:12">
       <c r="A327" s="20" t="s">
-        <v>167</v>
+        <v>269</v>
       </c>
       <c r="B327" s="27" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C327" s="27" t="s">
-        <v>138</v>
+        <v>244</v>
       </c>
       <c r="D327" s="27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E327" s="21">
         <f>IF(D327="?OLD","!!!","")</f>
@@ -13162,16 +13133,7 @@
     </row>
     <row r="328" spans="1:12">
       <c r="A328" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="B328" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="C328" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="D328" s="27" t="s">
-        <v>98</v>
+        <v>170</v>
       </c>
       <c r="E328" s="21">
         <f>IF(D328="?OLD","!!!","")</f>
@@ -13205,7 +13167,16 @@
     </row>
     <row r="329" spans="1:12">
       <c r="A329" s="20" t="s">
-        <v>268</v>
+        <v>169</v>
+      </c>
+      <c r="B329" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C329" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D329" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E329" s="21">
         <f>IF(D329="?OLD","!!!","")</f>
@@ -13239,7 +13210,16 @@
     </row>
     <row r="330" spans="1:12">
       <c r="A330" s="20" t="s">
-        <v>269</v>
+        <v>270</v>
+      </c>
+      <c r="B330" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C330" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D330" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E330" s="21">
         <f>IF(D330="?OLD","!!!","")</f>
@@ -13273,7 +13253,7 @@
     </row>
     <row r="331" spans="1:12">
       <c r="A331" s="20" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E331" s="21">
         <f>IF(D331="?OLD","!!!","")</f>
@@ -13307,7 +13287,7 @@
     </row>
     <row r="332" spans="1:12">
       <c r="A332" s="20" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E332" s="21">
         <f>IF(D332="?OLD","!!!","")</f>
@@ -13341,7 +13321,7 @@
     </row>
     <row r="333" spans="1:12">
       <c r="A333" s="20" t="s">
-        <v>206</v>
+        <v>273</v>
       </c>
       <c r="E333" s="21">
         <f>IF(D333="?OLD","!!!","")</f>
@@ -13375,16 +13355,7 @@
     </row>
     <row r="334" spans="1:12">
       <c r="A334" s="20" t="s">
-        <v>272</v>
-      </c>
-      <c r="B334" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C334" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D334" s="27" t="s">
-        <v>98</v>
+        <v>274</v>
       </c>
       <c r="E334" s="21">
         <f>IF(D334="?OLD","!!!","")</f>
@@ -13418,7 +13389,7 @@
     </row>
     <row r="335" spans="1:12">
       <c r="A335" s="20" t="s">
-        <v>111</v>
+        <v>209</v>
       </c>
       <c r="E335" s="21">
         <f>IF(D335="?OLD","!!!","")</f>
@@ -13452,13 +13423,16 @@
     </row>
     <row r="336" spans="1:12">
       <c r="A336" s="20" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B336" s="27" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C336" s="27" t="s">
-        <v>103</v>
+        <v>100</v>
+      </c>
+      <c r="D336" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E336" s="21">
         <f>IF(D336="?OLD","!!!","")</f>
@@ -13492,7 +13466,7 @@
     </row>
     <row r="337" spans="1:12">
       <c r="A337" s="20" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="E337" s="21">
         <f>IF(D337="?OLD","!!!","")</f>
@@ -13526,7 +13500,13 @@
     </row>
     <row r="338" spans="1:12">
       <c r="A338" s="20" t="s">
-        <v>188</v>
+        <v>276</v>
+      </c>
+      <c r="B338" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C338" s="27" t="s">
+        <v>106</v>
       </c>
       <c r="E338" s="21">
         <f>IF(D338="?OLD","!!!","")</f>
@@ -13560,13 +13540,7 @@
     </row>
     <row r="339" spans="1:12">
       <c r="A339" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="B339" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="C339" s="27" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="E339" s="21">
         <f>IF(D339="?OLD","!!!","")</f>
@@ -13600,13 +13574,7 @@
     </row>
     <row r="340" spans="1:12">
       <c r="A340" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="B340" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="C340" s="27" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E340" s="21">
         <f>IF(D340="?OLD","!!!","")</f>
@@ -13640,13 +13608,13 @@
     </row>
     <row r="341" spans="1:12">
       <c r="A341" s="20" t="s">
-        <v>143</v>
+        <v>192</v>
       </c>
       <c r="B341" s="27" t="s">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="C341" s="27" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="E341" s="21">
         <f>IF(D341="?OLD","!!!","")</f>
@@ -13680,7 +13648,13 @@
     </row>
     <row r="342" spans="1:12">
       <c r="A342" s="20" t="s">
-        <v>104</v>
+        <v>277</v>
+      </c>
+      <c r="B342" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C342" s="27" t="s">
+        <v>188</v>
       </c>
       <c r="E342" s="21">
         <f>IF(D342="?OLD","!!!","")</f>
@@ -13714,10 +13688,13 @@
     </row>
     <row r="343" spans="1:12">
       <c r="A343" s="20" t="s">
-        <v>201</v>
+        <v>146</v>
       </c>
       <c r="B343" s="27" t="s">
-        <v>275</v>
+        <v>136</v>
+      </c>
+      <c r="C343" s="27" t="s">
+        <v>154</v>
       </c>
       <c r="E343" s="21">
         <f>IF(D343="?OLD","!!!","")</f>
@@ -13751,7 +13728,7 @@
     </row>
     <row r="344" spans="1:12">
       <c r="A344" s="20" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="E344" s="21">
         <f>IF(D344="?OLD","!!!","")</f>
@@ -13785,13 +13762,10 @@
     </row>
     <row r="345" spans="1:12">
       <c r="A345" s="20" t="s">
-        <v>154</v>
+        <v>204</v>
       </c>
       <c r="B345" s="27" t="s">
-        <v>276</v>
-      </c>
-      <c r="C345" s="27" t="s">
-        <v>117</v>
+        <v>278</v>
       </c>
       <c r="E345" s="21">
         <f>IF(D345="?OLD","!!!","")</f>
@@ -13825,7 +13799,7 @@
     </row>
     <row r="346" spans="1:12">
       <c r="A346" s="20" t="s">
-        <v>277</v>
+        <v>133</v>
       </c>
       <c r="E346" s="21">
         <f>IF(D346="?OLD","!!!","")</f>
@@ -13859,7 +13833,13 @@
     </row>
     <row r="347" spans="1:12">
       <c r="A347" s="20" t="s">
-        <v>64</v>
+        <v>157</v>
+      </c>
+      <c r="B347" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="C347" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E347" s="21">
         <f>IF(D347="?OLD","!!!","")</f>
@@ -13893,7 +13873,7 @@
     </row>
     <row r="348" spans="1:12">
       <c r="A348" s="20" t="s">
-        <v>104</v>
+        <v>280</v>
       </c>
       <c r="E348" s="21">
         <f>IF(D348="?OLD","!!!","")</f>
@@ -13927,7 +13907,7 @@
     </row>
     <row r="349" spans="1:12">
       <c r="A349" s="20" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
       <c r="E349" s="21">
         <f>IF(D349="?OLD","!!!","")</f>
@@ -13961,7 +13941,7 @@
     </row>
     <row r="350" spans="1:12">
       <c r="A350" s="20" t="s">
-        <v>161</v>
+        <v>107</v>
       </c>
       <c r="E350" s="21">
         <f>IF(D350="?OLD","!!!","")</f>
@@ -13995,13 +13975,7 @@
     </row>
     <row r="351" spans="1:12">
       <c r="A351" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="B351" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C351" s="27" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="E351" s="21">
         <f>IF(D351="?OLD","!!!","")</f>
@@ -14035,7 +14009,7 @@
     </row>
     <row r="352" spans="1:12">
       <c r="A352" s="20" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E352" s="21">
         <f>IF(D352="?OLD","!!!","")</f>
@@ -14069,7 +14043,13 @@
     </row>
     <row r="353" spans="1:12">
       <c r="A353" s="20" t="s">
-        <v>130</v>
+        <v>157</v>
+      </c>
+      <c r="B353" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C353" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E353" s="21">
         <f>IF(D353="?OLD","!!!","")</f>
@@ -14103,13 +14083,7 @@
     </row>
     <row r="354" spans="1:12">
       <c r="A354" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="B354" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C354" s="27" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="E354" s="21">
         <f>IF(D354="?OLD","!!!","")</f>
@@ -14143,7 +14117,7 @@
     </row>
     <row r="355" spans="1:12">
       <c r="A355" s="20" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="E355" s="21">
         <f>IF(D355="?OLD","!!!","")</f>
@@ -14177,7 +14151,13 @@
     </row>
     <row r="356" spans="1:12">
       <c r="A356" s="20" t="s">
-        <v>278</v>
+        <v>194</v>
+      </c>
+      <c r="B356" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C356" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E356" s="21">
         <f>IF(D356="?OLD","!!!","")</f>
@@ -14211,7 +14191,7 @@
     </row>
     <row r="357" spans="1:12">
       <c r="A357" s="20" t="s">
-        <v>144</v>
+        <v>12</v>
       </c>
       <c r="E357" s="21">
         <f>IF(D357="?OLD","!!!","")</f>
@@ -14245,7 +14225,7 @@
     </row>
     <row r="358" spans="1:12">
       <c r="A358" s="20" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E358" s="21">
         <f>IF(D358="?OLD","!!!","")</f>
@@ -14279,13 +14259,7 @@
     </row>
     <row r="359" spans="1:12">
       <c r="A359" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="B359" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C359" s="27" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="E359" s="21">
         <f>IF(D359="?OLD","!!!","")</f>
@@ -14319,7 +14293,7 @@
     </row>
     <row r="360" spans="1:12">
       <c r="A360" s="20" t="s">
-        <v>134</v>
+        <v>282</v>
       </c>
       <c r="E360" s="21">
         <f>IF(D360="?OLD","!!!","")</f>
@@ -14353,7 +14327,13 @@
     </row>
     <row r="361" spans="1:12">
       <c r="A361" s="20" t="s">
-        <v>270</v>
+        <v>283</v>
+      </c>
+      <c r="B361" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C361" s="27" t="s">
+        <v>106</v>
       </c>
       <c r="E361" s="21">
         <f>IF(D361="?OLD","!!!","")</f>
@@ -14386,93 +14366,84 @@
       <c r="L361" s="26"/>
     </row>
     <row r="362" spans="1:12">
-      <c r="A362" s="20"/>
+      <c r="A362" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="E362" s="21">
+        <f>IF(D362="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F362" s="22" t="str">
+        <f>IF(OR(E362="",E362="!!!"),"",IF(NOT(ISNA(VLOOKUP(E362,E$1:E361,1,FALSE()))),"OLD",IF(AND(E362&lt;&gt;"",E362&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G362" s="23" t="str">
+        <f>IF(OR(E362="",E362="!!!"),"",IF(OR(J362=0,AND(J362=1,K362=1),AND(J362=1,I362="SBJ"),AND(J362=1,I362=0)),"?IN_FOCUS",IF(J362&lt;=2,"?ACTIVATED",IF(J362&lt;&gt;"","?FAMILIAR",IF(F362="NEW",IF(ISNA(VLOOKUP(E362,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H362" s="24" t="str">
+        <f>IF(J362&lt;&gt;1,"",IF(I362="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I362" s="25" t="str">
+        <f>IF(OR(E362="",E362="!!!",F362="NEW"),"",INDEX(B361:B$2,-1+SUMPRODUCT(MAX(ROW(E361:E$2)*(E362=E361:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J362" s="25" t="str">
+        <f>IF(OR(E362="",E362="!!!",F362="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E362)*(E362=E$2:E362)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E361)*(E2=E$1:E361))))))</f>
+        <v> </v>
+      </c>
+      <c r="K362" s="25" t="str">
+        <f>IF(OR(E362="",E362="!!!",F362="NEW"),"",INDEX(J$1:J361,SUMPRODUCT(MAX(ROW(E$1:E361)*(E362=E$1:E361)))))</f>
+        <v> </v>
+      </c>
+      <c r="L362" s="26"/>
     </row>
     <row r="363" spans="1:12">
       <c r="A363" s="20" t="s">
-        <v>281</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="E363" s="21">
+        <f>IF(D363="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F363" s="22" t="str">
+        <f>IF(OR(E363="",E363="!!!"),"",IF(NOT(ISNA(VLOOKUP(E363,E$1:E362,1,FALSE()))),"OLD",IF(AND(E363&lt;&gt;"",E363&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G363" s="23" t="str">
+        <f>IF(OR(E363="",E363="!!!"),"",IF(OR(J363=0,AND(J363=1,K363=1),AND(J363=1,I363="SBJ"),AND(J363=1,I363=0)),"?IN_FOCUS",IF(J363&lt;=2,"?ACTIVATED",IF(J363&lt;&gt;"","?FAMILIAR",IF(F363="NEW",IF(ISNA(VLOOKUP(E363,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H363" s="24" t="str">
+        <f>IF(J363&lt;&gt;1,"",IF(I363="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I363" s="25" t="str">
+        <f>IF(OR(E363="",E363="!!!",F363="NEW"),"",INDEX(B362:B$2,-1+SUMPRODUCT(MAX(ROW(E362:E$2)*(E363=E362:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J363" s="25" t="str">
+        <f>IF(OR(E363="",E363="!!!",F363="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E363)*(E363=E$2:E363)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E362)*(E2=E$1:E362))))))</f>
+        <v> </v>
+      </c>
+      <c r="K363" s="25" t="str">
+        <f>IF(OR(E363="",E363="!!!",F363="NEW"),"",INDEX(J$1:J362,SUMPRODUCT(MAX(ROW(E$1:E362)*(E363=E$1:E362)))))</f>
+        <v> </v>
+      </c>
+      <c r="L363" s="26"/>
     </row>
     <row r="364" spans="1:12">
-      <c r="A364" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="E364" s="21">
-        <f>IF(D364="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F364" s="22" t="str">
-        <f>IF(OR(E364="",E364="!!!"),"",IF(NOT(ISNA(VLOOKUP(E364,E$1:E363,1,FALSE()))),"OLD",IF(AND(E364&lt;&gt;"",E364&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G364" s="23" t="str">
-        <f>IF(OR(E364="",E364="!!!"),"",IF(OR(J364=0,AND(J364=1,K364=1),AND(J364=1,I364="SBJ"),AND(J364=1,I364=0)),"?IN_FOCUS",IF(J364&lt;=2,"?ACTIVATED",IF(J364&lt;&gt;"","?FAMILIAR",IF(F364="NEW",IF(ISNA(VLOOKUP(E364,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H364" s="24" t="str">
-        <f>IF(J364&lt;&gt;1,"",IF(I364="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I364" s="25" t="str">
-        <f>IF(OR(E364="",E364="!!!",F364="NEW"),"",INDEX(B363:B$2,-1+SUMPRODUCT(MAX(ROW(E363:E$2)*(E364=E363:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J364" s="25" t="str">
-        <f>IF(OR(E364="",E364="!!!",F364="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E364)*(E364=E$2:E364)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E363)*(E2=E$1:E363))))))</f>
-        <v> </v>
-      </c>
-      <c r="K364" s="25" t="str">
-        <f>IF(OR(E364="",E364="!!!",F364="NEW"),"",INDEX(J$1:J363,SUMPRODUCT(MAX(ROW(E$1:E363)*(E364=E$1:E363)))))</f>
-        <v> </v>
-      </c>
-      <c r="L364" s="26"/>
+      <c r="A364" s="20"/>
     </row>
     <row r="365" spans="1:12">
       <c r="A365" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="B365" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C365" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D365" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="E365" s="21">
-        <f>IF(D365="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F365" s="22" t="str">
-        <f>IF(OR(E365="",E365="!!!"),"",IF(NOT(ISNA(VLOOKUP(E365,E$1:E364,1,FALSE()))),"OLD",IF(AND(E365&lt;&gt;"",E365&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G365" s="23" t="str">
-        <f>IF(OR(E365="",E365="!!!"),"",IF(OR(J365=0,AND(J365=1,K365=1),AND(J365=1,I365="SBJ"),AND(J365=1,I365=0)),"?IN_FOCUS",IF(J365&lt;=2,"?ACTIVATED",IF(J365&lt;&gt;"","?FAMILIAR",IF(F365="NEW",IF(ISNA(VLOOKUP(E365,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H365" s="24" t="str">
-        <f>IF(J365&lt;&gt;1,"",IF(I365="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I365" s="25" t="str">
-        <f>IF(OR(E365="",E365="!!!",F365="NEW"),"",INDEX(B364:B$2,-1+SUMPRODUCT(MAX(ROW(E364:E$2)*(E365=E364:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J365" s="25" t="str">
-        <f>IF(OR(E365="",E365="!!!",F365="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E365)*(E365=E$2:E365)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E364)*(E2=E$1:E364))))))</f>
-        <v> </v>
-      </c>
-      <c r="K365" s="25" t="str">
-        <f>IF(OR(E365="",E365="!!!",F365="NEW"),"",INDEX(J$1:J364,SUMPRODUCT(MAX(ROW(E$1:E364)*(E365=E$1:E364)))))</f>
-        <v> </v>
-      </c>
-      <c r="L365" s="26"/>
+        <v>284</v>
+      </c>
     </row>
     <row r="366" spans="1:12">
       <c r="A366" s="20" t="s">
-        <v>283</v>
+        <v>167</v>
       </c>
       <c r="E366" s="21">
         <f>IF(D366="?OLD","!!!","")</f>
@@ -14506,7 +14477,16 @@
     </row>
     <row r="367" spans="1:12">
       <c r="A367" s="20" t="s">
-        <v>115</v>
+        <v>285</v>
+      </c>
+      <c r="B367" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C367" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D367" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E367" s="21">
         <f>IF(D367="?OLD","!!!","")</f>
@@ -14540,7 +14520,7 @@
     </row>
     <row r="368" spans="1:12">
       <c r="A368" s="20" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E368" s="21">
         <f>IF(D368="?OLD","!!!","")</f>
@@ -14574,12 +14554,6 @@
     </row>
     <row r="369" spans="1:12">
       <c r="A369" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="B369" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C369" s="27" t="s">
         <v>117</v>
       </c>
       <c r="E369" s="21">
@@ -14614,7 +14588,7 @@
     </row>
     <row r="370" spans="1:12">
       <c r="A370" s="20" t="s">
-        <v>109</v>
+        <v>287</v>
       </c>
       <c r="E370" s="21">
         <f>IF(D370="?OLD","!!!","")</f>
@@ -14648,7 +14622,13 @@
     </row>
     <row r="371" spans="1:12">
       <c r="A371" s="20" t="s">
-        <v>285</v>
+        <v>157</v>
+      </c>
+      <c r="B371" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C371" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E371" s="21">
         <f>IF(D371="?OLD","!!!","")</f>
@@ -14682,7 +14662,7 @@
     </row>
     <row r="372" spans="1:12">
       <c r="A372" s="20" t="s">
-        <v>286</v>
+        <v>111</v>
       </c>
       <c r="E372" s="21">
         <f>IF(D372="?OLD","!!!","")</f>
@@ -14716,13 +14696,7 @@
     </row>
     <row r="373" spans="1:12">
       <c r="A373" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="B373" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="C373" s="27" t="s">
-        <v>103</v>
+        <v>288</v>
       </c>
       <c r="E373" s="21">
         <f>IF(D373="?OLD","!!!","")</f>
@@ -14756,7 +14730,7 @@
     </row>
     <row r="374" spans="1:12">
       <c r="A374" s="20" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E374" s="21">
         <f>IF(D374="?OLD","!!!","")</f>
@@ -14790,7 +14764,13 @@
     </row>
     <row r="375" spans="1:12">
       <c r="A375" s="20" t="s">
-        <v>201</v>
+        <v>290</v>
+      </c>
+      <c r="B375" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C375" s="27" t="s">
+        <v>106</v>
       </c>
       <c r="E375" s="21">
         <f>IF(D375="?OLD","!!!","")</f>
@@ -14824,16 +14804,7 @@
     </row>
     <row r="376" spans="1:12">
       <c r="A376" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="B376" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C376" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D376" s="27" t="s">
-        <v>98</v>
+        <v>291</v>
       </c>
       <c r="E376" s="21">
         <f>IF(D376="?OLD","!!!","")</f>
@@ -14867,7 +14838,7 @@
     </row>
     <row r="377" spans="1:12">
       <c r="A377" s="20" t="s">
-        <v>145</v>
+        <v>204</v>
       </c>
       <c r="E377" s="21">
         <f>IF(D377="?OLD","!!!","")</f>
@@ -14901,13 +14872,16 @@
     </row>
     <row r="378" spans="1:12">
       <c r="A378" s="20" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B378" s="27" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C378" s="27" t="s">
-        <v>117</v>
+        <v>100</v>
+      </c>
+      <c r="D378" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E378" s="21">
         <f>IF(D378="?OLD","!!!","")</f>
@@ -14941,7 +14915,7 @@
     </row>
     <row r="379" spans="1:12">
       <c r="A379" s="20" t="s">
-        <v>64</v>
+        <v>148</v>
       </c>
       <c r="E379" s="21">
         <f>IF(D379="?OLD","!!!","")</f>
@@ -14975,7 +14949,13 @@
     </row>
     <row r="380" spans="1:12">
       <c r="A380" s="20" t="s">
-        <v>134</v>
+        <v>293</v>
+      </c>
+      <c r="B380" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C380" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E380" s="21">
         <f>IF(D380="?OLD","!!!","")</f>
@@ -15008,93 +14988,84 @@
       <c r="L380" s="26"/>
     </row>
     <row r="381" spans="1:12">
-      <c r="A381" s="20"/>
+      <c r="A381" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E381" s="21">
+        <f>IF(D381="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F381" s="22" t="str">
+        <f>IF(OR(E381="",E381="!!!"),"",IF(NOT(ISNA(VLOOKUP(E381,E$1:E380,1,FALSE()))),"OLD",IF(AND(E381&lt;&gt;"",E381&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G381" s="23" t="str">
+        <f>IF(OR(E381="",E381="!!!"),"",IF(OR(J381=0,AND(J381=1,K381=1),AND(J381=1,I381="SBJ"),AND(J381=1,I381=0)),"?IN_FOCUS",IF(J381&lt;=2,"?ACTIVATED",IF(J381&lt;&gt;"","?FAMILIAR",IF(F381="NEW",IF(ISNA(VLOOKUP(E381,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H381" s="24" t="str">
+        <f>IF(J381&lt;&gt;1,"",IF(I381="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I381" s="25" t="str">
+        <f>IF(OR(E381="",E381="!!!",F381="NEW"),"",INDEX(B380:B$2,-1+SUMPRODUCT(MAX(ROW(E380:E$2)*(E381=E380:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J381" s="25" t="str">
+        <f>IF(OR(E381="",E381="!!!",F381="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E381)*(E381=E$2:E381)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E380)*(E2=E$1:E380))))))</f>
+        <v> </v>
+      </c>
+      <c r="K381" s="25" t="str">
+        <f>IF(OR(E381="",E381="!!!",F381="NEW"),"",INDEX(J$1:J380,SUMPRODUCT(MAX(ROW(E$1:E380)*(E381=E$1:E380)))))</f>
+        <v> </v>
+      </c>
+      <c r="L381" s="26"/>
     </row>
     <row r="382" spans="1:12">
       <c r="A382" s="20" t="s">
-        <v>291</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E382" s="21">
+        <f>IF(D382="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F382" s="22" t="str">
+        <f>IF(OR(E382="",E382="!!!"),"",IF(NOT(ISNA(VLOOKUP(E382,E$1:E381,1,FALSE()))),"OLD",IF(AND(E382&lt;&gt;"",E382&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G382" s="23" t="str">
+        <f>IF(OR(E382="",E382="!!!"),"",IF(OR(J382=0,AND(J382=1,K382=1),AND(J382=1,I382="SBJ"),AND(J382=1,I382=0)),"?IN_FOCUS",IF(J382&lt;=2,"?ACTIVATED",IF(J382&lt;&gt;"","?FAMILIAR",IF(F382="NEW",IF(ISNA(VLOOKUP(E382,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H382" s="24" t="str">
+        <f>IF(J382&lt;&gt;1,"",IF(I382="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I382" s="25" t="str">
+        <f>IF(OR(E382="",E382="!!!",F382="NEW"),"",INDEX(B381:B$2,-1+SUMPRODUCT(MAX(ROW(E381:E$2)*(E382=E381:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J382" s="25" t="str">
+        <f>IF(OR(E382="",E382="!!!",F382="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E382)*(E382=E$2:E382)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E381)*(E2=E$1:E381))))))</f>
+        <v> </v>
+      </c>
+      <c r="K382" s="25" t="str">
+        <f>IF(OR(E382="",E382="!!!",F382="NEW"),"",INDEX(J$1:J381,SUMPRODUCT(MAX(ROW(E$1:E381)*(E382=E$1:E381)))))</f>
+        <v> </v>
+      </c>
+      <c r="L382" s="26"/>
     </row>
     <row r="383" spans="1:12">
-      <c r="A383" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="E383" s="21">
-        <f>IF(D383="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F383" s="22" t="str">
-        <f>IF(OR(E383="",E383="!!!"),"",IF(NOT(ISNA(VLOOKUP(E383,E$1:E382,1,FALSE()))),"OLD",IF(AND(E383&lt;&gt;"",E383&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G383" s="23" t="str">
-        <f>IF(OR(E383="",E383="!!!"),"",IF(OR(J383=0,AND(J383=1,K383=1),AND(J383=1,I383="SBJ"),AND(J383=1,I383=0)),"?IN_FOCUS",IF(J383&lt;=2,"?ACTIVATED",IF(J383&lt;&gt;"","?FAMILIAR",IF(F383="NEW",IF(ISNA(VLOOKUP(E383,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H383" s="24" t="str">
-        <f>IF(J383&lt;&gt;1,"",IF(I383="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I383" s="25" t="str">
-        <f>IF(OR(E383="",E383="!!!",F383="NEW"),"",INDEX(B382:B$2,-1+SUMPRODUCT(MAX(ROW(E382:E$2)*(E383=E382:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J383" s="25" t="str">
-        <f>IF(OR(E383="",E383="!!!",F383="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E383)*(E383=E$2:E383)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E382)*(E2=E$1:E382))))))</f>
-        <v> </v>
-      </c>
-      <c r="K383" s="25" t="str">
-        <f>IF(OR(E383="",E383="!!!",F383="NEW"),"",INDEX(J$1:J382,SUMPRODUCT(MAX(ROW(E$1:E382)*(E383=E$1:E382)))))</f>
-        <v> </v>
-      </c>
-      <c r="L383" s="26"/>
+      <c r="A383" s="20"/>
     </row>
     <row r="384" spans="1:12">
       <c r="A384" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="B384" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C384" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D384" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="E384" s="21">
-        <f>IF(D384="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F384" s="22" t="str">
-        <f>IF(OR(E384="",E384="!!!"),"",IF(NOT(ISNA(VLOOKUP(E384,E$1:E383,1,FALSE()))),"OLD",IF(AND(E384&lt;&gt;"",E384&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G384" s="23" t="str">
-        <f>IF(OR(E384="",E384="!!!"),"",IF(OR(J384=0,AND(J384=1,K384=1),AND(J384=1,I384="SBJ"),AND(J384=1,I384=0)),"?IN_FOCUS",IF(J384&lt;=2,"?ACTIVATED",IF(J384&lt;&gt;"","?FAMILIAR",IF(F384="NEW",IF(ISNA(VLOOKUP(E384,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H384" s="24" t="str">
-        <f>IF(J384&lt;&gt;1,"",IF(I384="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I384" s="25" t="str">
-        <f>IF(OR(E384="",E384="!!!",F384="NEW"),"",INDEX(B383:B$2,-1+SUMPRODUCT(MAX(ROW(E383:E$2)*(E384=E383:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J384" s="25" t="str">
-        <f>IF(OR(E384="",E384="!!!",F384="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E384)*(E384=E$2:E384)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E383)*(E2=E$1:E383))))))</f>
-        <v> </v>
-      </c>
-      <c r="K384" s="25" t="str">
-        <f>IF(OR(E384="",E384="!!!",F384="NEW"),"",INDEX(J$1:J383,SUMPRODUCT(MAX(ROW(E$1:E383)*(E384=E$1:E383)))))</f>
-        <v> </v>
-      </c>
-      <c r="L384" s="26"/>
+        <v>294</v>
+      </c>
     </row>
     <row r="385" spans="1:12">
       <c r="A385" s="20" t="s">
-        <v>293</v>
+        <v>167</v>
       </c>
       <c r="E385" s="21">
         <f>IF(D385="?OLD","!!!","")</f>
@@ -15128,7 +15099,16 @@
     </row>
     <row r="386" spans="1:12">
       <c r="A386" s="20" t="s">
-        <v>104</v>
+        <v>295</v>
+      </c>
+      <c r="B386" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C386" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D386" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E386" s="21">
         <f>IF(D386="?OLD","!!!","")</f>
@@ -15162,7 +15142,7 @@
     </row>
     <row r="387" spans="1:12">
       <c r="A387" s="20" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E387" s="21">
         <f>IF(D387="?OLD","!!!","")</f>
@@ -15196,16 +15176,7 @@
     </row>
     <row r="388" spans="1:12">
       <c r="A388" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="B388" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="C388" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="D388" s="27" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E388" s="21">
         <f>IF(D388="?OLD","!!!","")</f>
@@ -15239,7 +15210,7 @@
     </row>
     <row r="389" spans="1:12">
       <c r="A389" s="20" t="s">
-        <v>198</v>
+        <v>297</v>
       </c>
       <c r="E389" s="21">
         <f>IF(D389="?OLD","!!!","")</f>
@@ -15273,13 +15244,16 @@
     </row>
     <row r="390" spans="1:12">
       <c r="A390" s="20" t="s">
-        <v>295</v>
+        <v>141</v>
       </c>
       <c r="B390" s="27" t="s">
-        <v>102</v>
+        <v>160</v>
       </c>
       <c r="C390" s="27" t="s">
-        <v>103</v>
+        <v>142</v>
+      </c>
+      <c r="D390" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E390" s="21">
         <f>IF(D390="?OLD","!!!","")</f>
@@ -15313,7 +15287,7 @@
     </row>
     <row r="391" spans="1:12">
       <c r="A391" s="20" t="s">
-        <v>144</v>
+        <v>201</v>
       </c>
       <c r="E391" s="21">
         <f>IF(D391="?OLD","!!!","")</f>
@@ -15347,13 +15321,13 @@
     </row>
     <row r="392" spans="1:12">
       <c r="A392" s="20" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="B392" s="27" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C392" s="27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E392" s="21">
         <f>IF(D392="?OLD","!!!","")</f>
@@ -15387,7 +15361,7 @@
     </row>
     <row r="393" spans="1:12">
       <c r="A393" s="20" t="s">
-        <v>296</v>
+        <v>147</v>
       </c>
       <c r="E393" s="21">
         <f>IF(D393="?OLD","!!!","")</f>
@@ -15421,7 +15395,13 @@
     </row>
     <row r="394" spans="1:12">
       <c r="A394" s="20" t="s">
-        <v>297</v>
+        <v>260</v>
+      </c>
+      <c r="B394" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C394" s="27" t="s">
+        <v>106</v>
       </c>
       <c r="E394" s="21">
         <f>IF(D394="?OLD","!!!","")</f>
@@ -15455,7 +15435,7 @@
     </row>
     <row r="395" spans="1:12">
       <c r="A395" s="20" t="s">
-        <v>206</v>
+        <v>299</v>
       </c>
       <c r="E395" s="21">
         <f>IF(D395="?OLD","!!!","")</f>
@@ -15489,16 +15469,7 @@
     </row>
     <row r="396" spans="1:12">
       <c r="A396" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="B396" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C396" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D396" s="27" t="s">
-        <v>98</v>
+        <v>300</v>
       </c>
       <c r="E396" s="21">
         <f>IF(D396="?OLD","!!!","")</f>
@@ -15532,7 +15503,7 @@
     </row>
     <row r="397" spans="1:12">
       <c r="A397" s="20" t="s">
-        <v>299</v>
+        <v>209</v>
       </c>
       <c r="E397" s="21">
         <f>IF(D397="?OLD","!!!","")</f>
@@ -15566,13 +15537,16 @@
     </row>
     <row r="398" spans="1:12">
       <c r="A398" s="20" t="s">
-        <v>142</v>
+        <v>301</v>
       </c>
       <c r="B398" s="27" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C398" s="27" t="s">
-        <v>103</v>
+        <v>100</v>
+      </c>
+      <c r="D398" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E398" s="21">
         <f>IF(D398="?OLD","!!!","")</f>
@@ -15606,7 +15580,7 @@
     </row>
     <row r="399" spans="1:12">
       <c r="A399" s="20" t="s">
-        <v>187</v>
+        <v>302</v>
       </c>
       <c r="E399" s="21">
         <f>IF(D399="?OLD","!!!","")</f>
@@ -15640,13 +15614,13 @@
     </row>
     <row r="400" spans="1:12">
       <c r="A400" s="20" t="s">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="B400" s="27" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="C400" s="27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E400" s="21">
         <f>IF(D400="?OLD","!!!","")</f>
@@ -15680,7 +15654,7 @@
     </row>
     <row r="401" spans="1:12">
       <c r="A401" s="20" t="s">
-        <v>297</v>
+        <v>190</v>
       </c>
       <c r="E401" s="21">
         <f>IF(D401="?OLD","!!!","")</f>
@@ -15714,13 +15688,13 @@
     </row>
     <row r="402" spans="1:12">
       <c r="A402" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="B402" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="B402" s="27" t="s">
-        <v>163</v>
-      </c>
       <c r="C402" s="27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E402" s="21">
         <f>IF(D402="?OLD","!!!","")</f>
@@ -15788,7 +15762,13 @@
     </row>
     <row r="404" spans="1:12">
       <c r="A404" s="20" t="s">
-        <v>104</v>
+        <v>129</v>
+      </c>
+      <c r="B404" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C404" s="27" t="s">
+        <v>106</v>
       </c>
       <c r="E404" s="21">
         <f>IF(D404="?OLD","!!!","")</f>
@@ -15822,10 +15802,7 @@
     </row>
     <row r="405" spans="1:12">
       <c r="A405" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="B405" s="27" t="s">
-        <v>227</v>
+        <v>303</v>
       </c>
       <c r="E405" s="21">
         <f>IF(D405="?OLD","!!!","")</f>
@@ -15859,7 +15836,7 @@
     </row>
     <row r="406" spans="1:12">
       <c r="A406" s="20" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="E406" s="21">
         <f>IF(D406="?OLD","!!!","")</f>
@@ -15893,7 +15870,10 @@
     </row>
     <row r="407" spans="1:12">
       <c r="A407" s="20" t="s">
-        <v>130</v>
+        <v>204</v>
+      </c>
+      <c r="B407" s="27" t="s">
+        <v>230</v>
       </c>
       <c r="E407" s="21">
         <f>IF(D407="?OLD","!!!","")</f>
@@ -15927,13 +15907,7 @@
     </row>
     <row r="408" spans="1:12">
       <c r="A408" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="B408" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="C408" s="27" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="E408" s="21">
         <f>IF(D408="?OLD","!!!","")</f>
@@ -15967,7 +15941,7 @@
     </row>
     <row r="409" spans="1:12">
       <c r="A409" s="20" t="s">
-        <v>228</v>
+        <v>133</v>
       </c>
       <c r="E409" s="21">
         <f>IF(D409="?OLD","!!!","")</f>
@@ -16001,7 +15975,13 @@
     </row>
     <row r="410" spans="1:12">
       <c r="A410" s="20" t="s">
-        <v>134</v>
+        <v>157</v>
+      </c>
+      <c r="B410" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="C410" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E410" s="21">
         <f>IF(D410="?OLD","!!!","")</f>
@@ -16034,84 +16014,84 @@
       <c r="L410" s="26"/>
     </row>
     <row r="411" spans="1:12">
-      <c r="A411" s="20"/>
+      <c r="A411" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="E411" s="21">
+        <f>IF(D411="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F411" s="22" t="str">
+        <f>IF(OR(E411="",E411="!!!"),"",IF(NOT(ISNA(VLOOKUP(E411,E$1:E410,1,FALSE()))),"OLD",IF(AND(E411&lt;&gt;"",E411&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G411" s="23" t="str">
+        <f>IF(OR(E411="",E411="!!!"),"",IF(OR(J411=0,AND(J411=1,K411=1),AND(J411=1,I411="SBJ"),AND(J411=1,I411=0)),"?IN_FOCUS",IF(J411&lt;=2,"?ACTIVATED",IF(J411&lt;&gt;"","?FAMILIAR",IF(F411="NEW",IF(ISNA(VLOOKUP(E411,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H411" s="24" t="str">
+        <f>IF(J411&lt;&gt;1,"",IF(I411="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I411" s="25" t="str">
+        <f>IF(OR(E411="",E411="!!!",F411="NEW"),"",INDEX(B410:B$2,-1+SUMPRODUCT(MAX(ROW(E410:E$2)*(E411=E410:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J411" s="25" t="str">
+        <f>IF(OR(E411="",E411="!!!",F411="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E411)*(E411=E$2:E411)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E410)*(E2=E$1:E410))))))</f>
+        <v> </v>
+      </c>
+      <c r="K411" s="25" t="str">
+        <f>IF(OR(E411="",E411="!!!",F411="NEW"),"",INDEX(J$1:J410,SUMPRODUCT(MAX(ROW(E$1:E410)*(E411=E$1:E410)))))</f>
+        <v> </v>
+      </c>
+      <c r="L411" s="26"/>
     </row>
     <row r="412" spans="1:12">
       <c r="A412" s="20" t="s">
-        <v>301</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E412" s="21">
+        <f>IF(D412="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F412" s="22" t="str">
+        <f>IF(OR(E412="",E412="!!!"),"",IF(NOT(ISNA(VLOOKUP(E412,E$1:E411,1,FALSE()))),"OLD",IF(AND(E412&lt;&gt;"",E412&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G412" s="23" t="str">
+        <f>IF(OR(E412="",E412="!!!"),"",IF(OR(J412=0,AND(J412=1,K412=1),AND(J412=1,I412="SBJ"),AND(J412=1,I412=0)),"?IN_FOCUS",IF(J412&lt;=2,"?ACTIVATED",IF(J412&lt;&gt;"","?FAMILIAR",IF(F412="NEW",IF(ISNA(VLOOKUP(E412,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H412" s="24" t="str">
+        <f>IF(J412&lt;&gt;1,"",IF(I412="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I412" s="25" t="str">
+        <f>IF(OR(E412="",E412="!!!",F412="NEW"),"",INDEX(B411:B$2,-1+SUMPRODUCT(MAX(ROW(E411:E$2)*(E412=E411:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J412" s="25" t="str">
+        <f>IF(OR(E412="",E412="!!!",F412="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E412)*(E412=E$2:E412)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E411)*(E2=E$1:E411))))))</f>
+        <v> </v>
+      </c>
+      <c r="K412" s="25" t="str">
+        <f>IF(OR(E412="",E412="!!!",F412="NEW"),"",INDEX(J$1:J411,SUMPRODUCT(MAX(ROW(E$1:E411)*(E412=E$1:E411)))))</f>
+        <v> </v>
+      </c>
+      <c r="L412" s="26"/>
     </row>
     <row r="413" spans="1:12">
-      <c r="A413" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="E413" s="21">
-        <f>IF(D413="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F413" s="22" t="str">
-        <f>IF(OR(E413="",E413="!!!"),"",IF(NOT(ISNA(VLOOKUP(E413,E$1:E412,1,FALSE()))),"OLD",IF(AND(E413&lt;&gt;"",E413&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G413" s="23" t="str">
-        <f>IF(OR(E413="",E413="!!!"),"",IF(OR(J413=0,AND(J413=1,K413=1),AND(J413=1,I413="SBJ"),AND(J413=1,I413=0)),"?IN_FOCUS",IF(J413&lt;=2,"?ACTIVATED",IF(J413&lt;&gt;"","?FAMILIAR",IF(F413="NEW",IF(ISNA(VLOOKUP(E413,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H413" s="24" t="str">
-        <f>IF(J413&lt;&gt;1,"",IF(I413="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I413" s="25" t="str">
-        <f>IF(OR(E413="",E413="!!!",F413="NEW"),"",INDEX(B412:B$2,-1+SUMPRODUCT(MAX(ROW(E412:E$2)*(E413=E412:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J413" s="25" t="str">
-        <f>IF(OR(E413="",E413="!!!",F413="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E413)*(E413=E$2:E413)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E412)*(E2=E$1:E412))))))</f>
-        <v> </v>
-      </c>
-      <c r="K413" s="25" t="str">
-        <f>IF(OR(E413="",E413="!!!",F413="NEW"),"",INDEX(J$1:J412,SUMPRODUCT(MAX(ROW(E$1:E412)*(E413=E$1:E412)))))</f>
-        <v> </v>
-      </c>
-      <c r="L413" s="26"/>
+      <c r="A413" s="20"/>
     </row>
     <row r="414" spans="1:12">
       <c r="A414" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="E414" s="21">
-        <f>IF(D414="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F414" s="22" t="str">
-        <f>IF(OR(E414="",E414="!!!"),"",IF(NOT(ISNA(VLOOKUP(E414,E$1:E413,1,FALSE()))),"OLD",IF(AND(E414&lt;&gt;"",E414&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G414" s="23" t="str">
-        <f>IF(OR(E414="",E414="!!!"),"",IF(OR(J414=0,AND(J414=1,K414=1),AND(J414=1,I414="SBJ"),AND(J414=1,I414=0)),"?IN_FOCUS",IF(J414&lt;=2,"?ACTIVATED",IF(J414&lt;&gt;"","?FAMILIAR",IF(F414="NEW",IF(ISNA(VLOOKUP(E414,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H414" s="24" t="str">
-        <f>IF(J414&lt;&gt;1,"",IF(I414="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I414" s="25" t="str">
-        <f>IF(OR(E414="",E414="!!!",F414="NEW"),"",INDEX(B413:B$2,-1+SUMPRODUCT(MAX(ROW(E413:E$2)*(E414=E413:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J414" s="25" t="str">
-        <f>IF(OR(E414="",E414="!!!",F414="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E414)*(E414=E$2:E414)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E413)*(E2=E$1:E413))))))</f>
-        <v> </v>
-      </c>
-      <c r="K414" s="25" t="str">
-        <f>IF(OR(E414="",E414="!!!",F414="NEW"),"",INDEX(J$1:J413,SUMPRODUCT(MAX(ROW(E$1:E413)*(E414=E$1:E413)))))</f>
-        <v> </v>
-      </c>
-      <c r="L414" s="26"/>
+        <v>304</v>
+      </c>
     </row>
     <row r="415" spans="1:12">
       <c r="A415" s="20" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E415" s="21">
         <f>IF(D415="?OLD","!!!","")</f>
@@ -16145,13 +16125,7 @@
     </row>
     <row r="416" spans="1:12">
       <c r="A416" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="B416" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="C416" s="27" t="s">
-        <v>117</v>
+        <v>173</v>
       </c>
       <c r="E416" s="21">
         <f>IF(D416="?OLD","!!!","")</f>
@@ -16185,7 +16159,7 @@
     </row>
     <row r="417" spans="1:12">
       <c r="A417" s="20" t="s">
-        <v>111</v>
+        <v>306</v>
       </c>
       <c r="E417" s="21">
         <f>IF(D417="?OLD","!!!","")</f>
@@ -16219,16 +16193,13 @@
     </row>
     <row r="418" spans="1:12">
       <c r="A418" s="20" t="s">
-        <v>137</v>
+        <v>307</v>
       </c>
       <c r="B418" s="27" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="C418" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="D418" s="27" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="E418" s="21">
         <f>IF(D418="?OLD","!!!","")</f>
@@ -16262,7 +16233,7 @@
     </row>
     <row r="419" spans="1:12">
       <c r="A419" s="20" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="E419" s="21">
         <f>IF(D419="?OLD","!!!","")</f>
@@ -16296,16 +16267,16 @@
     </row>
     <row r="420" spans="1:12">
       <c r="A420" s="20" t="s">
-        <v>305</v>
+        <v>141</v>
       </c>
       <c r="B420" s="27" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C420" s="27" t="s">
-        <v>225</v>
+        <v>142</v>
       </c>
       <c r="D420" s="27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E420" s="21">
         <f>IF(D420="?OLD","!!!","")</f>
@@ -16339,16 +16310,7 @@
     </row>
     <row r="421" spans="1:12">
       <c r="A421" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="B421" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="C421" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="D421" s="27" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="E421" s="21">
         <f>IF(D421="?OLD","!!!","")</f>
@@ -16382,7 +16344,16 @@
     </row>
     <row r="422" spans="1:12">
       <c r="A422" s="20" t="s">
-        <v>104</v>
+        <v>308</v>
+      </c>
+      <c r="B422" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C422" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="D422" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E422" s="21">
         <f>IF(D422="?OLD","!!!","")</f>
@@ -16416,7 +16387,16 @@
     </row>
     <row r="423" spans="1:12">
       <c r="A423" s="20" t="s">
-        <v>294</v>
+        <v>309</v>
+      </c>
+      <c r="B423" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C423" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="D423" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E423" s="21">
         <f>IF(D423="?OLD","!!!","")</f>
@@ -16450,16 +16430,7 @@
     </row>
     <row r="424" spans="1:12">
       <c r="A424" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="B424" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="C424" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="D424" s="27" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E424" s="21">
         <f>IF(D424="?OLD","!!!","")</f>
@@ -16493,7 +16464,7 @@
     </row>
     <row r="425" spans="1:12">
       <c r="A425" s="20" t="s">
-        <v>198</v>
+        <v>297</v>
       </c>
       <c r="E425" s="21">
         <f>IF(D425="?OLD","!!!","")</f>
@@ -16527,7 +16498,16 @@
     </row>
     <row r="426" spans="1:12">
       <c r="A426" s="20" t="s">
-        <v>206</v>
+        <v>308</v>
+      </c>
+      <c r="B426" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="C426" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="D426" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E426" s="21">
         <f>IF(D426="?OLD","!!!","")</f>
@@ -16561,16 +16541,7 @@
     </row>
     <row r="427" spans="1:12">
       <c r="A427" s="20" t="s">
-        <v>307</v>
-      </c>
-      <c r="B427" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="C427" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D427" s="27" t="s">
-        <v>98</v>
+        <v>201</v>
       </c>
       <c r="E427" s="21">
         <f>IF(D427="?OLD","!!!","")</f>
@@ -16604,7 +16575,7 @@
     </row>
     <row r="428" spans="1:12">
       <c r="A428" s="20" t="s">
-        <v>308</v>
+        <v>209</v>
       </c>
       <c r="E428" s="21">
         <f>IF(D428="?OLD","!!!","")</f>
@@ -16638,7 +16609,16 @@
     </row>
     <row r="429" spans="1:12">
       <c r="A429" s="20" t="s">
-        <v>104</v>
+        <v>310</v>
+      </c>
+      <c r="B429" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C429" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D429" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E429" s="21">
         <f>IF(D429="?OLD","!!!","")</f>
@@ -16672,7 +16652,7 @@
     </row>
     <row r="430" spans="1:12">
       <c r="A430" s="20" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E430" s="21">
         <f>IF(D430="?OLD","!!!","")</f>
@@ -16706,13 +16686,7 @@
     </row>
     <row r="431" spans="1:12">
       <c r="A431" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="B431" s="27" t="s">
         <v>107</v>
-      </c>
-      <c r="C431" s="27" t="s">
-        <v>103</v>
       </c>
       <c r="E431" s="21">
         <f>IF(D431="?OLD","!!!","")</f>
@@ -16746,7 +16720,7 @@
     </row>
     <row r="432" spans="1:12">
       <c r="A432" s="20" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E432" s="21">
         <f>IF(D432="?OLD","!!!","")</f>
@@ -16780,13 +16754,13 @@
     </row>
     <row r="433" spans="1:12">
       <c r="A433" s="20" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B433" s="27" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="C433" s="27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E433" s="21">
         <f>IF(D433="?OLD","!!!","")</f>
@@ -16820,7 +16794,7 @@
     </row>
     <row r="434" spans="1:12">
       <c r="A434" s="20" t="s">
-        <v>111</v>
+        <v>314</v>
       </c>
       <c r="E434" s="21">
         <f>IF(D434="?OLD","!!!","")</f>
@@ -16854,13 +16828,13 @@
     </row>
     <row r="435" spans="1:12">
       <c r="A435" s="20" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B435" s="27" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="C435" s="27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E435" s="21">
         <f>IF(D435="?OLD","!!!","")</f>
@@ -16894,7 +16868,7 @@
     </row>
     <row r="436" spans="1:12">
       <c r="A436" s="20" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="E436" s="21">
         <f>IF(D436="?OLD","!!!","")</f>
@@ -16928,7 +16902,13 @@
     </row>
     <row r="437" spans="1:12">
       <c r="A437" s="20" t="s">
-        <v>314</v>
+        <v>316</v>
+      </c>
+      <c r="B437" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C437" s="27" t="s">
+        <v>106</v>
       </c>
       <c r="E437" s="21">
         <f>IF(D437="?OLD","!!!","")</f>
@@ -16962,7 +16942,7 @@
     </row>
     <row r="438" spans="1:12">
       <c r="A438" s="20" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E438" s="21">
         <f>IF(D438="?OLD","!!!","")</f>
@@ -16996,10 +16976,7 @@
     </row>
     <row r="439" spans="1:12">
       <c r="A439" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="B439" s="27" t="s">
-        <v>157</v>
+        <v>317</v>
       </c>
       <c r="E439" s="21">
         <f>IF(D439="?OLD","!!!","")</f>
@@ -17033,7 +17010,7 @@
     </row>
     <row r="440" spans="1:12">
       <c r="A440" s="20" t="s">
-        <v>190</v>
+        <v>107</v>
       </c>
       <c r="E440" s="21">
         <f>IF(D440="?OLD","!!!","")</f>
@@ -17067,7 +17044,10 @@
     </row>
     <row r="441" spans="1:12">
       <c r="A441" s="20" t="s">
-        <v>13</v>
+        <v>204</v>
+      </c>
+      <c r="B441" s="27" t="s">
+        <v>160</v>
       </c>
       <c r="E441" s="21">
         <f>IF(D441="?OLD","!!!","")</f>
@@ -17101,7 +17081,7 @@
     </row>
     <row r="442" spans="1:12">
       <c r="A442" s="20" t="s">
-        <v>315</v>
+        <v>193</v>
       </c>
       <c r="E442" s="21">
         <f>IF(D442="?OLD","!!!","")</f>
@@ -17135,7 +17115,7 @@
     </row>
     <row r="443" spans="1:12">
       <c r="A443" s="20" t="s">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="E443" s="21">
         <f>IF(D443="?OLD","!!!","")</f>
@@ -17168,93 +17148,84 @@
       <c r="L443" s="26"/>
     </row>
     <row r="444" spans="1:12">
-      <c r="A444" s="20"/>
+      <c r="A444" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="E444" s="21">
+        <f>IF(D444="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F444" s="22" t="str">
+        <f>IF(OR(E444="",E444="!!!"),"",IF(NOT(ISNA(VLOOKUP(E444,E$1:E443,1,FALSE()))),"OLD",IF(AND(E444&lt;&gt;"",E444&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G444" s="23" t="str">
+        <f>IF(OR(E444="",E444="!!!"),"",IF(OR(J444=0,AND(J444=1,K444=1),AND(J444=1,I444="SBJ"),AND(J444=1,I444=0)),"?IN_FOCUS",IF(J444&lt;=2,"?ACTIVATED",IF(J444&lt;&gt;"","?FAMILIAR",IF(F444="NEW",IF(ISNA(VLOOKUP(E444,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H444" s="24" t="str">
+        <f>IF(J444&lt;&gt;1,"",IF(I444="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I444" s="25" t="str">
+        <f>IF(OR(E444="",E444="!!!",F444="NEW"),"",INDEX(B443:B$2,-1+SUMPRODUCT(MAX(ROW(E443:E$2)*(E444=E443:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J444" s="25" t="str">
+        <f>IF(OR(E444="",E444="!!!",F444="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E444)*(E444=E$2:E444)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E443)*(E2=E$1:E443))))))</f>
+        <v> </v>
+      </c>
+      <c r="K444" s="25" t="str">
+        <f>IF(OR(E444="",E444="!!!",F444="NEW"),"",INDEX(J$1:J443,SUMPRODUCT(MAX(ROW(E$1:E443)*(E444=E$1:E443)))))</f>
+        <v> </v>
+      </c>
+      <c r="L444" s="26"/>
     </row>
     <row r="445" spans="1:12">
       <c r="A445" s="20" t="s">
-        <v>316</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E445" s="21">
+        <f>IF(D445="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F445" s="22" t="str">
+        <f>IF(OR(E445="",E445="!!!"),"",IF(NOT(ISNA(VLOOKUP(E445,E$1:E444,1,FALSE()))),"OLD",IF(AND(E445&lt;&gt;"",E445&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G445" s="23" t="str">
+        <f>IF(OR(E445="",E445="!!!"),"",IF(OR(J445=0,AND(J445=1,K445=1),AND(J445=1,I445="SBJ"),AND(J445=1,I445=0)),"?IN_FOCUS",IF(J445&lt;=2,"?ACTIVATED",IF(J445&lt;&gt;"","?FAMILIAR",IF(F445="NEW",IF(ISNA(VLOOKUP(E445,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H445" s="24" t="str">
+        <f>IF(J445&lt;&gt;1,"",IF(I445="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I445" s="25" t="str">
+        <f>IF(OR(E445="",E445="!!!",F445="NEW"),"",INDEX(B444:B$2,-1+SUMPRODUCT(MAX(ROW(E444:E$2)*(E445=E444:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J445" s="25" t="str">
+        <f>IF(OR(E445="",E445="!!!",F445="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E445)*(E445=E$2:E445)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E444)*(E2=E$1:E444))))))</f>
+        <v> </v>
+      </c>
+      <c r="K445" s="25" t="str">
+        <f>IF(OR(E445="",E445="!!!",F445="NEW"),"",INDEX(J$1:J444,SUMPRODUCT(MAX(ROW(E$1:E444)*(E445=E$1:E444)))))</f>
+        <v> </v>
+      </c>
+      <c r="L445" s="26"/>
     </row>
     <row r="446" spans="1:12">
-      <c r="A446" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="E446" s="21">
-        <f>IF(D446="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F446" s="22" t="str">
-        <f>IF(OR(E446="",E446="!!!"),"",IF(NOT(ISNA(VLOOKUP(E446,E$1:E445,1,FALSE()))),"OLD",IF(AND(E446&lt;&gt;"",E446&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G446" s="23" t="str">
-        <f>IF(OR(E446="",E446="!!!"),"",IF(OR(J446=0,AND(J446=1,K446=1),AND(J446=1,I446="SBJ"),AND(J446=1,I446=0)),"?IN_FOCUS",IF(J446&lt;=2,"?ACTIVATED",IF(J446&lt;&gt;"","?FAMILIAR",IF(F446="NEW",IF(ISNA(VLOOKUP(E446,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H446" s="24" t="str">
-        <f>IF(J446&lt;&gt;1,"",IF(I446="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I446" s="25" t="str">
-        <f>IF(OR(E446="",E446="!!!",F446="NEW"),"",INDEX(B445:B$2,-1+SUMPRODUCT(MAX(ROW(E445:E$2)*(E446=E445:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J446" s="25" t="str">
-        <f>IF(OR(E446="",E446="!!!",F446="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E446)*(E446=E$2:E446)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E445)*(E2=E$1:E445))))))</f>
-        <v> </v>
-      </c>
-      <c r="K446" s="25" t="str">
-        <f>IF(OR(E446="",E446="!!!",F446="NEW"),"",INDEX(J$1:J445,SUMPRODUCT(MAX(ROW(E$1:E445)*(E446=E$1:E445)))))</f>
-        <v> </v>
-      </c>
-      <c r="L446" s="26"/>
+      <c r="A446" s="20"/>
     </row>
     <row r="447" spans="1:12">
       <c r="A447" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="B447" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C447" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D447" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="E447" s="21">
-        <f>IF(D447="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F447" s="22" t="str">
-        <f>IF(OR(E447="",E447="!!!"),"",IF(NOT(ISNA(VLOOKUP(E447,E$1:E446,1,FALSE()))),"OLD",IF(AND(E447&lt;&gt;"",E447&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G447" s="23" t="str">
-        <f>IF(OR(E447="",E447="!!!"),"",IF(OR(J447=0,AND(J447=1,K447=1),AND(J447=1,I447="SBJ"),AND(J447=1,I447=0)),"?IN_FOCUS",IF(J447&lt;=2,"?ACTIVATED",IF(J447&lt;&gt;"","?FAMILIAR",IF(F447="NEW",IF(ISNA(VLOOKUP(E447,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H447" s="24" t="str">
-        <f>IF(J447&lt;&gt;1,"",IF(I447="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I447" s="25" t="str">
-        <f>IF(OR(E447="",E447="!!!",F447="NEW"),"",INDEX(B446:B$2,-1+SUMPRODUCT(MAX(ROW(E446:E$2)*(E447=E446:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J447" s="25" t="str">
-        <f>IF(OR(E447="",E447="!!!",F447="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E447)*(E447=E$2:E447)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E446)*(E2=E$1:E446))))))</f>
-        <v> </v>
-      </c>
-      <c r="K447" s="25" t="str">
-        <f>IF(OR(E447="",E447="!!!",F447="NEW"),"",INDEX(J$1:J446,SUMPRODUCT(MAX(ROW(E$1:E446)*(E447=E$1:E446)))))</f>
-        <v> </v>
-      </c>
-      <c r="L447" s="26"/>
+        <v>319</v>
+      </c>
     </row>
     <row r="448" spans="1:12">
       <c r="A448" s="20" t="s">
-        <v>318</v>
+        <v>167</v>
       </c>
       <c r="E448" s="21">
         <f>IF(D448="?OLD","!!!","")</f>
@@ -17288,7 +17259,16 @@
     </row>
     <row r="449" spans="1:12">
       <c r="A449" s="20" t="s">
-        <v>201</v>
+        <v>320</v>
+      </c>
+      <c r="B449" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C449" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D449" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E449" s="21">
         <f>IF(D449="?OLD","!!!","")</f>
@@ -17322,16 +17302,7 @@
     </row>
     <row r="450" spans="1:12">
       <c r="A450" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="B450" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C450" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D450" s="27" t="s">
-        <v>98</v>
+        <v>321</v>
       </c>
       <c r="E450" s="21">
         <f>IF(D450="?OLD","!!!","")</f>
@@ -17365,7 +17336,7 @@
     </row>
     <row r="451" spans="1:12">
       <c r="A451" s="20" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="E451" s="21">
         <f>IF(D451="?OLD","!!!","")</f>
@@ -17399,13 +17370,16 @@
     </row>
     <row r="452" spans="1:12">
       <c r="A452" s="20" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B452" s="27" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C452" s="27" t="s">
-        <v>103</v>
+        <v>100</v>
+      </c>
+      <c r="D452" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E452" s="21">
         <f>IF(D452="?OLD","!!!","")</f>
@@ -17439,7 +17413,7 @@
     </row>
     <row r="453" spans="1:12">
       <c r="A453" s="20" t="s">
-        <v>111</v>
+        <v>190</v>
       </c>
       <c r="E453" s="21">
         <f>IF(D453="?OLD","!!!","")</f>
@@ -17473,16 +17447,13 @@
     </row>
     <row r="454" spans="1:12">
       <c r="A454" s="20" t="s">
-        <v>137</v>
+        <v>323</v>
       </c>
       <c r="B454" s="27" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="C454" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="D454" s="27" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E454" s="21">
         <f>IF(D454="?OLD","!!!","")</f>
@@ -17516,7 +17487,7 @@
     </row>
     <row r="455" spans="1:12">
       <c r="A455" s="20" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="E455" s="21">
         <f>IF(D455="?OLD","!!!","")</f>
@@ -17550,7 +17521,16 @@
     </row>
     <row r="456" spans="1:12">
       <c r="A456" s="20" t="s">
-        <v>283</v>
+        <v>141</v>
+      </c>
+      <c r="B456" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C456" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D456" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E456" s="21">
         <f>IF(D456="?OLD","!!!","")</f>
@@ -17584,13 +17564,7 @@
     </row>
     <row r="457" spans="1:12">
       <c r="A457" s="20" t="s">
-        <v>321</v>
-      </c>
-      <c r="B457" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="C457" s="27" t="s">
-        <v>185</v>
+        <v>12</v>
       </c>
       <c r="E457" s="21">
         <f>IF(D457="?OLD","!!!","")</f>
@@ -17624,7 +17598,7 @@
     </row>
     <row r="458" spans="1:12">
       <c r="A458" s="20" t="s">
-        <v>105</v>
+        <v>286</v>
       </c>
       <c r="E458" s="21">
         <f>IF(D458="?OLD","!!!","")</f>
@@ -17658,7 +17632,13 @@
     </row>
     <row r="459" spans="1:12">
       <c r="A459" s="20" t="s">
-        <v>322</v>
+        <v>324</v>
+      </c>
+      <c r="B459" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C459" s="27" t="s">
+        <v>188</v>
       </c>
       <c r="E459" s="21">
         <f>IF(D459="?OLD","!!!","")</f>
@@ -17692,7 +17672,7 @@
     </row>
     <row r="460" spans="1:12">
       <c r="A460" s="20" t="s">
-        <v>12</v>
+        <v>108</v>
       </c>
       <c r="E460" s="21">
         <f>IF(D460="?OLD","!!!","")</f>
@@ -17726,7 +17706,7 @@
     </row>
     <row r="461" spans="1:12">
       <c r="A461" s="20" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="E461" s="21">
         <f>IF(D461="?OLD","!!!","")</f>
@@ -17760,7 +17740,7 @@
     </row>
     <row r="462" spans="1:12">
       <c r="A462" s="20" t="s">
-        <v>288</v>
+        <v>12</v>
       </c>
       <c r="E462" s="21">
         <f>IF(D462="?OLD","!!!","")</f>
@@ -17794,7 +17774,7 @@
     </row>
     <row r="463" spans="1:12">
       <c r="A463" s="20" t="s">
-        <v>130</v>
+        <v>303</v>
       </c>
       <c r="E463" s="21">
         <f>IF(D463="?OLD","!!!","")</f>
@@ -17828,13 +17808,7 @@
     </row>
     <row r="464" spans="1:12">
       <c r="A464" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="B464" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="C464" s="27" t="s">
-        <v>117</v>
+        <v>291</v>
       </c>
       <c r="E464" s="21">
         <f>IF(D464="?OLD","!!!","")</f>
@@ -17868,7 +17842,7 @@
     </row>
     <row r="465" spans="1:12">
       <c r="A465" s="20" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="E465" s="21">
         <f>IF(D465="?OLD","!!!","")</f>
@@ -17902,7 +17876,13 @@
     </row>
     <row r="466" spans="1:12">
       <c r="A466" s="20" t="s">
-        <v>213</v>
+        <v>135</v>
+      </c>
+      <c r="B466" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C466" s="27" t="s">
+        <v>119</v>
       </c>
       <c r="E466" s="21">
         <f>IF(D466="?OLD","!!!","")</f>
@@ -17936,7 +17916,7 @@
     </row>
     <row r="467" spans="1:12">
       <c r="A467" s="20" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="E467" s="21">
         <f>IF(D467="?OLD","!!!","")</f>
@@ -17970,7 +17950,7 @@
     </row>
     <row r="468" spans="1:12">
       <c r="A468" s="20" t="s">
-        <v>259</v>
+        <v>216</v>
       </c>
       <c r="E468" s="21">
         <f>IF(D468="?OLD","!!!","")</f>
@@ -18004,13 +17984,7 @@
     </row>
     <row r="469" spans="1:12">
       <c r="A469" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="B469" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="C469" s="27" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="E469" s="21">
         <f>IF(D469="?OLD","!!!","")</f>
@@ -18044,7 +18018,7 @@
     </row>
     <row r="470" spans="1:12">
       <c r="A470" s="20" t="s">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="E470" s="21">
         <f>IF(D470="?OLD","!!!","")</f>
@@ -18078,7 +18052,13 @@
     </row>
     <row r="471" spans="1:12">
       <c r="A471" s="20" t="s">
-        <v>134</v>
+        <v>326</v>
+      </c>
+      <c r="B471" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C471" s="27" t="s">
+        <v>154</v>
       </c>
       <c r="E471" s="21">
         <f>IF(D471="?OLD","!!!","")</f>
@@ -18111,93 +18091,84 @@
       <c r="L471" s="26"/>
     </row>
     <row r="472" spans="1:12">
-      <c r="A472" s="20"/>
+      <c r="A472" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="E472" s="21">
+        <f>IF(D472="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F472" s="22" t="str">
+        <f>IF(OR(E472="",E472="!!!"),"",IF(NOT(ISNA(VLOOKUP(E472,E$1:E471,1,FALSE()))),"OLD",IF(AND(E472&lt;&gt;"",E472&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G472" s="23" t="str">
+        <f>IF(OR(E472="",E472="!!!"),"",IF(OR(J472=0,AND(J472=1,K472=1),AND(J472=1,I472="SBJ"),AND(J472=1,I472=0)),"?IN_FOCUS",IF(J472&lt;=2,"?ACTIVATED",IF(J472&lt;&gt;"","?FAMILIAR",IF(F472="NEW",IF(ISNA(VLOOKUP(E472,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H472" s="24" t="str">
+        <f>IF(J472&lt;&gt;1,"",IF(I472="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I472" s="25" t="str">
+        <f>IF(OR(E472="",E472="!!!",F472="NEW"),"",INDEX(B471:B$2,-1+SUMPRODUCT(MAX(ROW(E471:E$2)*(E472=E471:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J472" s="25" t="str">
+        <f>IF(OR(E472="",E472="!!!",F472="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E472)*(E472=E$2:E472)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E471)*(E2=E$1:E471))))))</f>
+        <v> </v>
+      </c>
+      <c r="K472" s="25" t="str">
+        <f>IF(OR(E472="",E472="!!!",F472="NEW"),"",INDEX(J$1:J471,SUMPRODUCT(MAX(ROW(E$1:E471)*(E472=E$1:E471)))))</f>
+        <v> </v>
+      </c>
+      <c r="L472" s="26"/>
     </row>
     <row r="473" spans="1:12">
       <c r="A473" s="20" t="s">
-        <v>325</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E473" s="21">
+        <f>IF(D473="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F473" s="22" t="str">
+        <f>IF(OR(E473="",E473="!!!"),"",IF(NOT(ISNA(VLOOKUP(E473,E$1:E472,1,FALSE()))),"OLD",IF(AND(E473&lt;&gt;"",E473&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G473" s="23" t="str">
+        <f>IF(OR(E473="",E473="!!!"),"",IF(OR(J473=0,AND(J473=1,K473=1),AND(J473=1,I473="SBJ"),AND(J473=1,I473=0)),"?IN_FOCUS",IF(J473&lt;=2,"?ACTIVATED",IF(J473&lt;&gt;"","?FAMILIAR",IF(F473="NEW",IF(ISNA(VLOOKUP(E473,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H473" s="24" t="str">
+        <f>IF(J473&lt;&gt;1,"",IF(I473="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I473" s="25" t="str">
+        <f>IF(OR(E473="",E473="!!!",F473="NEW"),"",INDEX(B472:B$2,-1+SUMPRODUCT(MAX(ROW(E472:E$2)*(E473=E472:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J473" s="25" t="str">
+        <f>IF(OR(E473="",E473="!!!",F473="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E473)*(E473=E$2:E473)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E472)*(E2=E$1:E472))))))</f>
+        <v> </v>
+      </c>
+      <c r="K473" s="25" t="str">
+        <f>IF(OR(E473="",E473="!!!",F473="NEW"),"",INDEX(J$1:J472,SUMPRODUCT(MAX(ROW(E$1:E472)*(E473=E$1:E472)))))</f>
+        <v> </v>
+      </c>
+      <c r="L473" s="26"/>
     </row>
     <row r="474" spans="1:12">
-      <c r="A474" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="E474" s="21">
-        <f>IF(D474="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F474" s="22" t="str">
-        <f>IF(OR(E474="",E474="!!!"),"",IF(NOT(ISNA(VLOOKUP(E474,E$1:E473,1,FALSE()))),"OLD",IF(AND(E474&lt;&gt;"",E474&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G474" s="23" t="str">
-        <f>IF(OR(E474="",E474="!!!"),"",IF(OR(J474=0,AND(J474=1,K474=1),AND(J474=1,I474="SBJ"),AND(J474=1,I474=0)),"?IN_FOCUS",IF(J474&lt;=2,"?ACTIVATED",IF(J474&lt;&gt;"","?FAMILIAR",IF(F474="NEW",IF(ISNA(VLOOKUP(E474,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H474" s="24" t="str">
-        <f>IF(J474&lt;&gt;1,"",IF(I474="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I474" s="25" t="str">
-        <f>IF(OR(E474="",E474="!!!",F474="NEW"),"",INDEX(B473:B$2,-1+SUMPRODUCT(MAX(ROW(E473:E$2)*(E474=E473:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J474" s="25" t="str">
-        <f>IF(OR(E474="",E474="!!!",F474="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E474)*(E474=E$2:E474)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E473)*(E2=E$1:E473))))))</f>
-        <v> </v>
-      </c>
-      <c r="K474" s="25" t="str">
-        <f>IF(OR(E474="",E474="!!!",F474="NEW"),"",INDEX(J$1:J473,SUMPRODUCT(MAX(ROW(E$1:E473)*(E474=E$1:E473)))))</f>
-        <v> </v>
-      </c>
-      <c r="L474" s="26"/>
+      <c r="A474" s="20"/>
     </row>
     <row r="475" spans="1:12">
       <c r="A475" s="20" t="s">
-        <v>247</v>
-      </c>
-      <c r="B475" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C475" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D475" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="E475" s="21">
-        <f>IF(D475="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F475" s="22" t="str">
-        <f>IF(OR(E475="",E475="!!!"),"",IF(NOT(ISNA(VLOOKUP(E475,E$1:E474,1,FALSE()))),"OLD",IF(AND(E475&lt;&gt;"",E475&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G475" s="23" t="str">
-        <f>IF(OR(E475="",E475="!!!"),"",IF(OR(J475=0,AND(J475=1,K475=1),AND(J475=1,I475="SBJ"),AND(J475=1,I475=0)),"?IN_FOCUS",IF(J475&lt;=2,"?ACTIVATED",IF(J475&lt;&gt;"","?FAMILIAR",IF(F475="NEW",IF(ISNA(VLOOKUP(E475,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H475" s="24" t="str">
-        <f>IF(J475&lt;&gt;1,"",IF(I475="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I475" s="25" t="str">
-        <f>IF(OR(E475="",E475="!!!",F475="NEW"),"",INDEX(B474:B$2,-1+SUMPRODUCT(MAX(ROW(E474:E$2)*(E475=E474:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J475" s="25" t="str">
-        <f>IF(OR(E475="",E475="!!!",F475="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E475)*(E475=E$2:E475)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E474)*(E2=E$1:E474))))))</f>
-        <v> </v>
-      </c>
-      <c r="K475" s="25" t="str">
-        <f>IF(OR(E475="",E475="!!!",F475="NEW"),"",INDEX(J$1:J474,SUMPRODUCT(MAX(ROW(E$1:E474)*(E475=E$1:E474)))))</f>
-        <v> </v>
-      </c>
-      <c r="L475" s="26"/>
+        <v>328</v>
+      </c>
     </row>
     <row r="476" spans="1:12">
       <c r="A476" s="20" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E476" s="21">
         <f>IF(D476="?OLD","!!!","")</f>
@@ -18231,16 +18202,16 @@
     </row>
     <row r="477" spans="1:12">
       <c r="A477" s="20" t="s">
-        <v>326</v>
+        <v>250</v>
       </c>
       <c r="B477" s="27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C477" s="27" t="s">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="D477" s="27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E477" s="21">
         <f>IF(D477="?OLD","!!!","")</f>
@@ -18274,13 +18245,7 @@
     </row>
     <row r="478" spans="1:12">
       <c r="A478" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="B478" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="C478" s="27" t="s">
-        <v>151</v>
+        <v>253</v>
       </c>
       <c r="E478" s="21">
         <f>IF(D478="?OLD","!!!","")</f>
@@ -18314,7 +18279,16 @@
     </row>
     <row r="479" spans="1:12">
       <c r="A479" s="20" t="s">
-        <v>104</v>
+        <v>329</v>
+      </c>
+      <c r="B479" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C479" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="D479" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E479" s="21">
         <f>IF(D479="?OLD","!!!","")</f>
@@ -18348,16 +18322,13 @@
     </row>
     <row r="480" spans="1:12">
       <c r="A480" s="20" t="s">
-        <v>201</v>
+        <v>330</v>
       </c>
       <c r="B480" s="27" t="s">
-        <v>227</v>
+        <v>110</v>
       </c>
       <c r="C480" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="D480" s="27" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="E480" s="21">
         <f>IF(D480="?OLD","!!!","")</f>
@@ -18391,7 +18362,7 @@
     </row>
     <row r="481" spans="1:12">
       <c r="A481" s="20" t="s">
-        <v>318</v>
+        <v>107</v>
       </c>
       <c r="E481" s="21">
         <f>IF(D481="?OLD","!!!","")</f>
@@ -18425,16 +18396,16 @@
     </row>
     <row r="482" spans="1:12">
       <c r="A482" s="20" t="s">
-        <v>328</v>
+        <v>204</v>
       </c>
       <c r="B482" s="27" t="s">
-        <v>163</v>
+        <v>230</v>
       </c>
       <c r="C482" s="27" t="s">
-        <v>124</v>
+        <v>228</v>
       </c>
       <c r="D482" s="27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E482" s="21">
         <f>IF(D482="?OLD","!!!","")</f>
@@ -18468,16 +18439,7 @@
     </row>
     <row r="483" spans="1:12">
       <c r="A483" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="B483" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C483" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="D483" s="27" t="s">
-        <v>98</v>
+        <v>321</v>
       </c>
       <c r="E483" s="21">
         <f>IF(D483="?OLD","!!!","")</f>
@@ -18511,7 +18473,16 @@
     </row>
     <row r="484" spans="1:12">
       <c r="A484" s="20" t="s">
-        <v>329</v>
+        <v>331</v>
+      </c>
+      <c r="B484" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C484" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="D484" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E484" s="21">
         <f>IF(D484="?OLD","!!!","")</f>
@@ -18545,7 +18516,16 @@
     </row>
     <row r="485" spans="1:12">
       <c r="A485" s="20" t="s">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="B485" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C485" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="D485" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="E485" s="21">
         <f>IF(D485="?OLD","!!!","")</f>
@@ -18578,7 +18558,75 @@
       <c r="L485" s="26"/>
     </row>
     <row r="486" spans="1:12">
-      <c r="A486" s="20"/>
+      <c r="A486" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="E486" s="21">
+        <f>IF(D486="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F486" s="22" t="str">
+        <f>IF(OR(E486="",E486="!!!"),"",IF(NOT(ISNA(VLOOKUP(E486,E$1:E485,1,FALSE()))),"OLD",IF(AND(E486&lt;&gt;"",E486&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G486" s="23" t="str">
+        <f>IF(OR(E486="",E486="!!!"),"",IF(OR(J486=0,AND(J486=1,K486=1),AND(J486=1,I486="SBJ"),AND(J486=1,I486=0)),"?IN_FOCUS",IF(J486&lt;=2,"?ACTIVATED",IF(J486&lt;&gt;"","?FAMILIAR",IF(F486="NEW",IF(ISNA(VLOOKUP(E486,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H486" s="24" t="str">
+        <f>IF(J486&lt;&gt;1,"",IF(I486="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I486" s="25" t="str">
+        <f>IF(OR(E486="",E486="!!!",F486="NEW"),"",INDEX(B485:B$2,-1+SUMPRODUCT(MAX(ROW(E485:E$2)*(E486=E485:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J486" s="25" t="str">
+        <f>IF(OR(E486="",E486="!!!",F486="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E486)*(E486=E$2:E486)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E485)*(E2=E$1:E485))))))</f>
+        <v> </v>
+      </c>
+      <c r="K486" s="25" t="str">
+        <f>IF(OR(E486="",E486="!!!",F486="NEW"),"",INDEX(J$1:J485,SUMPRODUCT(MAX(ROW(E$1:E485)*(E486=E$1:E485)))))</f>
+        <v> </v>
+      </c>
+      <c r="L486" s="26"/>
+    </row>
+    <row r="487" spans="1:12">
+      <c r="A487" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="E487" s="21">
+        <f>IF(D487="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F487" s="22" t="str">
+        <f>IF(OR(E487="",E487="!!!"),"",IF(NOT(ISNA(VLOOKUP(E487,E$1:E486,1,FALSE()))),"OLD",IF(AND(E487&lt;&gt;"",E487&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G487" s="23" t="str">
+        <f>IF(OR(E487="",E487="!!!"),"",IF(OR(J487=0,AND(J487=1,K487=1),AND(J487=1,I487="SBJ"),AND(J487=1,I487=0)),"?IN_FOCUS",IF(J487&lt;=2,"?ACTIVATED",IF(J487&lt;&gt;"","?FAMILIAR",IF(F487="NEW",IF(ISNA(VLOOKUP(E487,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H487" s="24" t="str">
+        <f>IF(J487&lt;&gt;1,"",IF(I487="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I487" s="25" t="str">
+        <f>IF(OR(E487="",E487="!!!",F487="NEW"),"",INDEX(B486:B$2,-1+SUMPRODUCT(MAX(ROW(E486:E$2)*(E487=E486:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J487" s="25" t="str">
+        <f>IF(OR(E487="",E487="!!!",F487="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E487)*(E487=E$2:E487)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E486)*(E2=E$1:E486))))))</f>
+        <v> </v>
+      </c>
+      <c r="K487" s="25" t="str">
+        <f>IF(OR(E487="",E487="!!!",F487="NEW"),"",INDEX(J$1:J486,SUMPRODUCT(MAX(ROW(E$1:E486)*(E487=E$1:E486)))))</f>
+        <v> </v>
+      </c>
+      <c r="L487" s="26"/>
+    </row>
+    <row r="488" spans="1:12">
+      <c r="A488" s="20"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
